--- a/output/2024-09-10.xlsx
+++ b/output/2024-09-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.34</v>
+        <v>3.56</v>
       </c>
       <c r="F14" t="n">
-        <v>10.37</v>
+        <v>10.54</v>
       </c>
       <c r="G14" t="n">
-        <v>127.9</v>
+        <v>118.6</v>
       </c>
       <c r="H14" t="n">
-        <v>22.8</v>
+        <v>19</v>
       </c>
       <c r="I14" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>53.08</v>
+        <v>-56.17</v>
       </c>
       <c r="K14" t="n">
-        <v>-11.6</v>
+        <v>93.36</v>
       </c>
       <c r="L14" t="n">
-        <v>54.33</v>
+        <v>108.95</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:39:12</t>
+          <t>06:39:09</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.75</v>
+        <v>3.51</v>
       </c>
       <c r="F15" t="n">
-        <v>10.08</v>
+        <v>10.48</v>
       </c>
       <c r="G15" t="n">
-        <v>125.8</v>
+        <v>119.5</v>
       </c>
       <c r="H15" t="n">
-        <v>23.8</v>
+        <v>26.6</v>
       </c>
       <c r="I15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-49.05</v>
+        <v>-103.46</v>
       </c>
       <c r="K15" t="n">
-        <v>17.41</v>
+        <v>-42.9</v>
       </c>
       <c r="L15" t="n">
-        <v>52.05</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:40:42</t>
+          <t>06:40:40</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.24</v>
+        <v>3.06</v>
       </c>
       <c r="F16" t="n">
-        <v>10.61</v>
+        <v>10.36</v>
       </c>
       <c r="G16" t="n">
-        <v>122.9</v>
+        <v>136.3</v>
       </c>
       <c r="H16" t="n">
-        <v>20.5</v>
+        <v>17.8</v>
       </c>
       <c r="I16" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>-52.12</v>
+        <v>143.36</v>
       </c>
       <c r="K16" t="n">
-        <v>-9.02</v>
+        <v>-127.76</v>
       </c>
       <c r="L16" t="n">
-        <v>52.89</v>
+        <v>192.02</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:44:53</t>
+          <t>06:45:08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4.27</v>
+        <v>3.35</v>
       </c>
       <c r="F17" t="n">
-        <v>10.4</v>
+        <v>10.07</v>
       </c>
       <c r="G17" t="n">
-        <v>121.6</v>
+        <v>114.3</v>
       </c>
       <c r="H17" t="n">
-        <v>26.1</v>
+        <v>30.8</v>
       </c>
       <c r="I17" t="n">
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>46.59</v>
+        <v>-78.11</v>
       </c>
       <c r="K17" t="n">
-        <v>-82.93000000000001</v>
+        <v>-7.89</v>
       </c>
       <c r="L17" t="n">
-        <v>95.12</v>
+        <v>78.51000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:46:21</t>
+          <t>06:46:01</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.85</v>
+        <v>3.57</v>
       </c>
       <c r="F18" t="n">
-        <v>10.12</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>133.4</v>
+        <v>129.2</v>
       </c>
       <c r="H18" t="n">
-        <v>28.3</v>
+        <v>19.5</v>
       </c>
       <c r="I18" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>17.42</v>
+        <v>-251.9</v>
       </c>
       <c r="K18" t="n">
-        <v>44.05</v>
+        <v>-63.96</v>
       </c>
       <c r="L18" t="n">
-        <v>47.37</v>
+        <v>259.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:48:22</t>
+          <t>06:48:17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.81</v>
+        <v>3.43</v>
       </c>
       <c r="F19" t="n">
-        <v>11.24</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="G19" t="n">
-        <v>120.9</v>
+        <v>127.5</v>
       </c>
       <c r="H19" t="n">
-        <v>26.8</v>
+        <v>23.8</v>
       </c>
       <c r="I19" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>10.63</v>
+        <v>-49.52</v>
       </c>
       <c r="K19" t="n">
-        <v>-34.76</v>
+        <v>43.9</v>
       </c>
       <c r="L19" t="n">
-        <v>36.35</v>
+        <v>66.18000000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:53:09</t>
+          <t>06:53:29</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="F20" t="n">
-        <v>9.73</v>
+        <v>10.71</v>
       </c>
       <c r="G20" t="n">
-        <v>137.1</v>
+        <v>125.1</v>
       </c>
       <c r="H20" t="n">
-        <v>29.4</v>
+        <v>22.3</v>
       </c>
       <c r="I20" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>71.56</v>
+        <v>-133.94</v>
       </c>
       <c r="K20" t="n">
-        <v>-253.48</v>
+        <v>-27.89</v>
       </c>
       <c r="L20" t="n">
-        <v>263.38</v>
+        <v>136.81</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:54:10</t>
+          <t>06:55:53</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.94</v>
+        <v>4.28</v>
       </c>
       <c r="F21" t="n">
-        <v>10.56</v>
+        <v>10.14</v>
       </c>
       <c r="G21" t="n">
-        <v>136.2</v>
+        <v>118.4</v>
       </c>
       <c r="H21" t="n">
-        <v>25.1</v>
+        <v>28</v>
       </c>
       <c r="I21" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>117.84</v>
+        <v>70.56</v>
       </c>
       <c r="K21" t="n">
-        <v>24.89</v>
+        <v>172.76</v>
       </c>
       <c r="L21" t="n">
-        <v>120.44</v>
+        <v>186.61</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:55:32</t>
+          <t>06:57:50</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>4.32</v>
+        <v>2.81</v>
       </c>
       <c r="F22" t="n">
-        <v>9.98</v>
+        <v>9.92</v>
       </c>
       <c r="G22" t="n">
-        <v>131.7</v>
+        <v>132.1</v>
       </c>
       <c r="H22" t="n">
         <v>25.7</v>
       </c>
       <c r="I22" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>27.66</v>
+        <v>14.21</v>
       </c>
       <c r="K22" t="n">
-        <v>-20.14</v>
+        <v>127.7</v>
       </c>
       <c r="L22" t="n">
-        <v>34.21</v>
+        <v>128.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:00:19</t>
+          <t>07:03:00</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.13</v>
+        <v>3.64</v>
       </c>
       <c r="F23" t="n">
-        <v>10.36</v>
+        <v>10.9</v>
       </c>
       <c r="G23" t="n">
-        <v>137.4</v>
+        <v>130</v>
       </c>
       <c r="H23" t="n">
-        <v>13.3</v>
+        <v>22.5</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-34.7</v>
+        <v>-292.37</v>
       </c>
       <c r="K23" t="n">
-        <v>123.03</v>
+        <v>168.62</v>
       </c>
       <c r="L23" t="n">
-        <v>127.83</v>
+        <v>337.51</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:02:21</t>
+          <t>07:05:08</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.77</v>
+        <v>4.17</v>
       </c>
       <c r="F24" t="n">
-        <v>10.37</v>
+        <v>10.15</v>
       </c>
       <c r="G24" t="n">
-        <v>114.7</v>
+        <v>108.9</v>
       </c>
       <c r="H24" t="n">
-        <v>30</v>
+        <v>26.2</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>-131.64</v>
+        <v>62</v>
       </c>
       <c r="K24" t="n">
-        <v>375.91</v>
+        <v>533.14</v>
       </c>
       <c r="L24" t="n">
-        <v>398.29</v>
+        <v>536.73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:04:10</t>
+          <t>07:06:07</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.67</v>
+        <v>3.34</v>
       </c>
       <c r="F25" t="n">
-        <v>10.44</v>
+        <v>10.77</v>
       </c>
       <c r="G25" t="n">
-        <v>132.1</v>
+        <v>134.5</v>
       </c>
       <c r="H25" t="n">
-        <v>22.1</v>
+        <v>20.2</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>79.05</v>
+        <v>-203.3</v>
       </c>
       <c r="K25" t="n">
-        <v>192.04</v>
+        <v>123.98</v>
       </c>
       <c r="L25" t="n">
-        <v>207.68</v>
+        <v>238.12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:09:43</t>
+          <t>07:11:52</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.81</v>
+        <v>3.38</v>
       </c>
       <c r="F26" t="n">
-        <v>10.51</v>
+        <v>10.82</v>
       </c>
       <c r="G26" t="n">
-        <v>115.9</v>
+        <v>121.1</v>
       </c>
       <c r="H26" t="n">
-        <v>25.4</v>
+        <v>22.9</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-107.34</v>
+        <v>-31.26</v>
       </c>
       <c r="K26" t="n">
-        <v>163.52</v>
+        <v>-387.35</v>
       </c>
       <c r="L26" t="n">
-        <v>195.6</v>
+        <v>388.61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:11:00</t>
+          <t>07:13:47</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.32</v>
+        <v>4.08</v>
       </c>
       <c r="F27" t="n">
-        <v>10.64</v>
+        <v>10.41</v>
       </c>
       <c r="G27" t="n">
-        <v>131.8</v>
+        <v>124.1</v>
       </c>
       <c r="H27" t="n">
-        <v>19.6</v>
+        <v>27.6</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>-47.53</v>
+        <v>348.74</v>
       </c>
       <c r="K27" t="n">
-        <v>-471.05</v>
+        <v>-150.4</v>
       </c>
       <c r="L27" t="n">
-        <v>473.44</v>
+        <v>379.78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:12:08</t>
+          <t>07:15:44</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="F28" t="n">
-        <v>10.79</v>
+        <v>10.66</v>
       </c>
       <c r="G28" t="n">
-        <v>122.2</v>
+        <v>127.1</v>
       </c>
       <c r="H28" t="n">
-        <v>25.6</v>
+        <v>17</v>
       </c>
       <c r="I28" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>-379.79</v>
+        <v>407.71</v>
       </c>
       <c r="K28" t="n">
-        <v>-255.27</v>
+        <v>-180.62</v>
       </c>
       <c r="L28" t="n">
-        <v>457.61</v>
+        <v>445.93</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:20:17</t>
+          <t>07:26:20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.41</v>
+        <v>3.64</v>
       </c>
       <c r="F29" t="n">
-        <v>10.04</v>
+        <v>10.17</v>
       </c>
       <c r="G29" t="n">
-        <v>130.7</v>
+        <v>129.9</v>
       </c>
       <c r="H29" t="n">
-        <v>19.2</v>
+        <v>31.2</v>
       </c>
       <c r="I29" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-107.51</v>
+        <v>-201.65</v>
       </c>
       <c r="K29" t="n">
-        <v>10.18</v>
+        <v>-108.33</v>
       </c>
       <c r="L29" t="n">
-        <v>107.99</v>
+        <v>228.91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:22:44</t>
+          <t>07:27:25</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>3.68</v>
+        <v>4.05</v>
       </c>
       <c r="F30" t="n">
-        <v>10.28</v>
+        <v>10.66</v>
       </c>
       <c r="G30" t="n">
-        <v>132.9</v>
+        <v>120.9</v>
       </c>
       <c r="H30" t="n">
-        <v>16.7</v>
+        <v>19.5</v>
       </c>
       <c r="I30" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-32.45</v>
+        <v>-96.42</v>
       </c>
       <c r="K30" t="n">
-        <v>88.41</v>
+        <v>-51.89</v>
       </c>
       <c r="L30" t="n">
-        <v>94.18000000000001</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:24:04</t>
+          <t>07:29:43</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>3.96</v>
+        <v>4.54</v>
       </c>
       <c r="F31" t="n">
-        <v>10.68</v>
+        <v>10.14</v>
       </c>
       <c r="G31" t="n">
-        <v>129.9</v>
+        <v>126.5</v>
       </c>
       <c r="H31" t="n">
-        <v>18.9</v>
+        <v>16.3</v>
       </c>
       <c r="I31" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>18.96</v>
+        <v>182.14</v>
       </c>
       <c r="K31" t="n">
-        <v>-122.59</v>
+        <v>51.37</v>
       </c>
       <c r="L31" t="n">
-        <v>124.05</v>
+        <v>189.25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:27:22</t>
+          <t>07:33:56</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.86</v>
+        <v>3.53</v>
       </c>
       <c r="F32" t="n">
-        <v>10.98</v>
+        <v>10.46</v>
       </c>
       <c r="G32" t="n">
-        <v>134.4</v>
+        <v>133.5</v>
       </c>
       <c r="H32" t="n">
-        <v>19.1</v>
+        <v>25.8</v>
       </c>
       <c r="I32" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>18.34</v>
+        <v>17.87</v>
       </c>
       <c r="K32" t="n">
-        <v>61.33</v>
+        <v>52.35</v>
       </c>
       <c r="L32" t="n">
-        <v>64.01000000000001</v>
+        <v>55.32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:28:18</t>
+          <t>07:35:34</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.73</v>
+        <v>4.07</v>
       </c>
       <c r="F33" t="n">
-        <v>10.28</v>
+        <v>10.09</v>
       </c>
       <c r="G33" t="n">
-        <v>132.5</v>
+        <v>127</v>
       </c>
       <c r="H33" t="n">
-        <v>19.4</v>
+        <v>23.1</v>
       </c>
       <c r="I33" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>-10.4</v>
+        <v>108.11</v>
       </c>
       <c r="K33" t="n">
-        <v>20.11</v>
+        <v>-137.56</v>
       </c>
       <c r="L33" t="n">
-        <v>22.64</v>
+        <v>174.96</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:29:46</t>
+          <t>07:37:21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
       <c r="F34" t="n">
-        <v>10.66</v>
+        <v>10.74</v>
       </c>
       <c r="G34" t="n">
-        <v>137.6</v>
+        <v>132.8</v>
       </c>
       <c r="H34" t="n">
-        <v>21.6</v>
+        <v>26.6</v>
       </c>
       <c r="I34" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>-149.75</v>
+        <v>72.91</v>
       </c>
       <c r="K34" t="n">
-        <v>21.57</v>
+        <v>115</v>
       </c>
       <c r="L34" t="n">
-        <v>151.3</v>
+        <v>136.16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:34:04</t>
+          <t>07:43:24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>4.37</v>
+        <v>3.35</v>
       </c>
       <c r="F35" t="n">
-        <v>10.32</v>
+        <v>10.64</v>
       </c>
       <c r="G35" t="n">
-        <v>131.6</v>
+        <v>134.1</v>
       </c>
       <c r="H35" t="n">
-        <v>20.9</v>
+        <v>27.1</v>
       </c>
       <c r="I35" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-90.65000000000001</v>
+        <v>-10.33</v>
       </c>
       <c r="K35" t="n">
-        <v>256.3</v>
+        <v>183.94</v>
       </c>
       <c r="L35" t="n">
-        <v>271.86</v>
+        <v>184.23</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:35:58</t>
+          <t>07:44:20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.77</v>
+        <v>3.54</v>
       </c>
       <c r="F36" t="n">
-        <v>10.61</v>
+        <v>10.05</v>
       </c>
       <c r="G36" t="n">
-        <v>120.4</v>
+        <v>133</v>
       </c>
       <c r="H36" t="n">
-        <v>14.9</v>
+        <v>21.7</v>
       </c>
       <c r="I36" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>279.64</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>406.74</v>
+        <v>-225.84</v>
       </c>
       <c r="L36" t="n">
-        <v>493.59</v>
+        <v>226.02</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:37:35</t>
+          <t>07:45:54</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.22</v>
+        <v>3.06</v>
       </c>
       <c r="F37" t="n">
-        <v>10.05</v>
+        <v>10.64</v>
       </c>
       <c r="G37" t="n">
-        <v>125.3</v>
+        <v>131.7</v>
       </c>
       <c r="H37" t="n">
-        <v>32.2</v>
+        <v>25.2</v>
       </c>
       <c r="I37" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-146.44</v>
+        <v>-167.02</v>
       </c>
       <c r="K37" t="n">
-        <v>-26.01</v>
+        <v>69.19</v>
       </c>
       <c r="L37" t="n">
-        <v>148.74</v>
+        <v>180.78</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:42:05</t>
+          <t>07:51:18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="F38" t="n">
-        <v>10.82</v>
+        <v>10.21</v>
       </c>
       <c r="G38" t="n">
-        <v>118.1</v>
+        <v>138</v>
       </c>
       <c r="H38" t="n">
-        <v>20.8</v>
+        <v>24.8</v>
       </c>
       <c r="I38" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>-35.22</v>
+        <v>618.04</v>
       </c>
       <c r="K38" t="n">
-        <v>204.6</v>
+        <v>-14.9</v>
       </c>
       <c r="L38" t="n">
-        <v>207.61</v>
+        <v>618.22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:44:28</t>
+          <t>07:53:02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.02</v>
+        <v>4.07</v>
       </c>
       <c r="F39" t="n">
-        <v>10.55</v>
+        <v>10.2</v>
       </c>
       <c r="G39" t="n">
-        <v>117.6</v>
+        <v>136.7</v>
       </c>
       <c r="H39" t="n">
-        <v>25.4</v>
+        <v>26.9</v>
       </c>
       <c r="I39" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>34.52</v>
+        <v>136.33</v>
       </c>
       <c r="K39" t="n">
-        <v>55.84</v>
+        <v>100.03</v>
       </c>
       <c r="L39" t="n">
-        <v>65.65000000000001</v>
+        <v>169.09</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:45:24</t>
+          <t>07:54:43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.92</v>
+        <v>4.18</v>
       </c>
       <c r="F40" t="n">
-        <v>9.970000000000001</v>
+        <v>10.84</v>
       </c>
       <c r="G40" t="n">
-        <v>122.2</v>
+        <v>134.4</v>
       </c>
       <c r="H40" t="n">
-        <v>25.7</v>
+        <v>22.7</v>
       </c>
       <c r="I40" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-42.16</v>
+        <v>35.07</v>
       </c>
       <c r="K40" t="n">
-        <v>-514.41</v>
+        <v>-606.8200000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>516.14</v>
+        <v>607.83</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:51:37</t>
+          <t>07:59:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.39</v>
+        <v>4.13</v>
       </c>
       <c r="F41" t="n">
-        <v>10.52</v>
+        <v>10.25</v>
       </c>
       <c r="G41" t="n">
-        <v>128.9</v>
+        <v>125.9</v>
       </c>
       <c r="H41" t="n">
-        <v>31.7</v>
+        <v>23.8</v>
       </c>
       <c r="I41" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-266.29</v>
+        <v>-260.21</v>
       </c>
       <c r="K41" t="n">
-        <v>-274.53</v>
+        <v>-148.89</v>
       </c>
       <c r="L41" t="n">
-        <v>382.46</v>
+        <v>299.8</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>07:53:01</t>
+          <t>08:00:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="F42" t="n">
-        <v>10.83</v>
+        <v>10.41</v>
       </c>
       <c r="G42" t="n">
-        <v>131.1</v>
+        <v>124.3</v>
       </c>
       <c r="H42" t="n">
-        <v>21</v>
+        <v>24.3</v>
       </c>
       <c r="I42" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>109.33</v>
+        <v>492.29</v>
       </c>
       <c r="K42" t="n">
-        <v>-117.32</v>
+        <v>-206.53</v>
       </c>
       <c r="L42" t="n">
-        <v>160.37</v>
+        <v>533.86</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>07:54:16</t>
+          <t>08:01:42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.96</v>
+        <v>4.15</v>
       </c>
       <c r="F43" t="n">
-        <v>9.800000000000001</v>
+        <v>10.99</v>
       </c>
       <c r="G43" t="n">
-        <v>131.6</v>
+        <v>136.4</v>
       </c>
       <c r="H43" t="n">
-        <v>21.2</v>
+        <v>27.4</v>
       </c>
       <c r="I43" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>201.23</v>
+        <v>564.83</v>
       </c>
       <c r="K43" t="n">
-        <v>421.16</v>
+        <v>604.72</v>
       </c>
       <c r="L43" t="n">
-        <v>466.77</v>
+        <v>827.48</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:05:41</t>
+          <t>08:13:11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.4</v>
+        <v>3.62</v>
       </c>
       <c r="F44" t="n">
-        <v>10.52</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>121.1</v>
+        <v>136.2</v>
       </c>
       <c r="H44" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="I44" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>103.28</v>
+        <v>-125.48</v>
       </c>
       <c r="K44" t="n">
-        <v>-106.7</v>
+        <v>-204.41</v>
       </c>
       <c r="L44" t="n">
-        <v>148.5</v>
+        <v>239.85</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:07:35</t>
+          <t>08:13:59</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>3.77</v>
+        <v>4.08</v>
       </c>
       <c r="F45" t="n">
-        <v>10.44</v>
+        <v>9.65</v>
       </c>
       <c r="G45" t="n">
-        <v>125.4</v>
+        <v>127.8</v>
       </c>
       <c r="H45" t="n">
-        <v>28.3</v>
+        <v>23.1</v>
       </c>
       <c r="I45" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>16.35</v>
+        <v>-10.03</v>
       </c>
       <c r="K45" t="n">
-        <v>-76.93000000000001</v>
+        <v>-74.06</v>
       </c>
       <c r="L45" t="n">
-        <v>78.65000000000001</v>
+        <v>74.73999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:08:38</t>
+          <t>08:16:12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.82</v>
+        <v>3.89</v>
       </c>
       <c r="F46" t="n">
-        <v>11.24</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G46" t="n">
-        <v>138</v>
+        <v>125.2</v>
       </c>
       <c r="H46" t="n">
-        <v>28.4</v>
+        <v>31.9</v>
       </c>
       <c r="I46" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-8.51</v>
+        <v>47.18</v>
       </c>
       <c r="K46" t="n">
-        <v>-26.65</v>
+        <v>-15.13</v>
       </c>
       <c r="L46" t="n">
-        <v>27.97</v>
+        <v>49.54</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:12:35</t>
+          <t>08:20:45</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.11</v>
+        <v>4.22</v>
       </c>
       <c r="F47" t="n">
-        <v>10.31</v>
+        <v>10.19</v>
       </c>
       <c r="G47" t="n">
-        <v>113</v>
+        <v>140</v>
       </c>
       <c r="H47" t="n">
-        <v>27.7</v>
+        <v>21.3</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>254.22</v>
+        <v>109.78</v>
       </c>
       <c r="K47" t="n">
-        <v>-58.3</v>
+        <v>197.83</v>
       </c>
       <c r="L47" t="n">
-        <v>260.82</v>
+        <v>226.25</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:14:33</t>
+          <t>08:22:07</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>3.78</v>
+        <v>4.66</v>
       </c>
       <c r="F48" t="n">
-        <v>10.22</v>
+        <v>11.27</v>
       </c>
       <c r="G48" t="n">
-        <v>132.7</v>
+        <v>122.1</v>
       </c>
       <c r="H48" t="n">
-        <v>20</v>
+        <v>16.3</v>
       </c>
       <c r="I48" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>-131.96</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>102.7</v>
+        <v>-461.5</v>
       </c>
       <c r="L48" t="n">
-        <v>167.22</v>
+        <v>471.97</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:17:15</t>
+          <t>08:23:50</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="F49" t="n">
-        <v>9.68</v>
+        <v>9.6</v>
       </c>
       <c r="G49" t="n">
-        <v>120</v>
+        <v>121.2</v>
       </c>
       <c r="H49" t="n">
-        <v>31</v>
+        <v>21.8</v>
       </c>
       <c r="I49" t="n">
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>130.45</v>
+        <v>-34.25</v>
       </c>
       <c r="K49" t="n">
-        <v>90.12</v>
+        <v>-215.56</v>
       </c>
       <c r="L49" t="n">
-        <v>158.55</v>
+        <v>218.26</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:21:09</t>
+          <t>08:27:48</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>3.75</v>
+        <v>4.06</v>
       </c>
       <c r="F50" t="n">
-        <v>10.47</v>
+        <v>10.32</v>
       </c>
       <c r="G50" t="n">
-        <v>122</v>
+        <v>132.3</v>
       </c>
       <c r="H50" t="n">
-        <v>23.7</v>
+        <v>28.9</v>
       </c>
       <c r="I50" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-74.66</v>
+        <v>29.5</v>
       </c>
       <c r="K50" t="n">
-        <v>-111.52</v>
+        <v>-203.81</v>
       </c>
       <c r="L50" t="n">
-        <v>134.21</v>
+        <v>205.94</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:22:05</t>
+          <t>08:29:11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.66</v>
+        <v>4.07</v>
       </c>
       <c r="F51" t="n">
-        <v>10.51</v>
+        <v>10.65</v>
       </c>
       <c r="G51" t="n">
-        <v>131.8</v>
+        <v>122.3</v>
       </c>
       <c r="H51" t="n">
-        <v>19.2</v>
+        <v>26.5</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-94.92</v>
+        <v>-167.87</v>
       </c>
       <c r="K51" t="n">
-        <v>322.08</v>
+        <v>-139.08</v>
       </c>
       <c r="L51" t="n">
-        <v>335.78</v>
+        <v>218</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:24:42</t>
+          <t>08:31:13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.82</v>
+        <v>4.29</v>
       </c>
       <c r="F52" t="n">
-        <v>10.64</v>
+        <v>10.87</v>
       </c>
       <c r="G52" t="n">
-        <v>114.8</v>
+        <v>140.8</v>
       </c>
       <c r="H52" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="I52" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-1.31</v>
+        <v>-55.04</v>
       </c>
       <c r="K52" t="n">
-        <v>232.48</v>
+        <v>97.62</v>
       </c>
       <c r="L52" t="n">
-        <v>232.48</v>
+        <v>112.07</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:30:22</t>
+          <t>08:37:07</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.8</v>
+        <v>3.87</v>
       </c>
       <c r="F53" t="n">
-        <v>10.54</v>
+        <v>10.43</v>
       </c>
       <c r="G53" t="n">
-        <v>128.9</v>
+        <v>146.4</v>
       </c>
       <c r="H53" t="n">
-        <v>33.7</v>
+        <v>16.3</v>
       </c>
       <c r="I53" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-288.6</v>
+        <v>15.5</v>
       </c>
       <c r="K53" t="n">
-        <v>-480.29</v>
+        <v>-303.52</v>
       </c>
       <c r="L53" t="n">
-        <v>560.33</v>
+        <v>303.91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:32:41</t>
+          <t>08:38:20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>4.02</v>
+        <v>3.99</v>
       </c>
       <c r="F54" t="n">
-        <v>9.91</v>
+        <v>10.59</v>
       </c>
       <c r="G54" t="n">
-        <v>129.2</v>
+        <v>121.7</v>
       </c>
       <c r="H54" t="n">
-        <v>21</v>
+        <v>22.5</v>
       </c>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>53.85</v>
+        <v>179.2</v>
       </c>
       <c r="K54" t="n">
-        <v>-366.77</v>
+        <v>217.02</v>
       </c>
       <c r="L54" t="n">
-        <v>370.7</v>
+        <v>281.45</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:33:31</t>
+          <t>08:39:33</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.62</v>
+        <v>4.04</v>
       </c>
       <c r="F55" t="n">
-        <v>10.7</v>
+        <v>10.62</v>
       </c>
       <c r="G55" t="n">
-        <v>124.8</v>
+        <v>112.7</v>
       </c>
       <c r="H55" t="n">
-        <v>25.6</v>
+        <v>19.5</v>
       </c>
       <c r="I55" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-44.31</v>
+        <v>-285.28</v>
       </c>
       <c r="K55" t="n">
-        <v>-24.22</v>
+        <v>251.26</v>
       </c>
       <c r="L55" t="n">
-        <v>50.49</v>
+        <v>380.16</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:38:27</t>
+          <t>08:44:02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.15</v>
+        <v>4.06</v>
       </c>
       <c r="F56" t="n">
-        <v>10.22</v>
+        <v>10.37</v>
       </c>
       <c r="G56" t="n">
-        <v>134.3</v>
+        <v>114.8</v>
       </c>
       <c r="H56" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I56" t="n">
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>594.54</v>
+        <v>186.95</v>
       </c>
       <c r="K56" t="n">
-        <v>-814.97</v>
+        <v>-299.77</v>
       </c>
       <c r="L56" t="n">
-        <v>1008.79</v>
+        <v>353.29</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:40:35</t>
+          <t>08:45:26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.91</v>
+        <v>4.39</v>
       </c>
       <c r="F57" t="n">
-        <v>10.73</v>
+        <v>10.5</v>
       </c>
       <c r="G57" t="n">
-        <v>125.8</v>
+        <v>114.9</v>
       </c>
       <c r="H57" t="n">
-        <v>16.3</v>
+        <v>21.6</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-70.2</v>
+        <v>-709.73</v>
       </c>
       <c r="K57" t="n">
-        <v>537.91</v>
+        <v>-501.23</v>
       </c>
       <c r="L57" t="n">
-        <v>542.48</v>
+        <v>868.88</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:42:19</t>
+          <t>08:47:05</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.05</v>
+        <v>3.88</v>
       </c>
       <c r="F58" t="n">
-        <v>10.12</v>
+        <v>10.59</v>
       </c>
       <c r="G58" t="n">
-        <v>136</v>
+        <v>124.9</v>
       </c>
       <c r="H58" t="n">
         <v>26.1</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>237.47</v>
+        <v>-213.88</v>
       </c>
       <c r="K58" t="n">
-        <v>308.97</v>
+        <v>152.82</v>
       </c>
       <c r="L58" t="n">
-        <v>389.69</v>
+        <v>262.87</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:54:46</t>
+          <t>08:59:19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.26</v>
+        <v>4.22</v>
       </c>
       <c r="F59" t="n">
-        <v>10.58</v>
+        <v>10.74</v>
       </c>
       <c r="G59" t="n">
-        <v>135.5</v>
+        <v>127.6</v>
       </c>
       <c r="H59" t="n">
-        <v>22.5</v>
+        <v>24.7</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-85.88</v>
+        <v>193.53</v>
       </c>
       <c r="K59" t="n">
-        <v>68.67</v>
+        <v>79.78</v>
       </c>
       <c r="L59" t="n">
-        <v>109.96</v>
+        <v>209.33</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>08:55:38</t>
+          <t>09:01:55</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.43</v>
+        <v>4.75</v>
       </c>
       <c r="F60" t="n">
-        <v>10.47</v>
+        <v>9.76</v>
       </c>
       <c r="G60" t="n">
-        <v>114</v>
+        <v>122.3</v>
       </c>
       <c r="H60" t="n">
-        <v>25</v>
+        <v>30.3</v>
       </c>
       <c r="I60" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>52.51</v>
+        <v>-31.54</v>
       </c>
       <c r="K60" t="n">
-        <v>-22.61</v>
+        <v>231.92</v>
       </c>
       <c r="L60" t="n">
-        <v>57.17</v>
+        <v>234.05</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>08:57:52</t>
+          <t>09:03:31</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="F61" t="n">
-        <v>10.2</v>
+        <v>10.54</v>
       </c>
       <c r="G61" t="n">
-        <v>129</v>
+        <v>126.3</v>
       </c>
       <c r="H61" t="n">
-        <v>23.9</v>
+        <v>23.7</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>-11.96</v>
+        <v>225.49</v>
       </c>
       <c r="K61" t="n">
-        <v>-63.02</v>
+        <v>2.34</v>
       </c>
       <c r="L61" t="n">
-        <v>64.14</v>
+        <v>225.5</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:02:48</t>
+          <t>09:07:36</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>4.54</v>
+        <v>3.92</v>
       </c>
       <c r="F62" t="n">
-        <v>10.33</v>
+        <v>10.94</v>
       </c>
       <c r="G62" t="n">
-        <v>144.7</v>
+        <v>142</v>
       </c>
       <c r="H62" t="n">
-        <v>24.5</v>
+        <v>19</v>
       </c>
       <c r="I62" t="n">
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>-59.56</v>
+        <v>105.06</v>
       </c>
       <c r="K62" t="n">
-        <v>-152.26</v>
+        <v>-315.95</v>
       </c>
       <c r="L62" t="n">
-        <v>163.5</v>
+        <v>332.96</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:03:49</t>
+          <t>09:09:10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="F63" t="n">
-        <v>10.19</v>
+        <v>10.65</v>
       </c>
       <c r="G63" t="n">
-        <v>127.7</v>
+        <v>125.2</v>
       </c>
       <c r="H63" t="n">
-        <v>21.7</v>
+        <v>20.6</v>
       </c>
       <c r="I63" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-32.68</v>
+        <v>-172.31</v>
       </c>
       <c r="K63" t="n">
-        <v>-16.34</v>
+        <v>125.31</v>
       </c>
       <c r="L63" t="n">
-        <v>36.54</v>
+        <v>213.06</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:05:43</t>
+          <t>09:10:42</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.99</v>
+        <v>4.38</v>
       </c>
       <c r="F64" t="n">
-        <v>11.02</v>
+        <v>10.93</v>
       </c>
       <c r="G64" t="n">
-        <v>132.2</v>
+        <v>128.5</v>
       </c>
       <c r="H64" t="n">
-        <v>27.6</v>
+        <v>26.1</v>
       </c>
       <c r="I64" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>24.38</v>
+        <v>234.45</v>
       </c>
       <c r="K64" t="n">
-        <v>83.81</v>
+        <v>-327.31</v>
       </c>
       <c r="L64" t="n">
-        <v>87.28</v>
+        <v>402.61</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:10:27</t>
+          <t>09:14:39</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.68</v>
+        <v>4.37</v>
       </c>
       <c r="F65" t="n">
-        <v>10.05</v>
+        <v>9.6</v>
       </c>
       <c r="G65" t="n">
-        <v>131.3</v>
+        <v>134.8</v>
       </c>
       <c r="H65" t="n">
-        <v>20.7</v>
+        <v>27.9</v>
       </c>
       <c r="I65" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-127.13</v>
+        <v>177.1</v>
       </c>
       <c r="K65" t="n">
-        <v>-202.03</v>
+        <v>-211.01</v>
       </c>
       <c r="L65" t="n">
-        <v>238.7</v>
+        <v>275.48</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:12:24</t>
+          <t>09:16:36</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.84</v>
+        <v>3.95</v>
       </c>
       <c r="F66" t="n">
-        <v>10.34</v>
+        <v>10.72</v>
       </c>
       <c r="G66" t="n">
-        <v>129.7</v>
+        <v>126.3</v>
       </c>
       <c r="H66" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="I66" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-276.23</v>
+        <v>-230.84</v>
       </c>
       <c r="K66" t="n">
-        <v>-160.57</v>
+        <v>42.64</v>
       </c>
       <c r="L66" t="n">
-        <v>319.51</v>
+        <v>234.75</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:13:13</t>
+          <t>09:19:15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.4</v>
+        <v>4.15</v>
       </c>
       <c r="F67" t="n">
-        <v>10.28</v>
+        <v>10.62</v>
       </c>
       <c r="G67" t="n">
-        <v>123.9</v>
+        <v>131.3</v>
       </c>
       <c r="H67" t="n">
-        <v>17.1</v>
+        <v>25.8</v>
       </c>
       <c r="I67" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-14.39</v>
+        <v>54.5</v>
       </c>
       <c r="K67" t="n">
-        <v>186.48</v>
+        <v>-317.26</v>
       </c>
       <c r="L67" t="n">
-        <v>187.04</v>
+        <v>321.91</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:16:04</t>
+          <t>09:23:19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.79</v>
+        <v>3.92</v>
       </c>
       <c r="F68" t="n">
-        <v>10.63</v>
+        <v>9.98</v>
       </c>
       <c r="G68" t="n">
-        <v>134.1</v>
+        <v>114.7</v>
       </c>
       <c r="H68" t="n">
-        <v>23.5</v>
+        <v>24.3</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-0.77</v>
+        <v>309.12</v>
       </c>
       <c r="K68" t="n">
-        <v>-433.88</v>
+        <v>-247.74</v>
       </c>
       <c r="L68" t="n">
-        <v>433.88</v>
+        <v>396.15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:17:55</t>
+          <t>09:25:16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="F69" t="n">
-        <v>10.15</v>
+        <v>10.14</v>
       </c>
       <c r="G69" t="n">
-        <v>128.3</v>
+        <v>116.9</v>
       </c>
       <c r="H69" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="I69" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>23.79</v>
+        <v>519.54</v>
       </c>
       <c r="K69" t="n">
-        <v>-164.23</v>
+        <v>243.33</v>
       </c>
       <c r="L69" t="n">
-        <v>165.95</v>
+        <v>573.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:20:32</t>
+          <t>09:27:15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.58</v>
+        <v>4.63</v>
       </c>
       <c r="F70" t="n">
-        <v>10.3</v>
+        <v>11.37</v>
       </c>
       <c r="G70" t="n">
-        <v>127.8</v>
+        <v>125.2</v>
       </c>
       <c r="H70" t="n">
-        <v>20.2</v>
+        <v>19.5</v>
       </c>
       <c r="I70" t="n">
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>132.49</v>
+        <v>313.72</v>
       </c>
       <c r="K70" t="n">
-        <v>453.66</v>
+        <v>99.23999999999999</v>
       </c>
       <c r="L70" t="n">
-        <v>472.62</v>
+        <v>329.04</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:24:09</t>
+          <t>09:31:14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.65</v>
+        <v>4.39</v>
       </c>
       <c r="F71" t="n">
-        <v>10.55</v>
+        <v>9.32</v>
       </c>
       <c r="G71" t="n">
-        <v>127.6</v>
+        <v>118.1</v>
       </c>
       <c r="H71" t="n">
         <v>23.2</v>
       </c>
       <c r="I71" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-387.38</v>
+        <v>-194.73</v>
       </c>
       <c r="K71" t="n">
-        <v>-252.04</v>
+        <v>-900.3200000000001</v>
       </c>
       <c r="L71" t="n">
-        <v>462.16</v>
+        <v>921.13</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:25:39</t>
+          <t>09:32:42</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>3.88</v>
+        <v>4.42</v>
       </c>
       <c r="F72" t="n">
-        <v>10.09</v>
+        <v>10.03</v>
       </c>
       <c r="G72" t="n">
-        <v>134.8</v>
+        <v>136.6</v>
       </c>
       <c r="H72" t="n">
-        <v>23.7</v>
+        <v>26.4</v>
       </c>
       <c r="I72" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>52.33</v>
+        <v>-83.12</v>
       </c>
       <c r="K72" t="n">
-        <v>-464.77</v>
+        <v>325.99</v>
       </c>
       <c r="L72" t="n">
-        <v>467.7</v>
+        <v>336.42</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:26:46</t>
+          <t>09:33:18</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>4.42</v>
+        <v>3.58</v>
       </c>
       <c r="F73" t="n">
-        <v>10.53</v>
+        <v>10.83</v>
       </c>
       <c r="G73" t="n">
-        <v>110.2</v>
+        <v>133.4</v>
       </c>
       <c r="H73" t="n">
-        <v>28</v>
+        <v>26.9</v>
       </c>
       <c r="I73" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>368.23</v>
+        <v>709.41</v>
       </c>
       <c r="K73" t="n">
-        <v>602.1799999999999</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>705.84</v>
+        <v>714.51</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:39:05</t>
+          <t>09:45:59</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.65</v>
+        <v>4.76</v>
       </c>
       <c r="F74" t="n">
-        <v>10.38</v>
+        <v>10.03</v>
       </c>
       <c r="G74" t="n">
-        <v>115.1</v>
+        <v>142</v>
       </c>
       <c r="H74" t="n">
-        <v>20.5</v>
+        <v>16.3</v>
       </c>
       <c r="I74" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-52.66</v>
+        <v>98.41</v>
       </c>
       <c r="K74" t="n">
-        <v>17.96</v>
+        <v>133.55</v>
       </c>
       <c r="L74" t="n">
-        <v>55.64</v>
+        <v>165.89</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:41:14</t>
+          <t>09:47:54</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.38</v>
+        <v>4.68</v>
       </c>
       <c r="F75" t="n">
-        <v>9.890000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="G75" t="n">
-        <v>124.3</v>
+        <v>133.5</v>
       </c>
       <c r="H75" t="n">
-        <v>18.7</v>
+        <v>26.1</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.29</v>
+        <v>-361.09</v>
       </c>
       <c r="K75" t="n">
-        <v>-16.13</v>
+        <v>148.22</v>
       </c>
       <c r="L75" t="n">
-        <v>16.98</v>
+        <v>390.33</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:42:56</t>
+          <t>09:49:13</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>5.6</v>
+        <v>4.12</v>
       </c>
       <c r="F76" t="n">
-        <v>10.37</v>
+        <v>10.58</v>
       </c>
       <c r="G76" t="n">
-        <v>118.3</v>
+        <v>127.4</v>
       </c>
       <c r="H76" t="n">
-        <v>21</v>
+        <v>25.3</v>
       </c>
       <c r="I76" t="n">
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-77.56</v>
+        <v>102.77</v>
       </c>
       <c r="K76" t="n">
-        <v>-148.59</v>
+        <v>301.69</v>
       </c>
       <c r="L76" t="n">
-        <v>167.62</v>
+        <v>318.71</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:46:45</t>
+          <t>09:54:25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.33</v>
+        <v>3.89</v>
       </c>
       <c r="F77" t="n">
-        <v>10.38</v>
+        <v>10.03</v>
       </c>
       <c r="G77" t="n">
-        <v>123</v>
+        <v>124.7</v>
       </c>
       <c r="H77" t="n">
-        <v>25.5</v>
+        <v>21.4</v>
       </c>
       <c r="I77" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-114.17</v>
+        <v>-230.75</v>
       </c>
       <c r="K77" t="n">
-        <v>-14.87</v>
+        <v>72.81999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>115.14</v>
+        <v>241.97</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:48:13</t>
+          <t>09:56:29</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.31</v>
+        <v>4.56</v>
       </c>
       <c r="F78" t="n">
-        <v>10.71</v>
+        <v>10.42</v>
       </c>
       <c r="G78" t="n">
-        <v>121.9</v>
+        <v>135.3</v>
       </c>
       <c r="H78" t="n">
-        <v>24.6</v>
+        <v>25.2</v>
       </c>
       <c r="I78" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-60.27</v>
+        <v>111.85</v>
       </c>
       <c r="K78" t="n">
-        <v>-135.68</v>
+        <v>119.22</v>
       </c>
       <c r="L78" t="n">
-        <v>148.46</v>
+        <v>163.47</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:49:21</t>
+          <t>09:57:53</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.4</v>
+        <v>4.65</v>
       </c>
       <c r="F79" t="n">
-        <v>10.43</v>
+        <v>10.69</v>
       </c>
       <c r="G79" t="n">
-        <v>134</v>
+        <v>132.2</v>
       </c>
       <c r="H79" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>152.91</v>
+        <v>-145.27</v>
       </c>
       <c r="K79" t="n">
-        <v>-114.43</v>
+        <v>118.12</v>
       </c>
       <c r="L79" t="n">
-        <v>190.99</v>
+        <v>187.23</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>09:53:53</t>
+          <t>10:02:53</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>5.27</v>
+        <v>4.32</v>
       </c>
       <c r="F80" t="n">
-        <v>10.33</v>
+        <v>10.49</v>
       </c>
       <c r="G80" t="n">
-        <v>140</v>
+        <v>135.7</v>
       </c>
       <c r="H80" t="n">
-        <v>21.1</v>
+        <v>30.4</v>
       </c>
       <c r="I80" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>-183.02</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>-174.64</v>
+        <v>-165.7</v>
       </c>
       <c r="L80" t="n">
-        <v>252.98</v>
+        <v>190.5</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>09:56:09</t>
+          <t>10:04:27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.83</v>
+        <v>4.14</v>
       </c>
       <c r="F81" t="n">
-        <v>9.69</v>
+        <v>10.22</v>
       </c>
       <c r="G81" t="n">
-        <v>134.4</v>
+        <v>116.4</v>
       </c>
       <c r="H81" t="n">
-        <v>24.1</v>
+        <v>25.2</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>160.59</v>
+        <v>177.17</v>
       </c>
       <c r="K81" t="n">
-        <v>-70.16</v>
+        <v>-17.17</v>
       </c>
       <c r="L81" t="n">
-        <v>175.25</v>
+        <v>178</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>09:58:19</t>
+          <t>10:06:32</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.36</v>
+        <v>4.45</v>
       </c>
       <c r="F82" t="n">
-        <v>10.3</v>
+        <v>10.6</v>
       </c>
       <c r="G82" t="n">
-        <v>139.1</v>
+        <v>127.2</v>
       </c>
       <c r="H82" t="n">
-        <v>22.8</v>
+        <v>19.7</v>
       </c>
       <c r="I82" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>121.13</v>
+        <v>-221.27</v>
       </c>
       <c r="K82" t="n">
-        <v>-233.99</v>
+        <v>-87.97</v>
       </c>
       <c r="L82" t="n">
-        <v>263.48</v>
+        <v>238.12</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:02:24</t>
+          <t>10:10:43</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.23</v>
+        <v>4.89</v>
       </c>
       <c r="F83" t="n">
-        <v>10.85</v>
+        <v>10.4</v>
       </c>
       <c r="G83" t="n">
-        <v>117.1</v>
+        <v>122</v>
       </c>
       <c r="H83" t="n">
-        <v>18.3</v>
+        <v>19.2</v>
       </c>
       <c r="I83" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>195.64</v>
+        <v>281.94</v>
       </c>
       <c r="K83" t="n">
-        <v>-80.37</v>
+        <v>114.67</v>
       </c>
       <c r="L83" t="n">
-        <v>211.51</v>
+        <v>304.37</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:04:06</t>
+          <t>10:12:25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.24</v>
+        <v>4.27</v>
       </c>
       <c r="F84" t="n">
-        <v>10.28</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="G84" t="n">
-        <v>127.2</v>
+        <v>123.2</v>
       </c>
       <c r="H84" t="n">
-        <v>27.6</v>
+        <v>31.5</v>
       </c>
       <c r="I84" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-40.22</v>
+        <v>-73.44</v>
       </c>
       <c r="K84" t="n">
-        <v>450.48</v>
+        <v>283.35</v>
       </c>
       <c r="L84" t="n">
-        <v>452.27</v>
+        <v>292.71</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:05:26</t>
+          <t>10:13:13</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.81</v>
+        <v>4.2</v>
       </c>
       <c r="F85" t="n">
-        <v>10.79</v>
+        <v>10.1</v>
       </c>
       <c r="G85" t="n">
-        <v>113</v>
+        <v>121.6</v>
       </c>
       <c r="H85" t="n">
-        <v>20.9</v>
+        <v>27.7</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-141.87</v>
+        <v>211.64</v>
       </c>
       <c r="K85" t="n">
-        <v>-52.16</v>
+        <v>-89.59999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>151.15</v>
+        <v>229.82</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:10:34</t>
+          <t>10:19:15</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>3.88</v>
+        <v>4.5</v>
       </c>
       <c r="F86" t="n">
-        <v>10.23</v>
+        <v>10.19</v>
       </c>
       <c r="G86" t="n">
-        <v>127.3</v>
+        <v>125</v>
       </c>
       <c r="H86" t="n">
-        <v>25.3</v>
+        <v>17.6</v>
       </c>
       <c r="I86" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>179.23</v>
+        <v>300.73</v>
       </c>
       <c r="K86" t="n">
-        <v>-289.46</v>
+        <v>-322.97</v>
       </c>
       <c r="L86" t="n">
-        <v>340.46</v>
+        <v>441.31</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:12:16</t>
+          <t>10:20:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.03</v>
+        <v>3.74</v>
       </c>
       <c r="F87" t="n">
-        <v>10.12</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G87" t="n">
-        <v>129.2</v>
+        <v>134.1</v>
       </c>
       <c r="H87" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I87" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>119.45</v>
+        <v>189.23</v>
       </c>
       <c r="K87" t="n">
-        <v>-249.1</v>
+        <v>-598.96</v>
       </c>
       <c r="L87" t="n">
-        <v>276.26</v>
+        <v>628.14</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:15:00</t>
+          <t>10:22:35</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.66</v>
+        <v>4.67</v>
       </c>
       <c r="F88" t="n">
-        <v>10.06</v>
+        <v>9.48</v>
       </c>
       <c r="G88" t="n">
-        <v>118.6</v>
+        <v>121.5</v>
       </c>
       <c r="H88" t="n">
-        <v>22</v>
+        <v>22.7</v>
       </c>
       <c r="I88" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>164.55</v>
+        <v>875.33</v>
       </c>
       <c r="K88" t="n">
-        <v>-191.43</v>
+        <v>667.09</v>
       </c>
       <c r="L88" t="n">
-        <v>252.43</v>
+        <v>1100.55</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-10.xlsx
+++ b/output/2024-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-56.17</v>
+        <v>-67.01000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>93.36</v>
+        <v>111.37</v>
       </c>
       <c r="L14" t="n">
-        <v>108.95</v>
+        <v>129.98</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-103.46</v>
+        <v>-120.49</v>
       </c>
       <c r="K15" t="n">
-        <v>-42.9</v>
+        <v>-49.96</v>
       </c>
       <c r="L15" t="n">
-        <v>112</v>
+        <v>130.44</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>143.36</v>
+        <v>134.73</v>
       </c>
       <c r="K16" t="n">
-        <v>-127.76</v>
+        <v>-120.07</v>
       </c>
       <c r="L16" t="n">
-        <v>192.02</v>
+        <v>180.47</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-78.11</v>
+        <v>-105.38</v>
       </c>
       <c r="K17" t="n">
-        <v>-7.89</v>
+        <v>-10.64</v>
       </c>
       <c r="L17" t="n">
-        <v>78.51000000000001</v>
+        <v>105.92</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-251.9</v>
+        <v>-237.79</v>
       </c>
       <c r="K18" t="n">
-        <v>-63.96</v>
+        <v>-60.38</v>
       </c>
       <c r="L18" t="n">
-        <v>259.89</v>
+        <v>245.34</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>-49.52</v>
+        <v>-71.76000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>43.9</v>
+        <v>63.62</v>
       </c>
       <c r="L19" t="n">
-        <v>66.18000000000001</v>
+        <v>95.90000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-133.94</v>
+        <v>-221.26</v>
       </c>
       <c r="K20" t="n">
-        <v>-27.89</v>
+        <v>-46.07</v>
       </c>
       <c r="L20" t="n">
-        <v>136.81</v>
+        <v>226.01</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>70.56</v>
+        <v>108.4</v>
       </c>
       <c r="K21" t="n">
-        <v>172.76</v>
+        <v>265.42</v>
       </c>
       <c r="L21" t="n">
-        <v>186.61</v>
+        <v>286.7</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>14.21</v>
+        <v>20.9</v>
       </c>
       <c r="K22" t="n">
-        <v>127.7</v>
+        <v>187.73</v>
       </c>
       <c r="L22" t="n">
-        <v>128.49</v>
+        <v>188.89</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-292.37</v>
+        <v>-340.25</v>
       </c>
       <c r="K23" t="n">
-        <v>168.62</v>
+        <v>196.23</v>
       </c>
       <c r="L23" t="n">
-        <v>337.51</v>
+        <v>392.78</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>62</v>
+        <v>72.58</v>
       </c>
       <c r="K24" t="n">
-        <v>533.14</v>
+        <v>624.12</v>
       </c>
       <c r="L24" t="n">
-        <v>536.73</v>
+        <v>628.3200000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-203.3</v>
+        <v>-277.9</v>
       </c>
       <c r="K25" t="n">
-        <v>123.98</v>
+        <v>169.47</v>
       </c>
       <c r="L25" t="n">
-        <v>238.12</v>
+        <v>325.5</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-31.26</v>
+        <v>-41.9</v>
       </c>
       <c r="K26" t="n">
-        <v>-387.35</v>
+        <v>-519.1900000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>388.61</v>
+        <v>520.88</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>348.74</v>
+        <v>558.75</v>
       </c>
       <c r="K27" t="n">
-        <v>-150.4</v>
+        <v>-240.97</v>
       </c>
       <c r="L27" t="n">
-        <v>379.78</v>
+        <v>608.5</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>407.71</v>
+        <v>472.97</v>
       </c>
       <c r="K28" t="n">
-        <v>-180.62</v>
+        <v>-209.53</v>
       </c>
       <c r="L28" t="n">
-        <v>445.93</v>
+        <v>517.3</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-201.65</v>
+        <v>-191.6</v>
       </c>
       <c r="K29" t="n">
-        <v>-108.33</v>
+        <v>-102.92</v>
       </c>
       <c r="L29" t="n">
-        <v>228.91</v>
+        <v>217.49</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-96.42</v>
+        <v>-130.6</v>
       </c>
       <c r="K30" t="n">
-        <v>-51.89</v>
+        <v>-70.29000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>109.5</v>
+        <v>148.31</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>182.14</v>
+        <v>220.04</v>
       </c>
       <c r="K31" t="n">
-        <v>51.37</v>
+        <v>62.06</v>
       </c>
       <c r="L31" t="n">
-        <v>189.25</v>
+        <v>228.63</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>17.87</v>
+        <v>35.07</v>
       </c>
       <c r="K32" t="n">
-        <v>52.35</v>
+        <v>102.75</v>
       </c>
       <c r="L32" t="n">
-        <v>55.32</v>
+        <v>108.57</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>108.11</v>
+        <v>141.32</v>
       </c>
       <c r="K33" t="n">
-        <v>-137.56</v>
+        <v>-179.81</v>
       </c>
       <c r="L33" t="n">
-        <v>174.96</v>
+        <v>228.7</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>72.91</v>
+        <v>84.87</v>
       </c>
       <c r="K34" t="n">
-        <v>115</v>
+        <v>133.88</v>
       </c>
       <c r="L34" t="n">
-        <v>136.16</v>
+        <v>158.51</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-10.33</v>
+        <v>-11.99</v>
       </c>
       <c r="K35" t="n">
-        <v>183.94</v>
+        <v>213.41</v>
       </c>
       <c r="L35" t="n">
-        <v>184.23</v>
+        <v>213.75</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-9.050000000000001</v>
+        <v>-10.43</v>
       </c>
       <c r="K36" t="n">
-        <v>-225.84</v>
+        <v>-260.16</v>
       </c>
       <c r="L36" t="n">
-        <v>226.02</v>
+        <v>260.37</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-167.02</v>
+        <v>-213.36</v>
       </c>
       <c r="K37" t="n">
-        <v>69.19</v>
+        <v>88.39</v>
       </c>
       <c r="L37" t="n">
-        <v>180.78</v>
+        <v>230.95</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>618.04</v>
+        <v>683.1900000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>-14.9</v>
+        <v>-16.48</v>
       </c>
       <c r="L38" t="n">
-        <v>618.22</v>
+        <v>683.39</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>136.33</v>
+        <v>232.38</v>
       </c>
       <c r="K39" t="n">
-        <v>100.03</v>
+        <v>170.51</v>
       </c>
       <c r="L39" t="n">
-        <v>169.09</v>
+        <v>288.23</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>35.07</v>
+        <v>42.14</v>
       </c>
       <c r="K40" t="n">
-        <v>-606.8200000000001</v>
+        <v>-729.01</v>
       </c>
       <c r="L40" t="n">
-        <v>607.83</v>
+        <v>730.23</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-260.21</v>
+        <v>-377.71</v>
       </c>
       <c r="K41" t="n">
-        <v>-148.89</v>
+        <v>-216.12</v>
       </c>
       <c r="L41" t="n">
-        <v>299.8</v>
+        <v>435.17</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>492.29</v>
+        <v>603.63</v>
       </c>
       <c r="K42" t="n">
-        <v>-206.53</v>
+        <v>-253.24</v>
       </c>
       <c r="L42" t="n">
-        <v>533.86</v>
+        <v>654.6</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>564.83</v>
+        <v>666.46</v>
       </c>
       <c r="K43" t="n">
-        <v>604.72</v>
+        <v>713.54</v>
       </c>
       <c r="L43" t="n">
-        <v>827.48</v>
+        <v>976.37</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-125.48</v>
+        <v>-101.54</v>
       </c>
       <c r="K44" t="n">
-        <v>-204.41</v>
+        <v>-165.42</v>
       </c>
       <c r="L44" t="n">
-        <v>239.85</v>
+        <v>194.1</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-10.03</v>
+        <v>-17.54</v>
       </c>
       <c r="K45" t="n">
-        <v>-74.06</v>
+        <v>-129.47</v>
       </c>
       <c r="L45" t="n">
-        <v>74.73999999999999</v>
+        <v>130.66</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>47.18</v>
+        <v>93.98</v>
       </c>
       <c r="K46" t="n">
-        <v>-15.13</v>
+        <v>-30.14</v>
       </c>
       <c r="L46" t="n">
-        <v>49.54</v>
+        <v>98.7</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>109.78</v>
+        <v>112.57</v>
       </c>
       <c r="K47" t="n">
-        <v>197.83</v>
+        <v>202.87</v>
       </c>
       <c r="L47" t="n">
-        <v>226.25</v>
+        <v>232.01</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>98.90000000000001</v>
+        <v>94</v>
       </c>
       <c r="K48" t="n">
-        <v>-461.5</v>
+        <v>-438.64</v>
       </c>
       <c r="L48" t="n">
-        <v>471.97</v>
+        <v>448.6</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-34.25</v>
+        <v>-31.62</v>
       </c>
       <c r="K49" t="n">
-        <v>-215.56</v>
+        <v>-199.01</v>
       </c>
       <c r="L49" t="n">
-        <v>218.26</v>
+        <v>201.51</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>29.5</v>
+        <v>41.65</v>
       </c>
       <c r="K50" t="n">
-        <v>-203.81</v>
+        <v>-287.72</v>
       </c>
       <c r="L50" t="n">
-        <v>205.94</v>
+        <v>290.71</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-167.87</v>
+        <v>-239.67</v>
       </c>
       <c r="K51" t="n">
-        <v>-139.08</v>
+        <v>-198.57</v>
       </c>
       <c r="L51" t="n">
-        <v>218</v>
+        <v>311.24</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-55.04</v>
+        <v>-102.17</v>
       </c>
       <c r="K52" t="n">
-        <v>97.62</v>
+        <v>181.23</v>
       </c>
       <c r="L52" t="n">
-        <v>112.07</v>
+        <v>208.05</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>15.5</v>
+        <v>21.09</v>
       </c>
       <c r="K53" t="n">
-        <v>-303.52</v>
+        <v>-413.09</v>
       </c>
       <c r="L53" t="n">
-        <v>303.91</v>
+        <v>413.63</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>179.2</v>
+        <v>266.98</v>
       </c>
       <c r="K54" t="n">
-        <v>217.02</v>
+        <v>323.32</v>
       </c>
       <c r="L54" t="n">
-        <v>281.45</v>
+        <v>419.3</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-285.28</v>
+        <v>-338.99</v>
       </c>
       <c r="K55" t="n">
-        <v>251.26</v>
+        <v>298.57</v>
       </c>
       <c r="L55" t="n">
-        <v>380.16</v>
+        <v>451.73</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>186.95</v>
+        <v>251.54</v>
       </c>
       <c r="K56" t="n">
-        <v>-299.77</v>
+        <v>-403.34</v>
       </c>
       <c r="L56" t="n">
-        <v>353.29</v>
+        <v>475.35</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-709.73</v>
+        <v>-847.91</v>
       </c>
       <c r="K57" t="n">
-        <v>-501.23</v>
+        <v>-598.8200000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>868.88</v>
+        <v>1038.05</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-213.88</v>
+        <v>-410.92</v>
       </c>
       <c r="K58" t="n">
-        <v>152.82</v>
+        <v>293.62</v>
       </c>
       <c r="L58" t="n">
-        <v>262.87</v>
+        <v>505.04</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>193.53</v>
+        <v>222.47</v>
       </c>
       <c r="K59" t="n">
-        <v>79.78</v>
+        <v>91.70999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>209.33</v>
+        <v>240.63</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-31.54</v>
+        <v>-32.94</v>
       </c>
       <c r="K60" t="n">
-        <v>231.92</v>
+        <v>242.19</v>
       </c>
       <c r="L60" t="n">
-        <v>234.05</v>
+        <v>244.42</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>225.49</v>
+        <v>235.95</v>
       </c>
       <c r="K61" t="n">
-        <v>2.34</v>
+        <v>2.45</v>
       </c>
       <c r="L61" t="n">
-        <v>225.5</v>
+        <v>235.96</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>105.06</v>
+        <v>91.89</v>
       </c>
       <c r="K62" t="n">
-        <v>-315.95</v>
+        <v>-276.35</v>
       </c>
       <c r="L62" t="n">
-        <v>332.96</v>
+        <v>291.23</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-172.31</v>
+        <v>-162</v>
       </c>
       <c r="K63" t="n">
-        <v>125.31</v>
+        <v>117.81</v>
       </c>
       <c r="L63" t="n">
-        <v>213.06</v>
+        <v>200.31</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>234.45</v>
+        <v>224.89</v>
       </c>
       <c r="K64" t="n">
-        <v>-327.31</v>
+        <v>-313.96</v>
       </c>
       <c r="L64" t="n">
-        <v>402.61</v>
+        <v>386.2</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>177.1</v>
+        <v>231.08</v>
       </c>
       <c r="K65" t="n">
-        <v>-211.01</v>
+        <v>-275.33</v>
       </c>
       <c r="L65" t="n">
-        <v>275.48</v>
+        <v>359.46</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-230.84</v>
+        <v>-280.9</v>
       </c>
       <c r="K66" t="n">
-        <v>42.64</v>
+        <v>51.89</v>
       </c>
       <c r="L66" t="n">
-        <v>234.75</v>
+        <v>285.65</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>54.5</v>
+        <v>56</v>
       </c>
       <c r="K67" t="n">
-        <v>-317.26</v>
+        <v>-326.03</v>
       </c>
       <c r="L67" t="n">
-        <v>321.91</v>
+        <v>330.8</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>309.12</v>
+        <v>340.53</v>
       </c>
       <c r="K68" t="n">
-        <v>-247.74</v>
+        <v>-272.92</v>
       </c>
       <c r="L68" t="n">
-        <v>396.15</v>
+        <v>436.4</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>519.54</v>
+        <v>584.5</v>
       </c>
       <c r="K69" t="n">
-        <v>243.33</v>
+        <v>273.76</v>
       </c>
       <c r="L69" t="n">
-        <v>573.7</v>
+        <v>645.4299999999999</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>313.72</v>
+        <v>428.18</v>
       </c>
       <c r="K70" t="n">
-        <v>99.23999999999999</v>
+        <v>135.45</v>
       </c>
       <c r="L70" t="n">
-        <v>329.04</v>
+        <v>449.09</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-194.73</v>
+        <v>-243.06</v>
       </c>
       <c r="K71" t="n">
-        <v>-900.3200000000001</v>
+        <v>-1123.76</v>
       </c>
       <c r="L71" t="n">
-        <v>921.13</v>
+        <v>1149.75</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-83.12</v>
+        <v>-135.96</v>
       </c>
       <c r="K72" t="n">
-        <v>325.99</v>
+        <v>533.22</v>
       </c>
       <c r="L72" t="n">
-        <v>336.42</v>
+        <v>550.28</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>709.41</v>
+        <v>870.5700000000001</v>
       </c>
       <c r="K73" t="n">
-        <v>85.26000000000001</v>
+        <v>104.63</v>
       </c>
       <c r="L73" t="n">
-        <v>714.51</v>
+        <v>876.84</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>98.41</v>
+        <v>125.53</v>
       </c>
       <c r="K74" t="n">
-        <v>133.55</v>
+        <v>170.36</v>
       </c>
       <c r="L74" t="n">
-        <v>165.89</v>
+        <v>211.61</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-361.09</v>
+        <v>-314.16</v>
       </c>
       <c r="K75" t="n">
-        <v>148.22</v>
+        <v>128.96</v>
       </c>
       <c r="L75" t="n">
-        <v>390.33</v>
+        <v>339.6</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>102.77</v>
+        <v>93.72</v>
       </c>
       <c r="K76" t="n">
-        <v>301.69</v>
+        <v>275.13</v>
       </c>
       <c r="L76" t="n">
-        <v>318.71</v>
+        <v>290.66</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-230.75</v>
+        <v>-259.71</v>
       </c>
       <c r="K77" t="n">
-        <v>72.81999999999999</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="L77" t="n">
-        <v>241.97</v>
+        <v>272.34</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>111.85</v>
+        <v>159.07</v>
       </c>
       <c r="K78" t="n">
-        <v>119.22</v>
+        <v>169.54</v>
       </c>
       <c r="L78" t="n">
-        <v>163.47</v>
+        <v>232.48</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-145.27</v>
+        <v>-196.9</v>
       </c>
       <c r="K79" t="n">
-        <v>118.12</v>
+        <v>160.11</v>
       </c>
       <c r="L79" t="n">
-        <v>187.23</v>
+        <v>253.78</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>93.98999999999999</v>
+        <v>153.11</v>
       </c>
       <c r="K80" t="n">
-        <v>-165.7</v>
+        <v>-269.91</v>
       </c>
       <c r="L80" t="n">
-        <v>190.5</v>
+        <v>310.31</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>177.17</v>
+        <v>228.79</v>
       </c>
       <c r="K81" t="n">
-        <v>-17.17</v>
+        <v>-22.18</v>
       </c>
       <c r="L81" t="n">
-        <v>178</v>
+        <v>229.86</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-221.27</v>
+        <v>-331.04</v>
       </c>
       <c r="K82" t="n">
-        <v>-87.97</v>
+        <v>-131.62</v>
       </c>
       <c r="L82" t="n">
-        <v>238.12</v>
+        <v>356.25</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>281.94</v>
+        <v>428.12</v>
       </c>
       <c r="K83" t="n">
-        <v>114.67</v>
+        <v>174.13</v>
       </c>
       <c r="L83" t="n">
-        <v>304.37</v>
+        <v>462.17</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-73.44</v>
+        <v>-99.98</v>
       </c>
       <c r="K84" t="n">
-        <v>283.35</v>
+        <v>385.74</v>
       </c>
       <c r="L84" t="n">
-        <v>292.71</v>
+        <v>398.49</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>211.64</v>
+        <v>317.69</v>
       </c>
       <c r="K85" t="n">
-        <v>-89.59999999999999</v>
+        <v>-134.5</v>
       </c>
       <c r="L85" t="n">
-        <v>229.82</v>
+        <v>344.99</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>300.73</v>
+        <v>489.09</v>
       </c>
       <c r="K86" t="n">
-        <v>-322.97</v>
+        <v>-525.25</v>
       </c>
       <c r="L86" t="n">
-        <v>441.31</v>
+        <v>717.7</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>189.23</v>
+        <v>223.64</v>
       </c>
       <c r="K87" t="n">
-        <v>-598.96</v>
+        <v>-707.85</v>
       </c>
       <c r="L87" t="n">
-        <v>628.14</v>
+        <v>742.34</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>875.33</v>
+        <v>888.49</v>
       </c>
       <c r="K88" t="n">
-        <v>667.09</v>
+        <v>677.12</v>
       </c>
       <c r="L88" t="n">
-        <v>1100.55</v>
+        <v>1117.1</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-10.xlsx
+++ b/output/2024-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-67.01000000000001</v>
+        <v>-54.36</v>
       </c>
       <c r="K14" t="n">
-        <v>111.37</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>129.98</v>
+        <v>105.44</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-120.49</v>
+        <v>-98.06999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-49.96</v>
+        <v>-40.66</v>
       </c>
       <c r="L15" t="n">
-        <v>130.44</v>
+        <v>106.17</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>134.73</v>
+        <v>102.72</v>
       </c>
       <c r="K16" t="n">
-        <v>-120.07</v>
+        <v>-91.54000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>180.47</v>
+        <v>137.59</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-105.38</v>
+        <v>-89.66</v>
       </c>
       <c r="K17" t="n">
-        <v>-10.64</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>105.92</v>
+        <v>90.11</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-237.79</v>
+        <v>-183.71</v>
       </c>
       <c r="K18" t="n">
-        <v>-60.38</v>
+        <v>-46.64</v>
       </c>
       <c r="L18" t="n">
-        <v>245.34</v>
+        <v>189.54</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>-71.76000000000001</v>
+        <v>-63.45</v>
       </c>
       <c r="K19" t="n">
-        <v>63.62</v>
+        <v>56.26</v>
       </c>
       <c r="L19" t="n">
-        <v>95.90000000000001</v>
+        <v>84.8</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-221.26</v>
+        <v>-138.75</v>
       </c>
       <c r="K20" t="n">
-        <v>-46.07</v>
+        <v>-28.89</v>
       </c>
       <c r="L20" t="n">
-        <v>226.01</v>
+        <v>141.73</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>108.4</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>265.42</v>
+        <v>166.96</v>
       </c>
       <c r="L21" t="n">
-        <v>286.7</v>
+        <v>180.34</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>20.9</v>
+        <v>13.38</v>
       </c>
       <c r="K22" t="n">
-        <v>187.73</v>
+        <v>120.23</v>
       </c>
       <c r="L22" t="n">
-        <v>188.89</v>
+        <v>120.97</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-340.25</v>
+        <v>-218.45</v>
       </c>
       <c r="K23" t="n">
-        <v>196.23</v>
+        <v>125.98</v>
       </c>
       <c r="L23" t="n">
-        <v>392.78</v>
+        <v>252.18</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>72.58</v>
+        <v>41.97</v>
       </c>
       <c r="K24" t="n">
-        <v>624.12</v>
+        <v>360.91</v>
       </c>
       <c r="L24" t="n">
-        <v>628.3200000000001</v>
+        <v>363.34</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-277.9</v>
+        <v>-167.51</v>
       </c>
       <c r="K25" t="n">
-        <v>169.47</v>
+        <v>102.15</v>
       </c>
       <c r="L25" t="n">
-        <v>325.5</v>
+        <v>196.2</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-41.9</v>
+        <v>-23.04</v>
       </c>
       <c r="K26" t="n">
-        <v>-519.1900000000001</v>
+        <v>-285.47</v>
       </c>
       <c r="L26" t="n">
-        <v>520.88</v>
+        <v>286.4</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>558.75</v>
+        <v>279.03</v>
       </c>
       <c r="K27" t="n">
-        <v>-240.97</v>
+        <v>-120.34</v>
       </c>
       <c r="L27" t="n">
-        <v>608.5</v>
+        <v>303.87</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>472.97</v>
+        <v>292.07</v>
       </c>
       <c r="K28" t="n">
-        <v>-209.53</v>
+        <v>-129.39</v>
       </c>
       <c r="L28" t="n">
-        <v>517.3</v>
+        <v>319.44</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-191.6</v>
+        <v>-149.16</v>
       </c>
       <c r="K29" t="n">
-        <v>-102.92</v>
+        <v>-80.13</v>
       </c>
       <c r="L29" t="n">
-        <v>217.49</v>
+        <v>169.32</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-130.6</v>
+        <v>-99.45</v>
       </c>
       <c r="K30" t="n">
-        <v>-70.29000000000001</v>
+        <v>-53.53</v>
       </c>
       <c r="L30" t="n">
-        <v>148.31</v>
+        <v>112.94</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>220.04</v>
+        <v>158.67</v>
       </c>
       <c r="K31" t="n">
-        <v>62.06</v>
+        <v>44.75</v>
       </c>
       <c r="L31" t="n">
-        <v>228.63</v>
+        <v>164.86</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>35.07</v>
+        <v>26.2</v>
       </c>
       <c r="K32" t="n">
-        <v>102.75</v>
+        <v>76.77</v>
       </c>
       <c r="L32" t="n">
-        <v>108.57</v>
+        <v>81.12</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>141.32</v>
+        <v>95.81</v>
       </c>
       <c r="K33" t="n">
-        <v>-179.81</v>
+        <v>-121.9</v>
       </c>
       <c r="L33" t="n">
-        <v>228.7</v>
+        <v>155.05</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>84.87</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>133.88</v>
+        <v>113.67</v>
       </c>
       <c r="L34" t="n">
-        <v>158.51</v>
+        <v>134.59</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-11.99</v>
+        <v>-8.84</v>
       </c>
       <c r="K35" t="n">
-        <v>213.41</v>
+        <v>157.32</v>
       </c>
       <c r="L35" t="n">
-        <v>213.75</v>
+        <v>157.56</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-10.43</v>
+        <v>-7.3</v>
       </c>
       <c r="K36" t="n">
-        <v>-260.16</v>
+        <v>-182.09</v>
       </c>
       <c r="L36" t="n">
-        <v>260.37</v>
+        <v>182.24</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-213.36</v>
+        <v>-138.04</v>
       </c>
       <c r="K37" t="n">
-        <v>88.39</v>
+        <v>57.19</v>
       </c>
       <c r="L37" t="n">
-        <v>230.95</v>
+        <v>149.42</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>683.1900000000001</v>
+        <v>386.72</v>
       </c>
       <c r="K38" t="n">
-        <v>-16.48</v>
+        <v>-9.33</v>
       </c>
       <c r="L38" t="n">
-        <v>683.39</v>
+        <v>386.83</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>232.38</v>
+        <v>146.21</v>
       </c>
       <c r="K39" t="n">
-        <v>170.51</v>
+        <v>107.28</v>
       </c>
       <c r="L39" t="n">
-        <v>288.23</v>
+        <v>181.35</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>42.14</v>
+        <v>22.71</v>
       </c>
       <c r="K40" t="n">
-        <v>-729.01</v>
+        <v>-392.87</v>
       </c>
       <c r="L40" t="n">
-        <v>730.23</v>
+        <v>393.53</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-377.71</v>
+        <v>-228.9</v>
       </c>
       <c r="K41" t="n">
-        <v>-216.12</v>
+        <v>-130.97</v>
       </c>
       <c r="L41" t="n">
-        <v>435.17</v>
+        <v>263.72</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>603.63</v>
+        <v>328.41</v>
       </c>
       <c r="K42" t="n">
-        <v>-253.24</v>
+        <v>-137.78</v>
       </c>
       <c r="L42" t="n">
-        <v>654.6</v>
+        <v>356.14</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>666.46</v>
+        <v>343.51</v>
       </c>
       <c r="K43" t="n">
-        <v>713.54</v>
+        <v>367.78</v>
       </c>
       <c r="L43" t="n">
-        <v>976.37</v>
+        <v>503.25</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-101.54</v>
+        <v>-93</v>
       </c>
       <c r="K44" t="n">
-        <v>-165.42</v>
+        <v>-151.5</v>
       </c>
       <c r="L44" t="n">
-        <v>194.1</v>
+        <v>177.77</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-17.54</v>
+        <v>-12.89</v>
       </c>
       <c r="K45" t="n">
-        <v>-129.47</v>
+        <v>-95.18000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>130.66</v>
+        <v>96.05</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>93.98</v>
+        <v>74.8</v>
       </c>
       <c r="K46" t="n">
-        <v>-30.14</v>
+        <v>-23.99</v>
       </c>
       <c r="L46" t="n">
-        <v>98.7</v>
+        <v>78.55</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>112.57</v>
+        <v>90.94</v>
       </c>
       <c r="K47" t="n">
-        <v>202.87</v>
+        <v>163.87</v>
       </c>
       <c r="L47" t="n">
-        <v>232.01</v>
+        <v>187.41</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>94</v>
+        <v>69.37</v>
       </c>
       <c r="K48" t="n">
-        <v>-438.64</v>
+        <v>-323.7</v>
       </c>
       <c r="L48" t="n">
-        <v>448.6</v>
+        <v>331.05</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-31.62</v>
+        <v>-26.46</v>
       </c>
       <c r="K49" t="n">
-        <v>-199.01</v>
+        <v>-166.49</v>
       </c>
       <c r="L49" t="n">
-        <v>201.51</v>
+        <v>168.58</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>41.65</v>
+        <v>26.42</v>
       </c>
       <c r="K50" t="n">
-        <v>-287.72</v>
+        <v>-182.5</v>
       </c>
       <c r="L50" t="n">
-        <v>290.71</v>
+        <v>184.4</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-239.67</v>
+        <v>-146.89</v>
       </c>
       <c r="K51" t="n">
-        <v>-198.57</v>
+        <v>-121.7</v>
       </c>
       <c r="L51" t="n">
-        <v>311.24</v>
+        <v>190.76</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-102.17</v>
+        <v>-69.23999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>181.23</v>
+        <v>122.82</v>
       </c>
       <c r="L52" t="n">
-        <v>208.05</v>
+        <v>140.99</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>21.09</v>
+        <v>12.36</v>
       </c>
       <c r="K53" t="n">
-        <v>-413.09</v>
+        <v>-241.99</v>
       </c>
       <c r="L53" t="n">
-        <v>413.63</v>
+        <v>242.31</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>266.98</v>
+        <v>150.02</v>
       </c>
       <c r="K54" t="n">
-        <v>323.32</v>
+        <v>181.69</v>
       </c>
       <c r="L54" t="n">
-        <v>419.3</v>
+        <v>235.62</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-338.99</v>
+        <v>-213.56</v>
       </c>
       <c r="K55" t="n">
-        <v>298.57</v>
+        <v>188.09</v>
       </c>
       <c r="L55" t="n">
-        <v>451.73</v>
+        <v>284.58</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>251.54</v>
+        <v>152.78</v>
       </c>
       <c r="K56" t="n">
-        <v>-403.34</v>
+        <v>-244.99</v>
       </c>
       <c r="L56" t="n">
-        <v>475.35</v>
+        <v>288.72</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-847.91</v>
+        <v>-433.84</v>
       </c>
       <c r="K57" t="n">
-        <v>-598.8200000000001</v>
+        <v>-306.39</v>
       </c>
       <c r="L57" t="n">
-        <v>1038.05</v>
+        <v>531.13</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-410.92</v>
+        <v>-200.12</v>
       </c>
       <c r="K58" t="n">
-        <v>293.62</v>
+        <v>143</v>
       </c>
       <c r="L58" t="n">
-        <v>505.04</v>
+        <v>245.96</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>222.47</v>
+        <v>157.42</v>
       </c>
       <c r="K59" t="n">
-        <v>91.70999999999999</v>
+        <v>64.89</v>
       </c>
       <c r="L59" t="n">
-        <v>240.63</v>
+        <v>170.27</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-32.94</v>
+        <v>-26.27</v>
       </c>
       <c r="K60" t="n">
-        <v>242.19</v>
+        <v>193.18</v>
       </c>
       <c r="L60" t="n">
-        <v>244.42</v>
+        <v>194.96</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>235.95</v>
+        <v>170.41</v>
       </c>
       <c r="K61" t="n">
-        <v>2.45</v>
+        <v>1.77</v>
       </c>
       <c r="L61" t="n">
-        <v>235.96</v>
+        <v>170.42</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>91.89</v>
+        <v>75.33</v>
       </c>
       <c r="K62" t="n">
-        <v>-276.35</v>
+        <v>-226.53</v>
       </c>
       <c r="L62" t="n">
-        <v>291.23</v>
+        <v>238.73</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-162</v>
+        <v>-139.41</v>
       </c>
       <c r="K63" t="n">
-        <v>117.81</v>
+        <v>101.39</v>
       </c>
       <c r="L63" t="n">
-        <v>200.31</v>
+        <v>172.38</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>224.89</v>
+        <v>166.5</v>
       </c>
       <c r="K64" t="n">
-        <v>-313.96</v>
+        <v>-232.45</v>
       </c>
       <c r="L64" t="n">
-        <v>386.2</v>
+        <v>285.94</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>231.08</v>
+        <v>144.89</v>
       </c>
       <c r="K65" t="n">
-        <v>-275.33</v>
+        <v>-172.64</v>
       </c>
       <c r="L65" t="n">
-        <v>359.46</v>
+        <v>225.38</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-280.9</v>
+        <v>-192.9</v>
       </c>
       <c r="K66" t="n">
-        <v>51.89</v>
+        <v>35.63</v>
       </c>
       <c r="L66" t="n">
-        <v>285.65</v>
+        <v>196.16</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>56</v>
+        <v>41.59</v>
       </c>
       <c r="K67" t="n">
-        <v>-326.03</v>
+        <v>-242.14</v>
       </c>
       <c r="L67" t="n">
-        <v>330.8</v>
+        <v>245.68</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>340.53</v>
+        <v>225.55</v>
       </c>
       <c r="K68" t="n">
-        <v>-272.92</v>
+        <v>-180.76</v>
       </c>
       <c r="L68" t="n">
-        <v>436.4</v>
+        <v>289.05</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>584.5</v>
+        <v>349.57</v>
       </c>
       <c r="K69" t="n">
-        <v>273.76</v>
+        <v>163.73</v>
       </c>
       <c r="L69" t="n">
-        <v>645.4299999999999</v>
+        <v>386.01</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>428.18</v>
+        <v>264.74</v>
       </c>
       <c r="K70" t="n">
-        <v>135.45</v>
+        <v>83.75</v>
       </c>
       <c r="L70" t="n">
-        <v>449.09</v>
+        <v>277.67</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-243.06</v>
+        <v>-116.45</v>
       </c>
       <c r="K71" t="n">
-        <v>-1123.76</v>
+        <v>-538.39</v>
       </c>
       <c r="L71" t="n">
-        <v>1149.75</v>
+        <v>550.84</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-135.96</v>
+        <v>-72.06999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>533.22</v>
+        <v>282.63</v>
       </c>
       <c r="L72" t="n">
-        <v>550.28</v>
+        <v>291.67</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>870.5700000000001</v>
+        <v>428.75</v>
       </c>
       <c r="K73" t="n">
-        <v>104.63</v>
+        <v>51.53</v>
       </c>
       <c r="L73" t="n">
-        <v>876.84</v>
+        <v>431.83</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>125.53</v>
+        <v>92.87</v>
       </c>
       <c r="K74" t="n">
-        <v>170.36</v>
+        <v>126.04</v>
       </c>
       <c r="L74" t="n">
-        <v>211.61</v>
+        <v>156.56</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-314.16</v>
+        <v>-261.89</v>
       </c>
       <c r="K75" t="n">
-        <v>128.96</v>
+        <v>107.5</v>
       </c>
       <c r="L75" t="n">
-        <v>339.6</v>
+        <v>283.1</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>93.72</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>275.13</v>
+        <v>216.53</v>
       </c>
       <c r="L76" t="n">
-        <v>290.66</v>
+        <v>228.75</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-259.71</v>
+        <v>-177.71</v>
       </c>
       <c r="K77" t="n">
-        <v>81.95999999999999</v>
+        <v>56.09</v>
       </c>
       <c r="L77" t="n">
-        <v>272.34</v>
+        <v>186.35</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>159.07</v>
+        <v>109.45</v>
       </c>
       <c r="K78" t="n">
-        <v>169.54</v>
+        <v>116.65</v>
       </c>
       <c r="L78" t="n">
-        <v>232.48</v>
+        <v>159.96</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-196.9</v>
+        <v>-135.47</v>
       </c>
       <c r="K79" t="n">
-        <v>160.11</v>
+        <v>110.15</v>
       </c>
       <c r="L79" t="n">
-        <v>253.78</v>
+        <v>174.6</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>153.11</v>
+        <v>90.05</v>
       </c>
       <c r="K80" t="n">
-        <v>-269.91</v>
+        <v>-158.75</v>
       </c>
       <c r="L80" t="n">
-        <v>310.31</v>
+        <v>182.51</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>228.79</v>
+        <v>169.98</v>
       </c>
       <c r="K81" t="n">
-        <v>-22.18</v>
+        <v>-16.48</v>
       </c>
       <c r="L81" t="n">
-        <v>229.86</v>
+        <v>170.78</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-331.04</v>
+        <v>-193.83</v>
       </c>
       <c r="K82" t="n">
-        <v>-131.62</v>
+        <v>-77.06</v>
       </c>
       <c r="L82" t="n">
-        <v>356.25</v>
+        <v>208.59</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>428.12</v>
+        <v>252.48</v>
       </c>
       <c r="K83" t="n">
-        <v>174.13</v>
+        <v>102.69</v>
       </c>
       <c r="L83" t="n">
-        <v>462.17</v>
+        <v>272.56</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-99.98</v>
+        <v>-62.41</v>
       </c>
       <c r="K84" t="n">
-        <v>385.74</v>
+        <v>240.77</v>
       </c>
       <c r="L84" t="n">
-        <v>398.49</v>
+        <v>248.72</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>317.69</v>
+        <v>198.83</v>
       </c>
       <c r="K85" t="n">
-        <v>-134.5</v>
+        <v>-84.18000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>344.99</v>
+        <v>215.92</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>489.09</v>
+        <v>233.07</v>
       </c>
       <c r="K86" t="n">
-        <v>-525.25</v>
+        <v>-250.31</v>
       </c>
       <c r="L86" t="n">
-        <v>717.7</v>
+        <v>342.02</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>223.64</v>
+        <v>121.21</v>
       </c>
       <c r="K87" t="n">
-        <v>-707.85</v>
+        <v>-383.66</v>
       </c>
       <c r="L87" t="n">
-        <v>742.34</v>
+        <v>402.35</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>888.49</v>
+        <v>524.21</v>
       </c>
       <c r="K88" t="n">
-        <v>677.12</v>
+        <v>399.5</v>
       </c>
       <c r="L88" t="n">
-        <v>1117.1</v>
+        <v>659.09</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-10.xlsx
+++ b/output/2024-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-54.36</v>
+        <v>-51.42</v>
       </c>
       <c r="K14" t="n">
-        <v>90.34999999999999</v>
+        <v>85.45999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>105.44</v>
+        <v>99.73999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-98.06999999999999</v>
+        <v>-93.67</v>
       </c>
       <c r="K15" t="n">
-        <v>-40.66</v>
+        <v>-38.84</v>
       </c>
       <c r="L15" t="n">
-        <v>106.17</v>
+        <v>101.4</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>102.72</v>
+        <v>97.61</v>
       </c>
       <c r="K16" t="n">
-        <v>-91.54000000000001</v>
+        <v>-86.98</v>
       </c>
       <c r="L16" t="n">
-        <v>137.59</v>
+        <v>130.74</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-89.66</v>
+        <v>-88.39</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.050000000000001</v>
+        <v>-8.93</v>
       </c>
       <c r="L17" t="n">
-        <v>90.11</v>
+        <v>88.84</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-183.71</v>
+        <v>-179.7</v>
       </c>
       <c r="K18" t="n">
-        <v>-46.64</v>
+        <v>-45.62</v>
       </c>
       <c r="L18" t="n">
-        <v>189.54</v>
+        <v>185.4</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>-63.45</v>
+        <v>-61.52</v>
       </c>
       <c r="K19" t="n">
-        <v>56.26</v>
+        <v>54.55</v>
       </c>
       <c r="L19" t="n">
-        <v>84.8</v>
+        <v>82.23</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-138.75</v>
+        <v>-142.18</v>
       </c>
       <c r="K20" t="n">
-        <v>-28.89</v>
+        <v>-29.61</v>
       </c>
       <c r="L20" t="n">
-        <v>141.73</v>
+        <v>145.22</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>68.18000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>166.96</v>
+        <v>171.64</v>
       </c>
       <c r="L21" t="n">
-        <v>180.34</v>
+        <v>185.4</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>13.38</v>
+        <v>13.85</v>
       </c>
       <c r="K22" t="n">
-        <v>120.23</v>
+        <v>124.39</v>
       </c>
       <c r="L22" t="n">
-        <v>120.97</v>
+        <v>125.16</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-218.45</v>
+        <v>-224.41</v>
       </c>
       <c r="K23" t="n">
-        <v>125.98</v>
+        <v>129.42</v>
       </c>
       <c r="L23" t="n">
-        <v>252.18</v>
+        <v>259.05</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>41.97</v>
+        <v>44</v>
       </c>
       <c r="K24" t="n">
-        <v>360.91</v>
+        <v>378.36</v>
       </c>
       <c r="L24" t="n">
-        <v>363.34</v>
+        <v>380.91</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-167.51</v>
+        <v>-172.84</v>
       </c>
       <c r="K25" t="n">
-        <v>102.15</v>
+        <v>105.4</v>
       </c>
       <c r="L25" t="n">
-        <v>196.2</v>
+        <v>202.45</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-23.04</v>
+        <v>-24.22</v>
       </c>
       <c r="K26" t="n">
-        <v>-285.47</v>
+        <v>-300.04</v>
       </c>
       <c r="L26" t="n">
-        <v>286.4</v>
+        <v>301.02</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>279.03</v>
+        <v>302.34</v>
       </c>
       <c r="K27" t="n">
-        <v>-120.34</v>
+        <v>-130.39</v>
       </c>
       <c r="L27" t="n">
-        <v>303.87</v>
+        <v>329.25</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>292.07</v>
+        <v>300.81</v>
       </c>
       <c r="K28" t="n">
-        <v>-129.39</v>
+        <v>-133.26</v>
       </c>
       <c r="L28" t="n">
-        <v>319.44</v>
+        <v>329</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-149.16</v>
+        <v>-144.6</v>
       </c>
       <c r="K29" t="n">
-        <v>-80.13</v>
+        <v>-77.68000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>169.32</v>
+        <v>164.15</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-99.45</v>
+        <v>-95.62</v>
       </c>
       <c r="K30" t="n">
-        <v>-53.53</v>
+        <v>-51.46</v>
       </c>
       <c r="L30" t="n">
-        <v>112.94</v>
+        <v>108.59</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>158.67</v>
+        <v>153.82</v>
       </c>
       <c r="K31" t="n">
-        <v>44.75</v>
+        <v>43.38</v>
       </c>
       <c r="L31" t="n">
-        <v>164.86</v>
+        <v>159.82</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>26.2</v>
+        <v>26.01</v>
       </c>
       <c r="K32" t="n">
-        <v>76.77</v>
+        <v>76.2</v>
       </c>
       <c r="L32" t="n">
-        <v>81.12</v>
+        <v>80.51000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>95.81</v>
+        <v>95.19</v>
       </c>
       <c r="K33" t="n">
-        <v>-121.9</v>
+        <v>-121.12</v>
       </c>
       <c r="L33" t="n">
-        <v>155.05</v>
+        <v>154.05</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>72.06999999999999</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>113.67</v>
+        <v>110</v>
       </c>
       <c r="L34" t="n">
-        <v>134.59</v>
+        <v>130.24</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.84</v>
+        <v>-8.93</v>
       </c>
       <c r="K35" t="n">
-        <v>157.32</v>
+        <v>158.98</v>
       </c>
       <c r="L35" t="n">
-        <v>157.56</v>
+        <v>159.23</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.3</v>
+        <v>-7.36</v>
       </c>
       <c r="K36" t="n">
-        <v>-182.09</v>
+        <v>-183.59</v>
       </c>
       <c r="L36" t="n">
-        <v>182.24</v>
+        <v>183.74</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-138.04</v>
+        <v>-142.04</v>
       </c>
       <c r="K37" t="n">
-        <v>57.19</v>
+        <v>58.84</v>
       </c>
       <c r="L37" t="n">
-        <v>149.42</v>
+        <v>153.75</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>386.72</v>
+        <v>405.61</v>
       </c>
       <c r="K38" t="n">
-        <v>-9.33</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>386.83</v>
+        <v>405.73</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>146.21</v>
+        <v>151.69</v>
       </c>
       <c r="K39" t="n">
-        <v>107.28</v>
+        <v>111.3</v>
       </c>
       <c r="L39" t="n">
-        <v>181.35</v>
+        <v>188.14</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>22.71</v>
+        <v>23.93</v>
       </c>
       <c r="K40" t="n">
-        <v>-392.87</v>
+        <v>-413.95</v>
       </c>
       <c r="L40" t="n">
-        <v>393.53</v>
+        <v>414.64</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-228.9</v>
+        <v>-240.44</v>
       </c>
       <c r="K41" t="n">
-        <v>-130.97</v>
+        <v>-137.58</v>
       </c>
       <c r="L41" t="n">
-        <v>263.72</v>
+        <v>277.02</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>328.41</v>
+        <v>347.78</v>
       </c>
       <c r="K42" t="n">
-        <v>-137.78</v>
+        <v>-145.9</v>
       </c>
       <c r="L42" t="n">
-        <v>356.14</v>
+        <v>377.15</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>343.51</v>
+        <v>370.72</v>
       </c>
       <c r="K43" t="n">
-        <v>367.78</v>
+        <v>396.9</v>
       </c>
       <c r="L43" t="n">
-        <v>503.25</v>
+        <v>543.11</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-93</v>
+        <v>-86.45</v>
       </c>
       <c r="K44" t="n">
-        <v>-151.5</v>
+        <v>-140.83</v>
       </c>
       <c r="L44" t="n">
-        <v>177.77</v>
+        <v>165.24</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-12.89</v>
+        <v>-12.53</v>
       </c>
       <c r="K45" t="n">
-        <v>-95.18000000000001</v>
+        <v>-92.48999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>96.05</v>
+        <v>93.33</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>74.8</v>
+        <v>72.61</v>
       </c>
       <c r="K46" t="n">
-        <v>-23.99</v>
+        <v>-23.29</v>
       </c>
       <c r="L46" t="n">
-        <v>78.55</v>
+        <v>76.25</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>90.94</v>
+        <v>87.76000000000001</v>
       </c>
       <c r="K47" t="n">
-        <v>163.87</v>
+        <v>158.14</v>
       </c>
       <c r="L47" t="n">
-        <v>187.41</v>
+        <v>180.86</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>69.37</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>-323.7</v>
+        <v>-312.62</v>
       </c>
       <c r="L48" t="n">
-        <v>331.05</v>
+        <v>319.72</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-26.46</v>
+        <v>-25.68</v>
       </c>
       <c r="K49" t="n">
-        <v>-166.49</v>
+        <v>-161.63</v>
       </c>
       <c r="L49" t="n">
-        <v>168.58</v>
+        <v>163.66</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>26.42</v>
+        <v>27.19</v>
       </c>
       <c r="K50" t="n">
-        <v>-182.5</v>
+        <v>-187.86</v>
       </c>
       <c r="L50" t="n">
-        <v>184.4</v>
+        <v>189.81</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-146.89</v>
+        <v>-151.43</v>
       </c>
       <c r="K51" t="n">
-        <v>-121.7</v>
+        <v>-125.46</v>
       </c>
       <c r="L51" t="n">
-        <v>190.76</v>
+        <v>196.65</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-69.23999999999999</v>
+        <v>-69.25</v>
       </c>
       <c r="K52" t="n">
-        <v>122.82</v>
+        <v>122.83</v>
       </c>
       <c r="L52" t="n">
-        <v>140.99</v>
+        <v>141</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>12.36</v>
+        <v>12.74</v>
       </c>
       <c r="K53" t="n">
-        <v>-241.99</v>
+        <v>-249.51</v>
       </c>
       <c r="L53" t="n">
-        <v>242.31</v>
+        <v>249.84</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>150.02</v>
+        <v>157.03</v>
       </c>
       <c r="K54" t="n">
-        <v>181.69</v>
+        <v>190.18</v>
       </c>
       <c r="L54" t="n">
-        <v>235.62</v>
+        <v>246.63</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-213.56</v>
+        <v>-219.15</v>
       </c>
       <c r="K55" t="n">
-        <v>188.09</v>
+        <v>193.02</v>
       </c>
       <c r="L55" t="n">
-        <v>284.58</v>
+        <v>292.04</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>152.78</v>
+        <v>161.96</v>
       </c>
       <c r="K56" t="n">
-        <v>-244.99</v>
+        <v>-259.7</v>
       </c>
       <c r="L56" t="n">
-        <v>288.72</v>
+        <v>306.07</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-433.84</v>
+        <v>-466.1</v>
       </c>
       <c r="K57" t="n">
-        <v>-306.39</v>
+        <v>-329.17</v>
       </c>
       <c r="L57" t="n">
-        <v>531.13</v>
+        <v>570.62</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-200.12</v>
+        <v>-216.63</v>
       </c>
       <c r="K58" t="n">
-        <v>143</v>
+        <v>154.79</v>
       </c>
       <c r="L58" t="n">
-        <v>245.96</v>
+        <v>266.25</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>157.42</v>
+        <v>154.44</v>
       </c>
       <c r="K59" t="n">
-        <v>64.89</v>
+        <v>63.66</v>
       </c>
       <c r="L59" t="n">
-        <v>170.27</v>
+        <v>167.05</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-26.27</v>
+        <v>-25.67</v>
       </c>
       <c r="K60" t="n">
-        <v>193.18</v>
+        <v>188.74</v>
       </c>
       <c r="L60" t="n">
-        <v>194.96</v>
+        <v>190.48</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>170.41</v>
+        <v>165.62</v>
       </c>
       <c r="K61" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="L61" t="n">
-        <v>170.42</v>
+        <v>165.62</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>75.33</v>
+        <v>72.61</v>
       </c>
       <c r="K62" t="n">
-        <v>-226.53</v>
+        <v>-218.37</v>
       </c>
       <c r="L62" t="n">
-        <v>238.73</v>
+        <v>230.12</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-139.41</v>
+        <v>-134.02</v>
       </c>
       <c r="K63" t="n">
-        <v>101.39</v>
+        <v>97.45999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>172.38</v>
+        <v>165.71</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>166.5</v>
+        <v>163.38</v>
       </c>
       <c r="K64" t="n">
-        <v>-232.45</v>
+        <v>-228.09</v>
       </c>
       <c r="L64" t="n">
-        <v>285.94</v>
+        <v>280.56</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>144.89</v>
+        <v>148.93</v>
       </c>
       <c r="K65" t="n">
-        <v>-172.64</v>
+        <v>-177.45</v>
       </c>
       <c r="L65" t="n">
-        <v>225.38</v>
+        <v>231.67</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-192.9</v>
+        <v>-194.54</v>
       </c>
       <c r="K66" t="n">
-        <v>35.63</v>
+        <v>35.94</v>
       </c>
       <c r="L66" t="n">
-        <v>196.16</v>
+        <v>197.84</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>41.59</v>
+        <v>41.72</v>
       </c>
       <c r="K67" t="n">
-        <v>-242.14</v>
+        <v>-242.86</v>
       </c>
       <c r="L67" t="n">
-        <v>245.68</v>
+        <v>246.41</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>225.55</v>
+        <v>231.54</v>
       </c>
       <c r="K68" t="n">
-        <v>-180.76</v>
+        <v>-185.56</v>
       </c>
       <c r="L68" t="n">
-        <v>289.05</v>
+        <v>296.72</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>349.57</v>
+        <v>363.93</v>
       </c>
       <c r="K69" t="n">
-        <v>163.73</v>
+        <v>170.45</v>
       </c>
       <c r="L69" t="n">
-        <v>386.01</v>
+        <v>401.87</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>264.74</v>
+        <v>272.73</v>
       </c>
       <c r="K70" t="n">
-        <v>83.75</v>
+        <v>86.27</v>
       </c>
       <c r="L70" t="n">
-        <v>277.67</v>
+        <v>286.05</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-116.45</v>
+        <v>-126.61</v>
       </c>
       <c r="K71" t="n">
-        <v>-538.39</v>
+        <v>-585.39</v>
       </c>
       <c r="L71" t="n">
-        <v>550.84</v>
+        <v>598.9299999999999</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-72.06999999999999</v>
+        <v>-77.59999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>282.63</v>
+        <v>304.34</v>
       </c>
       <c r="L72" t="n">
-        <v>291.67</v>
+        <v>314.08</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>428.75</v>
+        <v>461.94</v>
       </c>
       <c r="K73" t="n">
-        <v>51.53</v>
+        <v>55.52</v>
       </c>
       <c r="L73" t="n">
-        <v>431.83</v>
+        <v>465.27</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>92.87</v>
+        <v>89.86</v>
       </c>
       <c r="K74" t="n">
-        <v>126.04</v>
+        <v>121.95</v>
       </c>
       <c r="L74" t="n">
-        <v>156.56</v>
+        <v>151.48</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-261.89</v>
+        <v>-252.72</v>
       </c>
       <c r="K75" t="n">
-        <v>107.5</v>
+        <v>103.74</v>
       </c>
       <c r="L75" t="n">
-        <v>283.1</v>
+        <v>273.19</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>73.76000000000001</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="K76" t="n">
-        <v>216.53</v>
+        <v>209.14</v>
       </c>
       <c r="L76" t="n">
-        <v>228.75</v>
+        <v>220.94</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-177.71</v>
+        <v>-176.39</v>
       </c>
       <c r="K77" t="n">
-        <v>56.09</v>
+        <v>55.67</v>
       </c>
       <c r="L77" t="n">
-        <v>186.35</v>
+        <v>184.96</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>109.45</v>
+        <v>108.21</v>
       </c>
       <c r="K78" t="n">
-        <v>116.65</v>
+        <v>115.34</v>
       </c>
       <c r="L78" t="n">
-        <v>159.96</v>
+        <v>158.15</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-135.47</v>
+        <v>-132.68</v>
       </c>
       <c r="K79" t="n">
-        <v>110.15</v>
+        <v>107.88</v>
       </c>
       <c r="L79" t="n">
-        <v>174.6</v>
+        <v>171</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>90.05</v>
+        <v>93.79000000000001</v>
       </c>
       <c r="K80" t="n">
-        <v>-158.75</v>
+        <v>-165.35</v>
       </c>
       <c r="L80" t="n">
-        <v>182.51</v>
+        <v>190.1</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>169.98</v>
+        <v>170.34</v>
       </c>
       <c r="K81" t="n">
-        <v>-16.48</v>
+        <v>-16.51</v>
       </c>
       <c r="L81" t="n">
-        <v>170.78</v>
+        <v>171.14</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-193.83</v>
+        <v>-198.8</v>
       </c>
       <c r="K82" t="n">
-        <v>-77.06</v>
+        <v>-79.04000000000001</v>
       </c>
       <c r="L82" t="n">
-        <v>208.59</v>
+        <v>213.94</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>252.48</v>
+        <v>261.34</v>
       </c>
       <c r="K83" t="n">
-        <v>102.69</v>
+        <v>106.29</v>
       </c>
       <c r="L83" t="n">
-        <v>272.56</v>
+        <v>282.13</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-62.41</v>
+        <v>-65.26000000000001</v>
       </c>
       <c r="K84" t="n">
-        <v>240.77</v>
+        <v>251.79</v>
       </c>
       <c r="L84" t="n">
-        <v>248.72</v>
+        <v>260.11</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>198.83</v>
+        <v>206.71</v>
       </c>
       <c r="K85" t="n">
-        <v>-84.18000000000001</v>
+        <v>-87.51000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>215.92</v>
+        <v>224.47</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>233.07</v>
+        <v>251.79</v>
       </c>
       <c r="K86" t="n">
-        <v>-250.31</v>
+        <v>-270.41</v>
       </c>
       <c r="L86" t="n">
-        <v>342.02</v>
+        <v>369.48</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>121.21</v>
+        <v>128.8</v>
       </c>
       <c r="K87" t="n">
-        <v>-383.66</v>
+        <v>-407.68</v>
       </c>
       <c r="L87" t="n">
-        <v>402.35</v>
+        <v>427.54</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>524.21</v>
+        <v>554.38</v>
       </c>
       <c r="K88" t="n">
-        <v>399.5</v>
+        <v>422.49</v>
       </c>
       <c r="L88" t="n">
-        <v>659.09</v>
+        <v>697.02</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-10.xlsx
+++ b/output/2024-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-51.42</v>
+        <v>-25.86</v>
       </c>
       <c r="K14" t="n">
-        <v>85.45999999999999</v>
+        <v>42.97</v>
       </c>
       <c r="L14" t="n">
-        <v>99.73999999999999</v>
+        <v>50.15</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-93.67</v>
+        <v>-47.69</v>
       </c>
       <c r="K15" t="n">
-        <v>-38.84</v>
+        <v>-19.78</v>
       </c>
       <c r="L15" t="n">
-        <v>101.4</v>
+        <v>51.63</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>97.61</v>
+        <v>54.69</v>
       </c>
       <c r="K16" t="n">
-        <v>-86.98</v>
+        <v>-48.74</v>
       </c>
       <c r="L16" t="n">
-        <v>130.74</v>
+        <v>73.26000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-88.39</v>
+        <v>-46.65</v>
       </c>
       <c r="K17" t="n">
-        <v>-8.93</v>
+        <v>-4.71</v>
       </c>
       <c r="L17" t="n">
-        <v>88.84</v>
+        <v>46.88</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-179.7</v>
+        <v>-90.45</v>
       </c>
       <c r="K18" t="n">
-        <v>-45.62</v>
+        <v>-22.97</v>
       </c>
       <c r="L18" t="n">
-        <v>185.4</v>
+        <v>93.31999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>-61.52</v>
+        <v>-31.9</v>
       </c>
       <c r="K19" t="n">
-        <v>54.55</v>
+        <v>28.28</v>
       </c>
       <c r="L19" t="n">
-        <v>82.23</v>
+        <v>42.63</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-142.18</v>
+        <v>-71.87</v>
       </c>
       <c r="K20" t="n">
-        <v>-29.61</v>
+        <v>-14.97</v>
       </c>
       <c r="L20" t="n">
-        <v>145.22</v>
+        <v>73.41</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>70.09999999999999</v>
+        <v>34.12</v>
       </c>
       <c r="K21" t="n">
-        <v>171.64</v>
+        <v>83.56</v>
       </c>
       <c r="L21" t="n">
-        <v>185.4</v>
+        <v>90.26000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>13.85</v>
+        <v>7.83</v>
       </c>
       <c r="K22" t="n">
-        <v>124.39</v>
+        <v>70.38</v>
       </c>
       <c r="L22" t="n">
-        <v>125.16</v>
+        <v>70.81</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-224.41</v>
+        <v>-119.07</v>
       </c>
       <c r="K23" t="n">
-        <v>129.42</v>
+        <v>68.67</v>
       </c>
       <c r="L23" t="n">
-        <v>259.05</v>
+        <v>137.45</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>44</v>
+        <v>21.07</v>
       </c>
       <c r="K24" t="n">
-        <v>378.36</v>
+        <v>181.22</v>
       </c>
       <c r="L24" t="n">
-        <v>380.91</v>
+        <v>182.44</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-172.84</v>
+        <v>-97.93000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>105.4</v>
+        <v>59.72</v>
       </c>
       <c r="L25" t="n">
-        <v>202.45</v>
+        <v>114.7</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-24.22</v>
+        <v>-13.63</v>
       </c>
       <c r="K26" t="n">
-        <v>-300.04</v>
+        <v>-168.84</v>
       </c>
       <c r="L26" t="n">
-        <v>301.02</v>
+        <v>169.39</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>302.34</v>
+        <v>164.08</v>
       </c>
       <c r="K27" t="n">
-        <v>-130.39</v>
+        <v>-70.76000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>329.25</v>
+        <v>178.69</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>300.81</v>
+        <v>167.2</v>
       </c>
       <c r="K28" t="n">
-        <v>-133.26</v>
+        <v>-74.06999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>329</v>
+        <v>182.87</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-144.6</v>
+        <v>-71.31999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>-77.68000000000001</v>
+        <v>-38.31</v>
       </c>
       <c r="L29" t="n">
-        <v>164.15</v>
+        <v>80.95999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-95.62</v>
+        <v>-43.1</v>
       </c>
       <c r="K30" t="n">
-        <v>-51.46</v>
+        <v>-23.19</v>
       </c>
       <c r="L30" t="n">
-        <v>108.59</v>
+        <v>48.94</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>153.82</v>
+        <v>63.25</v>
       </c>
       <c r="K31" t="n">
-        <v>43.38</v>
+        <v>17.84</v>
       </c>
       <c r="L31" t="n">
-        <v>159.82</v>
+        <v>65.72</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>26.01</v>
+        <v>13.2</v>
       </c>
       <c r="K32" t="n">
-        <v>76.2</v>
+        <v>38.67</v>
       </c>
       <c r="L32" t="n">
-        <v>80.51000000000001</v>
+        <v>40.86</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>95.19</v>
+        <v>43.67</v>
       </c>
       <c r="K33" t="n">
-        <v>-121.12</v>
+        <v>-55.57</v>
       </c>
       <c r="L33" t="n">
-        <v>154.05</v>
+        <v>70.68000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>69.73999999999999</v>
+        <v>31.78</v>
       </c>
       <c r="K34" t="n">
-        <v>110</v>
+        <v>50.13</v>
       </c>
       <c r="L34" t="n">
-        <v>130.24</v>
+        <v>59.36</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-8.93</v>
+        <v>-4.57</v>
       </c>
       <c r="K35" t="n">
-        <v>158.98</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>159.23</v>
+        <v>81.56</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-7.36</v>
+        <v>-3.72</v>
       </c>
       <c r="K36" t="n">
-        <v>-183.59</v>
+        <v>-92.92</v>
       </c>
       <c r="L36" t="n">
-        <v>183.74</v>
+        <v>92.98999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-142.04</v>
+        <v>-76.08</v>
       </c>
       <c r="K37" t="n">
-        <v>58.84</v>
+        <v>31.52</v>
       </c>
       <c r="L37" t="n">
-        <v>153.75</v>
+        <v>82.34999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>405.61</v>
+        <v>207.08</v>
       </c>
       <c r="K38" t="n">
-        <v>-9.779999999999999</v>
+        <v>-4.99</v>
       </c>
       <c r="L38" t="n">
-        <v>405.73</v>
+        <v>207.14</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>151.69</v>
+        <v>73.98</v>
       </c>
       <c r="K39" t="n">
-        <v>111.3</v>
+        <v>54.29</v>
       </c>
       <c r="L39" t="n">
-        <v>188.14</v>
+        <v>91.76000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>23.93</v>
+        <v>11.44</v>
       </c>
       <c r="K40" t="n">
-        <v>-413.95</v>
+        <v>-197.91</v>
       </c>
       <c r="L40" t="n">
-        <v>414.64</v>
+        <v>198.24</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-240.44</v>
+        <v>-130.19</v>
       </c>
       <c r="K41" t="n">
-        <v>-137.58</v>
+        <v>-74.48999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>277.02</v>
+        <v>150</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>347.78</v>
+        <v>192.89</v>
       </c>
       <c r="K42" t="n">
-        <v>-145.9</v>
+        <v>-80.92</v>
       </c>
       <c r="L42" t="n">
-        <v>377.15</v>
+        <v>209.18</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>370.72</v>
+        <v>200.55</v>
       </c>
       <c r="K43" t="n">
-        <v>396.9</v>
+        <v>214.72</v>
       </c>
       <c r="L43" t="n">
-        <v>543.11</v>
+        <v>293.81</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-86.45</v>
+        <v>-42.84</v>
       </c>
       <c r="K44" t="n">
-        <v>-140.83</v>
+        <v>-69.79000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>165.24</v>
+        <v>81.89</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-12.53</v>
+        <v>-5.61</v>
       </c>
       <c r="K45" t="n">
-        <v>-92.48999999999999</v>
+        <v>-41.43</v>
       </c>
       <c r="L45" t="n">
-        <v>93.33</v>
+        <v>41.81</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>72.61</v>
+        <v>30.11</v>
       </c>
       <c r="K46" t="n">
-        <v>-23.29</v>
+        <v>-9.66</v>
       </c>
       <c r="L46" t="n">
-        <v>76.25</v>
+        <v>31.62</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>87.76000000000001</v>
+        <v>39.29</v>
       </c>
       <c r="K47" t="n">
-        <v>158.14</v>
+        <v>70.8</v>
       </c>
       <c r="L47" t="n">
-        <v>180.86</v>
+        <v>80.95999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>66.98999999999999</v>
+        <v>28.11</v>
       </c>
       <c r="K48" t="n">
-        <v>-312.62</v>
+        <v>-131.15</v>
       </c>
       <c r="L48" t="n">
-        <v>319.72</v>
+        <v>134.13</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-25.68</v>
+        <v>-12.9</v>
       </c>
       <c r="K49" t="n">
-        <v>-161.63</v>
+        <v>-81.19</v>
       </c>
       <c r="L49" t="n">
-        <v>163.66</v>
+        <v>82.20999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>27.19</v>
+        <v>13.38</v>
       </c>
       <c r="K50" t="n">
-        <v>-187.86</v>
+        <v>-92.41</v>
       </c>
       <c r="L50" t="n">
-        <v>189.81</v>
+        <v>93.38</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-151.43</v>
+        <v>-74.45999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-125.46</v>
+        <v>-61.69</v>
       </c>
       <c r="L51" t="n">
-        <v>196.65</v>
+        <v>96.69</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-69.25</v>
+        <v>-33.7</v>
       </c>
       <c r="K52" t="n">
-        <v>122.83</v>
+        <v>59.77</v>
       </c>
       <c r="L52" t="n">
-        <v>141</v>
+        <v>68.61</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>12.74</v>
+        <v>6.45</v>
       </c>
       <c r="K53" t="n">
-        <v>-249.51</v>
+        <v>-126.39</v>
       </c>
       <c r="L53" t="n">
-        <v>249.84</v>
+        <v>126.56</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>157.03</v>
+        <v>77.73999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>190.18</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>246.63</v>
+        <v>122.09</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-219.15</v>
+        <v>-107.48</v>
       </c>
       <c r="K55" t="n">
-        <v>193.02</v>
+        <v>94.67</v>
       </c>
       <c r="L55" t="n">
-        <v>292.04</v>
+        <v>143.23</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>161.96</v>
+        <v>87.98</v>
       </c>
       <c r="K56" t="n">
-        <v>-259.7</v>
+        <v>-141.07</v>
       </c>
       <c r="L56" t="n">
-        <v>306.07</v>
+        <v>166.26</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-466.1</v>
+        <v>-249.54</v>
       </c>
       <c r="K57" t="n">
-        <v>-329.17</v>
+        <v>-176.23</v>
       </c>
       <c r="L57" t="n">
-        <v>570.62</v>
+        <v>305.5</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-216.63</v>
+        <v>-118.69</v>
       </c>
       <c r="K58" t="n">
-        <v>154.79</v>
+        <v>84.81</v>
       </c>
       <c r="L58" t="n">
-        <v>266.25</v>
+        <v>145.88</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>154.44</v>
+        <v>67.31</v>
       </c>
       <c r="K59" t="n">
-        <v>63.66</v>
+        <v>27.75</v>
       </c>
       <c r="L59" t="n">
-        <v>167.05</v>
+        <v>72.8</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-25.67</v>
+        <v>-10.19</v>
       </c>
       <c r="K60" t="n">
-        <v>188.74</v>
+        <v>74.94</v>
       </c>
       <c r="L60" t="n">
-        <v>190.48</v>
+        <v>75.63</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>165.62</v>
+        <v>78.73</v>
       </c>
       <c r="K61" t="n">
-        <v>1.72</v>
+        <v>0.82</v>
       </c>
       <c r="L61" t="n">
-        <v>165.62</v>
+        <v>78.73</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>72.61</v>
+        <v>34.19</v>
       </c>
       <c r="K62" t="n">
-        <v>-218.37</v>
+        <v>-102.82</v>
       </c>
       <c r="L62" t="n">
-        <v>230.12</v>
+        <v>108.35</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-134.02</v>
+        <v>-63.9</v>
       </c>
       <c r="K63" t="n">
-        <v>97.45999999999999</v>
+        <v>46.47</v>
       </c>
       <c r="L63" t="n">
-        <v>165.71</v>
+        <v>79.01000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>163.38</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="K64" t="n">
-        <v>-228.09</v>
+        <v>-99.61</v>
       </c>
       <c r="L64" t="n">
-        <v>280.56</v>
+        <v>122.53</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>148.93</v>
+        <v>72.20999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-177.45</v>
+        <v>-86.04000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>231.67</v>
+        <v>112.33</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-194.54</v>
+        <v>-96.23999999999999</v>
       </c>
       <c r="K66" t="n">
-        <v>35.94</v>
+        <v>17.78</v>
       </c>
       <c r="L66" t="n">
-        <v>197.84</v>
+        <v>97.87</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>41.72</v>
+        <v>20.43</v>
       </c>
       <c r="K67" t="n">
-        <v>-242.86</v>
+        <v>-118.95</v>
       </c>
       <c r="L67" t="n">
-        <v>246.41</v>
+        <v>120.69</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>231.54</v>
+        <v>116.16</v>
       </c>
       <c r="K68" t="n">
-        <v>-185.56</v>
+        <v>-93.09</v>
       </c>
       <c r="L68" t="n">
-        <v>296.72</v>
+        <v>148.86</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>363.93</v>
+        <v>170.37</v>
       </c>
       <c r="K69" t="n">
-        <v>170.45</v>
+        <v>79.79000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>401.87</v>
+        <v>188.13</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>272.73</v>
+        <v>120.89</v>
       </c>
       <c r="K70" t="n">
-        <v>86.27</v>
+        <v>38.24</v>
       </c>
       <c r="L70" t="n">
-        <v>286.05</v>
+        <v>126.79</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-126.61</v>
+        <v>-67.79000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-585.39</v>
+        <v>-313.41</v>
       </c>
       <c r="L71" t="n">
-        <v>598.9299999999999</v>
+        <v>320.65</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-77.59999999999999</v>
+        <v>-41.5</v>
       </c>
       <c r="K72" t="n">
-        <v>304.34</v>
+        <v>162.74</v>
       </c>
       <c r="L72" t="n">
-        <v>314.08</v>
+        <v>167.94</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>461.94</v>
+        <v>257.04</v>
       </c>
       <c r="K73" t="n">
-        <v>55.52</v>
+        <v>30.89</v>
       </c>
       <c r="L73" t="n">
-        <v>465.27</v>
+        <v>258.89</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>89.86</v>
+        <v>35.69</v>
       </c>
       <c r="K74" t="n">
-        <v>121.95</v>
+        <v>48.43</v>
       </c>
       <c r="L74" t="n">
-        <v>151.48</v>
+        <v>60.16</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-252.72</v>
+        <v>-101.5</v>
       </c>
       <c r="K75" t="n">
-        <v>103.74</v>
+        <v>41.66</v>
       </c>
       <c r="L75" t="n">
-        <v>273.19</v>
+        <v>109.72</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>71.23999999999999</v>
+        <v>31.66</v>
       </c>
       <c r="K76" t="n">
-        <v>209.14</v>
+        <v>92.94</v>
       </c>
       <c r="L76" t="n">
-        <v>220.94</v>
+        <v>98.19</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-176.39</v>
+        <v>-83.5</v>
       </c>
       <c r="K77" t="n">
-        <v>55.67</v>
+        <v>26.35</v>
       </c>
       <c r="L77" t="n">
-        <v>184.96</v>
+        <v>87.56</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>108.21</v>
+        <v>46.03</v>
       </c>
       <c r="K78" t="n">
-        <v>115.34</v>
+        <v>49.06</v>
       </c>
       <c r="L78" t="n">
-        <v>158.15</v>
+        <v>67.28</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-132.68</v>
+        <v>-55.74</v>
       </c>
       <c r="K79" t="n">
-        <v>107.88</v>
+        <v>45.32</v>
       </c>
       <c r="L79" t="n">
-        <v>171</v>
+        <v>71.84</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>93.79000000000001</v>
+        <v>45.58</v>
       </c>
       <c r="K80" t="n">
-        <v>-165.35</v>
+        <v>-80.34999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>190.1</v>
+        <v>92.38</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>170.34</v>
+        <v>83.47</v>
       </c>
       <c r="K81" t="n">
-        <v>-16.51</v>
+        <v>-8.09</v>
       </c>
       <c r="L81" t="n">
-        <v>171.14</v>
+        <v>83.86</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-198.8</v>
+        <v>-96.06</v>
       </c>
       <c r="K82" t="n">
-        <v>-79.04000000000001</v>
+        <v>-38.19</v>
       </c>
       <c r="L82" t="n">
-        <v>213.94</v>
+        <v>103.37</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>261.34</v>
+        <v>114.72</v>
       </c>
       <c r="K83" t="n">
-        <v>106.29</v>
+        <v>46.66</v>
       </c>
       <c r="L83" t="n">
-        <v>282.13</v>
+        <v>123.85</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-65.26000000000001</v>
+        <v>-30.71</v>
       </c>
       <c r="K84" t="n">
-        <v>251.79</v>
+        <v>118.49</v>
       </c>
       <c r="L84" t="n">
-        <v>260.11</v>
+        <v>122.4</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>206.71</v>
+        <v>98.48</v>
       </c>
       <c r="K85" t="n">
-        <v>-87.51000000000001</v>
+        <v>-41.69</v>
       </c>
       <c r="L85" t="n">
-        <v>224.47</v>
+        <v>106.94</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>251.79</v>
+        <v>134.19</v>
       </c>
       <c r="K86" t="n">
-        <v>-270.41</v>
+        <v>-144.12</v>
       </c>
       <c r="L86" t="n">
-        <v>369.48</v>
+        <v>196.92</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>128.8</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>-407.68</v>
+        <v>-224.94</v>
       </c>
       <c r="L87" t="n">
-        <v>427.54</v>
+        <v>235.9</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>554.38</v>
+        <v>293.48</v>
       </c>
       <c r="K88" t="n">
-        <v>422.49</v>
+        <v>223.66</v>
       </c>
       <c r="L88" t="n">
-        <v>697.02</v>
+        <v>369</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-10.xlsx
+++ b/output/2024-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-25.86</v>
+        <v>-26.5</v>
       </c>
       <c r="K14" t="n">
-        <v>42.97</v>
+        <v>44.05</v>
       </c>
       <c r="L14" t="n">
-        <v>50.15</v>
+        <v>51.41</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-47.69</v>
+        <v>-48.8</v>
       </c>
       <c r="K15" t="n">
-        <v>-19.78</v>
+        <v>-20.23</v>
       </c>
       <c r="L15" t="n">
-        <v>51.63</v>
+        <v>52.83</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>54.69</v>
+        <v>53.83</v>
       </c>
       <c r="K16" t="n">
-        <v>-48.74</v>
+        <v>-47.98</v>
       </c>
       <c r="L16" t="n">
-        <v>73.26000000000001</v>
+        <v>72.11</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-46.65</v>
+        <v>-49.58</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.71</v>
+        <v>-5.01</v>
       </c>
       <c r="L17" t="n">
-        <v>46.88</v>
+        <v>49.83</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-90.45</v>
+        <v>-87.45</v>
       </c>
       <c r="K18" t="n">
-        <v>-22.97</v>
+        <v>-22.2</v>
       </c>
       <c r="L18" t="n">
-        <v>93.31999999999999</v>
+        <v>90.23</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>-31.9</v>
+        <v>-34.27</v>
       </c>
       <c r="K19" t="n">
-        <v>28.28</v>
+        <v>30.38</v>
       </c>
       <c r="L19" t="n">
-        <v>42.63</v>
+        <v>45.8</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-71.87</v>
+        <v>-76.26000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-14.97</v>
+        <v>-15.88</v>
       </c>
       <c r="L20" t="n">
-        <v>73.41</v>
+        <v>77.89</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>34.12</v>
+        <v>35.33</v>
       </c>
       <c r="K21" t="n">
-        <v>83.56</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>90.26000000000001</v>
+        <v>93.44</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>7.83</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>70.38</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>70.81</v>
+        <v>74.92</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-119.07</v>
+        <v>-119.94</v>
       </c>
       <c r="K23" t="n">
-        <v>68.67</v>
+        <v>69.17</v>
       </c>
       <c r="L23" t="n">
-        <v>137.45</v>
+        <v>138.46</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>21.07</v>
+        <v>20.83</v>
       </c>
       <c r="K24" t="n">
-        <v>181.22</v>
+        <v>179.09</v>
       </c>
       <c r="L24" t="n">
-        <v>182.44</v>
+        <v>180.3</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-97.93000000000001</v>
+        <v>-101.14</v>
       </c>
       <c r="K25" t="n">
-        <v>59.72</v>
+        <v>61.68</v>
       </c>
       <c r="L25" t="n">
-        <v>114.7</v>
+        <v>118.46</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.63</v>
+        <v>-13.98</v>
       </c>
       <c r="K26" t="n">
-        <v>-168.84</v>
+        <v>-173.23</v>
       </c>
       <c r="L26" t="n">
-        <v>169.39</v>
+        <v>173.79</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>164.08</v>
+        <v>177.21</v>
       </c>
       <c r="K27" t="n">
-        <v>-70.76000000000001</v>
+        <v>-76.43000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>178.69</v>
+        <v>192.99</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>167.2</v>
+        <v>171.11</v>
       </c>
       <c r="K28" t="n">
-        <v>-74.06999999999999</v>
+        <v>-75.8</v>
       </c>
       <c r="L28" t="n">
-        <v>182.87</v>
+        <v>187.15</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-71.31999999999999</v>
+        <v>-68.73</v>
       </c>
       <c r="K29" t="n">
-        <v>-38.31</v>
+        <v>-36.92</v>
       </c>
       <c r="L29" t="n">
-        <v>80.95999999999999</v>
+        <v>78.01000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-43.1</v>
+        <v>-43.83</v>
       </c>
       <c r="K30" t="n">
-        <v>-23.19</v>
+        <v>-23.59</v>
       </c>
       <c r="L30" t="n">
-        <v>48.94</v>
+        <v>49.77</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>63.25</v>
+        <v>61.24</v>
       </c>
       <c r="K31" t="n">
-        <v>17.84</v>
+        <v>17.27</v>
       </c>
       <c r="L31" t="n">
-        <v>65.72</v>
+        <v>63.63</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>13.2</v>
+        <v>12.89</v>
       </c>
       <c r="K32" t="n">
-        <v>38.67</v>
+        <v>37.76</v>
       </c>
       <c r="L32" t="n">
-        <v>40.86</v>
+        <v>39.9</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>43.67</v>
+        <v>43.41</v>
       </c>
       <c r="K33" t="n">
-        <v>-55.57</v>
+        <v>-55.23</v>
       </c>
       <c r="L33" t="n">
-        <v>70.68000000000001</v>
+        <v>70.25</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>31.78</v>
+        <v>31.83</v>
       </c>
       <c r="K34" t="n">
-        <v>50.13</v>
+        <v>50.21</v>
       </c>
       <c r="L34" t="n">
-        <v>59.36</v>
+        <v>59.45</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.57</v>
+        <v>-4.67</v>
       </c>
       <c r="K35" t="n">
-        <v>81.43000000000001</v>
+        <v>83.18000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>81.56</v>
+        <v>83.31999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.72</v>
+        <v>-3.75</v>
       </c>
       <c r="K36" t="n">
-        <v>-92.92</v>
+        <v>-93.61</v>
       </c>
       <c r="L36" t="n">
-        <v>92.98999999999999</v>
+        <v>93.69</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-76.08</v>
+        <v>-78.18000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>31.52</v>
+        <v>32.39</v>
       </c>
       <c r="L37" t="n">
-        <v>82.34999999999999</v>
+        <v>84.63</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>207.08</v>
+        <v>200.75</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.99</v>
+        <v>-4.84</v>
       </c>
       <c r="L38" t="n">
-        <v>207.14</v>
+        <v>200.81</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>73.98</v>
+        <v>79.45999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>54.29</v>
+        <v>58.3</v>
       </c>
       <c r="L39" t="n">
-        <v>91.76000000000001</v>
+        <v>98.56</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>11.44</v>
+        <v>11.21</v>
       </c>
       <c r="K40" t="n">
-        <v>-197.91</v>
+        <v>-193.91</v>
       </c>
       <c r="L40" t="n">
-        <v>198.24</v>
+        <v>194.24</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-130.19</v>
+        <v>-141.72</v>
       </c>
       <c r="K41" t="n">
-        <v>-74.48999999999999</v>
+        <v>-81.09</v>
       </c>
       <c r="L41" t="n">
-        <v>150</v>
+        <v>163.29</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>192.89</v>
+        <v>195.65</v>
       </c>
       <c r="K42" t="n">
-        <v>-80.92</v>
+        <v>-82.08</v>
       </c>
       <c r="L42" t="n">
-        <v>209.18</v>
+        <v>212.17</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>200.55</v>
+        <v>203.45</v>
       </c>
       <c r="K43" t="n">
-        <v>214.72</v>
+        <v>217.82</v>
       </c>
       <c r="L43" t="n">
-        <v>293.81</v>
+        <v>298.06</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-42.84</v>
+        <v>-40.93</v>
       </c>
       <c r="K44" t="n">
-        <v>-69.79000000000001</v>
+        <v>-66.68000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>81.89</v>
+        <v>78.23999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.61</v>
+        <v>-5.91</v>
       </c>
       <c r="K45" t="n">
-        <v>-41.43</v>
+        <v>-43.63</v>
       </c>
       <c r="L45" t="n">
-        <v>41.81</v>
+        <v>44.03</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>30.11</v>
+        <v>28.79</v>
       </c>
       <c r="K46" t="n">
-        <v>-9.66</v>
+        <v>-9.23</v>
       </c>
       <c r="L46" t="n">
-        <v>31.62</v>
+        <v>30.23</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>39.29</v>
+        <v>37.88</v>
       </c>
       <c r="K47" t="n">
-        <v>70.8</v>
+        <v>68.27</v>
       </c>
       <c r="L47" t="n">
-        <v>80.95999999999999</v>
+        <v>78.06999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>28.11</v>
+        <v>25.68</v>
       </c>
       <c r="K48" t="n">
-        <v>-131.15</v>
+        <v>-119.85</v>
       </c>
       <c r="L48" t="n">
-        <v>134.13</v>
+        <v>122.57</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.9</v>
+        <v>-12.57</v>
       </c>
       <c r="K49" t="n">
-        <v>-81.19</v>
+        <v>-79.09</v>
       </c>
       <c r="L49" t="n">
-        <v>82.20999999999999</v>
+        <v>80.09</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>13.38</v>
+        <v>13.7</v>
       </c>
       <c r="K50" t="n">
-        <v>-92.41</v>
+        <v>-94.64</v>
       </c>
       <c r="L50" t="n">
-        <v>93.38</v>
+        <v>95.63</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-74.45999999999999</v>
+        <v>-76.05</v>
       </c>
       <c r="K51" t="n">
-        <v>-61.69</v>
+        <v>-63.01</v>
       </c>
       <c r="L51" t="n">
-        <v>96.69</v>
+        <v>98.76000000000001</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-33.7</v>
+        <v>-36.15</v>
       </c>
       <c r="K52" t="n">
-        <v>59.77</v>
+        <v>64.12</v>
       </c>
       <c r="L52" t="n">
-        <v>68.61</v>
+        <v>73.61</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>6.45</v>
+        <v>6.61</v>
       </c>
       <c r="K53" t="n">
-        <v>-126.39</v>
+        <v>-129.52</v>
       </c>
       <c r="L53" t="n">
-        <v>126.56</v>
+        <v>129.69</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>77.73999999999999</v>
+        <v>80.59</v>
       </c>
       <c r="K54" t="n">
-        <v>94.15000000000001</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>122.09</v>
+        <v>126.57</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-107.48</v>
+        <v>-108.15</v>
       </c>
       <c r="K55" t="n">
-        <v>94.67</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>143.23</v>
+        <v>144.12</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>87.98</v>
+        <v>94.3</v>
       </c>
       <c r="K56" t="n">
-        <v>-141.07</v>
+        <v>-151.21</v>
       </c>
       <c r="L56" t="n">
-        <v>166.26</v>
+        <v>178.21</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-249.54</v>
+        <v>-258.23</v>
       </c>
       <c r="K57" t="n">
-        <v>-176.23</v>
+        <v>-182.37</v>
       </c>
       <c r="L57" t="n">
-        <v>305.5</v>
+        <v>316.14</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-118.69</v>
+        <v>-130.63</v>
       </c>
       <c r="K58" t="n">
-        <v>84.81</v>
+        <v>93.34</v>
       </c>
       <c r="L58" t="n">
-        <v>145.88</v>
+        <v>160.56</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>67.31</v>
+        <v>65.16</v>
       </c>
       <c r="K59" t="n">
-        <v>27.75</v>
+        <v>26.86</v>
       </c>
       <c r="L59" t="n">
-        <v>72.8</v>
+        <v>70.48</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-10.19</v>
+        <v>-9.640000000000001</v>
       </c>
       <c r="K60" t="n">
-        <v>74.94</v>
+        <v>70.88</v>
       </c>
       <c r="L60" t="n">
-        <v>75.63</v>
+        <v>71.53</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>78.73</v>
+        <v>76.19</v>
       </c>
       <c r="K61" t="n">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="L61" t="n">
-        <v>78.73</v>
+        <v>76.2</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>34.19</v>
+        <v>32.17</v>
       </c>
       <c r="K62" t="n">
-        <v>-102.82</v>
+        <v>-96.73999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>108.35</v>
+        <v>101.95</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-63.9</v>
+        <v>-62.02</v>
       </c>
       <c r="K63" t="n">
-        <v>46.47</v>
+        <v>45.1</v>
       </c>
       <c r="L63" t="n">
-        <v>79.01000000000001</v>
+        <v>76.69</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>71.34999999999999</v>
+        <v>66.11</v>
       </c>
       <c r="K64" t="n">
-        <v>-99.61</v>
+        <v>-92.29000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>122.53</v>
+        <v>113.52</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>72.20999999999999</v>
+        <v>72.28</v>
       </c>
       <c r="K65" t="n">
-        <v>-86.04000000000001</v>
+        <v>-86.12</v>
       </c>
       <c r="L65" t="n">
-        <v>112.33</v>
+        <v>112.43</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-96.23999999999999</v>
+        <v>-97.01000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>17.78</v>
+        <v>17.92</v>
       </c>
       <c r="L66" t="n">
-        <v>97.87</v>
+        <v>98.65000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>20.43</v>
+        <v>20.01</v>
       </c>
       <c r="K67" t="n">
-        <v>-118.95</v>
+        <v>-116.51</v>
       </c>
       <c r="L67" t="n">
-        <v>120.69</v>
+        <v>118.21</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>116.16</v>
+        <v>115.89</v>
       </c>
       <c r="K68" t="n">
-        <v>-93.09</v>
+        <v>-92.88</v>
       </c>
       <c r="L68" t="n">
-        <v>148.86</v>
+        <v>148.52</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>170.37</v>
+        <v>167.44</v>
       </c>
       <c r="K69" t="n">
-        <v>79.79000000000001</v>
+        <v>78.42</v>
       </c>
       <c r="L69" t="n">
-        <v>188.13</v>
+        <v>184.9</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>120.89</v>
+        <v>127.32</v>
       </c>
       <c r="K70" t="n">
-        <v>38.24</v>
+        <v>40.28</v>
       </c>
       <c r="L70" t="n">
-        <v>126.79</v>
+        <v>133.54</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-67.79000000000001</v>
+        <v>-70.09</v>
       </c>
       <c r="K71" t="n">
-        <v>-313.41</v>
+        <v>-324.04</v>
       </c>
       <c r="L71" t="n">
-        <v>320.65</v>
+        <v>331.54</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-41.5</v>
+        <v>-46.43</v>
       </c>
       <c r="K72" t="n">
-        <v>162.74</v>
+        <v>182.07</v>
       </c>
       <c r="L72" t="n">
-        <v>167.94</v>
+        <v>187.9</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>257.04</v>
+        <v>255.94</v>
       </c>
       <c r="K73" t="n">
-        <v>30.89</v>
+        <v>30.76</v>
       </c>
       <c r="L73" t="n">
-        <v>258.89</v>
+        <v>257.78</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>35.69</v>
+        <v>34.76</v>
       </c>
       <c r="K74" t="n">
-        <v>48.43</v>
+        <v>47.17</v>
       </c>
       <c r="L74" t="n">
-        <v>60.16</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-101.5</v>
+        <v>-92.52</v>
       </c>
       <c r="K75" t="n">
-        <v>41.66</v>
+        <v>37.98</v>
       </c>
       <c r="L75" t="n">
-        <v>109.72</v>
+        <v>100.01</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>31.66</v>
+        <v>29.59</v>
       </c>
       <c r="K76" t="n">
-        <v>92.94</v>
+        <v>86.87</v>
       </c>
       <c r="L76" t="n">
-        <v>98.19</v>
+        <v>91.78</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-83.5</v>
+        <v>-81.14</v>
       </c>
       <c r="K77" t="n">
-        <v>26.35</v>
+        <v>25.61</v>
       </c>
       <c r="L77" t="n">
-        <v>87.56</v>
+        <v>85.09</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>46.03</v>
+        <v>45.78</v>
       </c>
       <c r="K78" t="n">
-        <v>49.06</v>
+        <v>48.8</v>
       </c>
       <c r="L78" t="n">
-        <v>67.28</v>
+        <v>66.91</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-55.74</v>
+        <v>-54.76</v>
       </c>
       <c r="K79" t="n">
-        <v>45.32</v>
+        <v>44.53</v>
       </c>
       <c r="L79" t="n">
-        <v>71.84</v>
+        <v>70.58</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>45.58</v>
+        <v>47.2</v>
       </c>
       <c r="K80" t="n">
-        <v>-80.34999999999999</v>
+        <v>-83.20999999999999</v>
       </c>
       <c r="L80" t="n">
-        <v>92.38</v>
+        <v>95.67</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>83.47</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="K81" t="n">
-        <v>-8.09</v>
+        <v>-8.31</v>
       </c>
       <c r="L81" t="n">
-        <v>83.86</v>
+        <v>86.16</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-96.06</v>
+        <v>-97.7</v>
       </c>
       <c r="K82" t="n">
-        <v>-38.19</v>
+        <v>-38.85</v>
       </c>
       <c r="L82" t="n">
-        <v>103.37</v>
+        <v>105.14</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>114.72</v>
+        <v>126.01</v>
       </c>
       <c r="K83" t="n">
-        <v>46.66</v>
+        <v>51.25</v>
       </c>
       <c r="L83" t="n">
-        <v>123.85</v>
+        <v>136.04</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-30.71</v>
+        <v>-31.73</v>
       </c>
       <c r="K84" t="n">
-        <v>118.49</v>
+        <v>122.4</v>
       </c>
       <c r="L84" t="n">
-        <v>122.4</v>
+        <v>126.45</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>98.48</v>
+        <v>103.63</v>
       </c>
       <c r="K85" t="n">
-        <v>-41.69</v>
+        <v>-43.87</v>
       </c>
       <c r="L85" t="n">
-        <v>106.94</v>
+        <v>112.53</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>134.19</v>
+        <v>149.68</v>
       </c>
       <c r="K86" t="n">
-        <v>-144.12</v>
+        <v>-160.75</v>
       </c>
       <c r="L86" t="n">
-        <v>196.92</v>
+        <v>219.64</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>71.06999999999999</v>
+        <v>71.76000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-224.94</v>
+        <v>-227.14</v>
       </c>
       <c r="L87" t="n">
-        <v>235.9</v>
+        <v>238.2</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>293.48</v>
+        <v>310.84</v>
       </c>
       <c r="K88" t="n">
-        <v>223.66</v>
+        <v>236.89</v>
       </c>
       <c r="L88" t="n">
-        <v>369</v>
+        <v>390.82</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-10.xlsx
+++ b/output/2024-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-26.5</v>
+        <v>-27.51</v>
       </c>
       <c r="K14" t="n">
-        <v>44.05</v>
+        <v>45.72</v>
       </c>
       <c r="L14" t="n">
-        <v>51.41</v>
+        <v>53.36</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-48.8</v>
+        <v>-50.48</v>
       </c>
       <c r="K15" t="n">
-        <v>-20.23</v>
+        <v>-20.93</v>
       </c>
       <c r="L15" t="n">
-        <v>52.83</v>
+        <v>54.65</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>53.83</v>
+        <v>52.85</v>
       </c>
       <c r="K16" t="n">
-        <v>-47.98</v>
+        <v>-47.1</v>
       </c>
       <c r="L16" t="n">
-        <v>72.11</v>
+        <v>70.8</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-49.58</v>
+        <v>-53.1</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.01</v>
+        <v>-5.36</v>
       </c>
       <c r="L17" t="n">
-        <v>49.83</v>
+        <v>53.37</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-87.45</v>
+        <v>-85.02</v>
       </c>
       <c r="K18" t="n">
-        <v>-22.2</v>
+        <v>-21.59</v>
       </c>
       <c r="L18" t="n">
-        <v>90.23</v>
+        <v>87.72</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>-34.27</v>
+        <v>-37.17</v>
       </c>
       <c r="K19" t="n">
-        <v>30.38</v>
+        <v>32.96</v>
       </c>
       <c r="L19" t="n">
-        <v>45.8</v>
+        <v>49.68</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-76.26000000000001</v>
+        <v>-81.55</v>
       </c>
       <c r="K20" t="n">
-        <v>-15.88</v>
+        <v>-16.98</v>
       </c>
       <c r="L20" t="n">
-        <v>77.89</v>
+        <v>83.3</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>35.33</v>
+        <v>37.1</v>
       </c>
       <c r="K21" t="n">
-        <v>86.51000000000001</v>
+        <v>90.84</v>
       </c>
       <c r="L21" t="n">
-        <v>93.44</v>
+        <v>98.12</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>8.289999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="K22" t="n">
-        <v>74.45999999999999</v>
+        <v>79.12</v>
       </c>
       <c r="L22" t="n">
-        <v>74.92</v>
+        <v>79.61</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-119.94</v>
+        <v>-120.56</v>
       </c>
       <c r="K23" t="n">
-        <v>69.17</v>
+        <v>69.53</v>
       </c>
       <c r="L23" t="n">
-        <v>138.46</v>
+        <v>139.17</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>20.83</v>
+        <v>20.39</v>
       </c>
       <c r="K24" t="n">
-        <v>179.09</v>
+        <v>175.31</v>
       </c>
       <c r="L24" t="n">
-        <v>180.3</v>
+        <v>176.49</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-101.14</v>
+        <v>-104.74</v>
       </c>
       <c r="K25" t="n">
-        <v>61.68</v>
+        <v>63.87</v>
       </c>
       <c r="L25" t="n">
-        <v>118.46</v>
+        <v>122.68</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-13.98</v>
+        <v>-14.28</v>
       </c>
       <c r="K26" t="n">
-        <v>-173.23</v>
+        <v>-176.91</v>
       </c>
       <c r="L26" t="n">
-        <v>173.79</v>
+        <v>177.48</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>177.21</v>
+        <v>184.68</v>
       </c>
       <c r="K27" t="n">
-        <v>-76.43000000000001</v>
+        <v>-79.64</v>
       </c>
       <c r="L27" t="n">
-        <v>192.99</v>
+        <v>201.12</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>171.11</v>
+        <v>172.1</v>
       </c>
       <c r="K28" t="n">
-        <v>-75.8</v>
+        <v>-76.23999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>187.15</v>
+        <v>188.23</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-68.73</v>
+        <v>-66.7</v>
       </c>
       <c r="K29" t="n">
-        <v>-36.92</v>
+        <v>-35.83</v>
       </c>
       <c r="L29" t="n">
-        <v>78.01000000000001</v>
+        <v>75.70999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-43.83</v>
+        <v>-45.77</v>
       </c>
       <c r="K30" t="n">
-        <v>-23.59</v>
+        <v>-24.63</v>
       </c>
       <c r="L30" t="n">
-        <v>49.77</v>
+        <v>51.98</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>61.24</v>
+        <v>61.5</v>
       </c>
       <c r="K31" t="n">
-        <v>17.27</v>
+        <v>17.34</v>
       </c>
       <c r="L31" t="n">
-        <v>63.63</v>
+        <v>63.9</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>12.89</v>
+        <v>14.16</v>
       </c>
       <c r="K32" t="n">
-        <v>37.76</v>
+        <v>41.49</v>
       </c>
       <c r="L32" t="n">
-        <v>39.9</v>
+        <v>43.84</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>43.41</v>
+        <v>44.27</v>
       </c>
       <c r="K33" t="n">
-        <v>-55.23</v>
+        <v>-56.33</v>
       </c>
       <c r="L33" t="n">
-        <v>70.25</v>
+        <v>71.64</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>31.83</v>
+        <v>32.77</v>
       </c>
       <c r="K34" t="n">
-        <v>50.21</v>
+        <v>51.69</v>
       </c>
       <c r="L34" t="n">
-        <v>59.45</v>
+        <v>61.2</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.67</v>
+        <v>-4.79</v>
       </c>
       <c r="K35" t="n">
-        <v>83.18000000000001</v>
+        <v>85.3</v>
       </c>
       <c r="L35" t="n">
-        <v>83.31999999999999</v>
+        <v>85.43000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.75</v>
+        <v>-3.8</v>
       </c>
       <c r="K36" t="n">
-        <v>-93.61</v>
+        <v>-94.73999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>93.69</v>
+        <v>94.81999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-78.18000000000001</v>
+        <v>-80.59</v>
       </c>
       <c r="K37" t="n">
-        <v>32.39</v>
+        <v>33.39</v>
       </c>
       <c r="L37" t="n">
-        <v>84.63</v>
+        <v>87.23</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>200.75</v>
+        <v>192.51</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.84</v>
+        <v>-4.64</v>
       </c>
       <c r="L38" t="n">
-        <v>200.81</v>
+        <v>192.57</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>79.45999999999999</v>
+        <v>85.23</v>
       </c>
       <c r="K39" t="n">
-        <v>58.3</v>
+        <v>62.54</v>
       </c>
       <c r="L39" t="n">
-        <v>98.56</v>
+        <v>105.72</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>11.21</v>
+        <v>10.86</v>
       </c>
       <c r="K40" t="n">
-        <v>-193.91</v>
+        <v>-187.84</v>
       </c>
       <c r="L40" t="n">
-        <v>194.24</v>
+        <v>188.16</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-141.72</v>
+        <v>-148.6</v>
       </c>
       <c r="K41" t="n">
-        <v>-81.09</v>
+        <v>-85.03</v>
       </c>
       <c r="L41" t="n">
-        <v>163.29</v>
+        <v>171.21</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>195.65</v>
+        <v>194.33</v>
       </c>
       <c r="K42" t="n">
-        <v>-82.08</v>
+        <v>-81.52</v>
       </c>
       <c r="L42" t="n">
-        <v>212.17</v>
+        <v>210.74</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>203.45</v>
+        <v>196.72</v>
       </c>
       <c r="K43" t="n">
-        <v>217.82</v>
+        <v>210.61</v>
       </c>
       <c r="L43" t="n">
-        <v>298.06</v>
+        <v>288.2</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-40.93</v>
+        <v>-39.29</v>
       </c>
       <c r="K44" t="n">
-        <v>-66.68000000000001</v>
+        <v>-64</v>
       </c>
       <c r="L44" t="n">
-        <v>78.23999999999999</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-5.91</v>
+        <v>-6.4</v>
       </c>
       <c r="K45" t="n">
-        <v>-43.63</v>
+        <v>-47.25</v>
       </c>
       <c r="L45" t="n">
-        <v>44.03</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>28.79</v>
+        <v>31.52</v>
       </c>
       <c r="K46" t="n">
-        <v>-9.23</v>
+        <v>-10.11</v>
       </c>
       <c r="L46" t="n">
-        <v>30.23</v>
+        <v>33.1</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>37.88</v>
+        <v>37.5</v>
       </c>
       <c r="K47" t="n">
-        <v>68.27</v>
+        <v>67.58</v>
       </c>
       <c r="L47" t="n">
-        <v>78.06999999999999</v>
+        <v>77.28</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>25.68</v>
+        <v>24.14</v>
       </c>
       <c r="K48" t="n">
-        <v>-119.85</v>
+        <v>-112.65</v>
       </c>
       <c r="L48" t="n">
-        <v>122.57</v>
+        <v>115.21</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.57</v>
+        <v>-12.33</v>
       </c>
       <c r="K49" t="n">
-        <v>-79.09</v>
+        <v>-77.61</v>
       </c>
       <c r="L49" t="n">
-        <v>80.09</v>
+        <v>78.59</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>13.7</v>
+        <v>14.19</v>
       </c>
       <c r="K50" t="n">
-        <v>-94.64</v>
+        <v>-98.06</v>
       </c>
       <c r="L50" t="n">
-        <v>95.63</v>
+        <v>99.08</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-76.05</v>
+        <v>-78.58</v>
       </c>
       <c r="K51" t="n">
-        <v>-63.01</v>
+        <v>-65.11</v>
       </c>
       <c r="L51" t="n">
-        <v>98.76000000000001</v>
+        <v>102.05</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-36.15</v>
+        <v>-39.34</v>
       </c>
       <c r="K52" t="n">
-        <v>64.12</v>
+        <v>69.78</v>
       </c>
       <c r="L52" t="n">
-        <v>73.61</v>
+        <v>80.09999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>6.61</v>
+        <v>6.76</v>
       </c>
       <c r="K53" t="n">
-        <v>-129.52</v>
+        <v>-132.46</v>
       </c>
       <c r="L53" t="n">
-        <v>129.69</v>
+        <v>132.64</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>80.59</v>
+        <v>83.38</v>
       </c>
       <c r="K54" t="n">
-        <v>97.59999999999999</v>
+        <v>100.97</v>
       </c>
       <c r="L54" t="n">
-        <v>126.57</v>
+        <v>130.95</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-108.15</v>
+        <v>-108.23</v>
       </c>
       <c r="K55" t="n">
-        <v>95.26000000000001</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>144.12</v>
+        <v>144.22</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>94.3</v>
+        <v>97.56</v>
       </c>
       <c r="K56" t="n">
-        <v>-151.21</v>
+        <v>-156.44</v>
       </c>
       <c r="L56" t="n">
-        <v>178.21</v>
+        <v>184.37</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-258.23</v>
+        <v>-251.24</v>
       </c>
       <c r="K57" t="n">
-        <v>-182.37</v>
+        <v>-177.44</v>
       </c>
       <c r="L57" t="n">
-        <v>316.14</v>
+        <v>307.58</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-130.63</v>
+        <v>-140.05</v>
       </c>
       <c r="K58" t="n">
-        <v>93.34</v>
+        <v>100.07</v>
       </c>
       <c r="L58" t="n">
-        <v>160.56</v>
+        <v>172.13</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>65.16</v>
+        <v>64.8</v>
       </c>
       <c r="K59" t="n">
-        <v>26.86</v>
+        <v>26.71</v>
       </c>
       <c r="L59" t="n">
-        <v>70.48</v>
+        <v>70.09</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.640000000000001</v>
+        <v>-9.48</v>
       </c>
       <c r="K60" t="n">
-        <v>70.88</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>71.53</v>
+        <v>70.34999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>76.19</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="L61" t="n">
-        <v>76.2</v>
+        <v>74.73999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>32.17</v>
+        <v>30.62</v>
       </c>
       <c r="K62" t="n">
-        <v>-96.73999999999999</v>
+        <v>-92.08</v>
       </c>
       <c r="L62" t="n">
-        <v>101.95</v>
+        <v>97.04000000000001</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-62.02</v>
+        <v>-61.15</v>
       </c>
       <c r="K63" t="n">
-        <v>45.1</v>
+        <v>44.47</v>
       </c>
       <c r="L63" t="n">
-        <v>76.69</v>
+        <v>75.61</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>66.11</v>
+        <v>62.67</v>
       </c>
       <c r="K64" t="n">
-        <v>-92.29000000000001</v>
+        <v>-87.5</v>
       </c>
       <c r="L64" t="n">
-        <v>113.52</v>
+        <v>107.63</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>72.28</v>
+        <v>73.25</v>
       </c>
       <c r="K65" t="n">
-        <v>-86.12</v>
+        <v>-87.27</v>
       </c>
       <c r="L65" t="n">
-        <v>112.43</v>
+        <v>113.94</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-97.01000000000001</v>
+        <v>-98.69</v>
       </c>
       <c r="K66" t="n">
-        <v>17.92</v>
+        <v>18.23</v>
       </c>
       <c r="L66" t="n">
-        <v>98.65000000000001</v>
+        <v>100.36</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>20.01</v>
+        <v>19.74</v>
       </c>
       <c r="K67" t="n">
-        <v>-116.51</v>
+        <v>-114.95</v>
       </c>
       <c r="L67" t="n">
-        <v>118.21</v>
+        <v>116.63</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>115.89</v>
+        <v>114.95</v>
       </c>
       <c r="K68" t="n">
-        <v>-92.88</v>
+        <v>-92.12</v>
       </c>
       <c r="L68" t="n">
-        <v>148.52</v>
+        <v>147.31</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>167.44</v>
+        <v>162.65</v>
       </c>
       <c r="K69" t="n">
-        <v>78.42</v>
+        <v>76.18000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>184.9</v>
+        <v>179.6</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>127.32</v>
+        <v>131.05</v>
       </c>
       <c r="K70" t="n">
-        <v>40.28</v>
+        <v>41.46</v>
       </c>
       <c r="L70" t="n">
-        <v>133.54</v>
+        <v>137.45</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-70.09</v>
+        <v>-68.12</v>
       </c>
       <c r="K71" t="n">
-        <v>-324.04</v>
+        <v>-314.94</v>
       </c>
       <c r="L71" t="n">
-        <v>331.54</v>
+        <v>322.22</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-46.43</v>
+        <v>-49.08</v>
       </c>
       <c r="K72" t="n">
-        <v>182.07</v>
+        <v>192.46</v>
       </c>
       <c r="L72" t="n">
-        <v>187.9</v>
+        <v>198.62</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>255.94</v>
+        <v>249.58</v>
       </c>
       <c r="K73" t="n">
-        <v>30.76</v>
+        <v>30</v>
       </c>
       <c r="L73" t="n">
-        <v>257.78</v>
+        <v>251.38</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>34.76</v>
+        <v>35.43</v>
       </c>
       <c r="K74" t="n">
-        <v>47.17</v>
+        <v>48.08</v>
       </c>
       <c r="L74" t="n">
-        <v>58.6</v>
+        <v>59.73</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-92.52</v>
+        <v>-86.8</v>
       </c>
       <c r="K75" t="n">
-        <v>37.98</v>
+        <v>35.63</v>
       </c>
       <c r="L75" t="n">
-        <v>100.01</v>
+        <v>93.83</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>29.59</v>
+        <v>28.13</v>
       </c>
       <c r="K76" t="n">
-        <v>86.87</v>
+        <v>82.58</v>
       </c>
       <c r="L76" t="n">
-        <v>91.78</v>
+        <v>87.23999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-81.14</v>
+        <v>-80.23</v>
       </c>
       <c r="K77" t="n">
-        <v>25.61</v>
+        <v>25.32</v>
       </c>
       <c r="L77" t="n">
-        <v>85.09</v>
+        <v>84.13</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>45.78</v>
+        <v>47.35</v>
       </c>
       <c r="K78" t="n">
-        <v>48.8</v>
+        <v>50.46</v>
       </c>
       <c r="L78" t="n">
-        <v>66.91</v>
+        <v>69.2</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-54.76</v>
+        <v>-56.03</v>
       </c>
       <c r="K79" t="n">
-        <v>44.53</v>
+        <v>45.56</v>
       </c>
       <c r="L79" t="n">
-        <v>70.58</v>
+        <v>72.20999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>47.2</v>
+        <v>49.6</v>
       </c>
       <c r="K80" t="n">
-        <v>-83.20999999999999</v>
+        <v>-87.44</v>
       </c>
       <c r="L80" t="n">
-        <v>95.67</v>
+        <v>100.53</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>85.76000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="K81" t="n">
-        <v>-8.31</v>
+        <v>-8.65</v>
       </c>
       <c r="L81" t="n">
-        <v>86.16</v>
+        <v>89.63</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-97.7</v>
+        <v>-100.85</v>
       </c>
       <c r="K82" t="n">
-        <v>-38.85</v>
+        <v>-40.09</v>
       </c>
       <c r="L82" t="n">
-        <v>105.14</v>
+        <v>108.52</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>126.01</v>
+        <v>131.52</v>
       </c>
       <c r="K83" t="n">
-        <v>51.25</v>
+        <v>53.49</v>
       </c>
       <c r="L83" t="n">
-        <v>136.04</v>
+        <v>141.98</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-31.73</v>
+        <v>-32.64</v>
       </c>
       <c r="K84" t="n">
-        <v>122.4</v>
+        <v>125.91</v>
       </c>
       <c r="L84" t="n">
-        <v>126.45</v>
+        <v>130.07</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>103.63</v>
+        <v>108.77</v>
       </c>
       <c r="K85" t="n">
-        <v>-43.87</v>
+        <v>-46.05</v>
       </c>
       <c r="L85" t="n">
-        <v>112.53</v>
+        <v>118.11</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>149.68</v>
+        <v>155.65</v>
       </c>
       <c r="K86" t="n">
-        <v>-160.75</v>
+        <v>-167.16</v>
       </c>
       <c r="L86" t="n">
-        <v>219.64</v>
+        <v>228.4</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>71.76000000000001</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="K87" t="n">
-        <v>-227.14</v>
+        <v>-223.19</v>
       </c>
       <c r="L87" t="n">
-        <v>238.2</v>
+        <v>234.06</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>310.84</v>
+        <v>295.34</v>
       </c>
       <c r="K88" t="n">
-        <v>236.89</v>
+        <v>225.08</v>
       </c>
       <c r="L88" t="n">
-        <v>390.82</v>
+        <v>371.33</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-10.xlsx
+++ b/output/2024-09-10.xlsx
@@ -628,25 +628,25 @@
         <v>3.56</v>
       </c>
       <c r="F14" t="n">
-        <v>10.54</v>
+        <v>7.01</v>
       </c>
       <c r="G14" t="n">
-        <v>118.6</v>
+        <v>130.5</v>
       </c>
       <c r="H14" t="n">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="I14" t="n">
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-27.51</v>
+        <v>-29.18</v>
       </c>
       <c r="K14" t="n">
-        <v>45.72</v>
+        <v>48.68</v>
       </c>
       <c r="L14" t="n">
-        <v>53.36</v>
+        <v>56.75</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>3.51</v>
       </c>
       <c r="F15" t="n">
-        <v>10.48</v>
+        <v>8.16</v>
       </c>
       <c r="G15" t="n">
-        <v>119.5</v>
+        <v>129.4</v>
       </c>
       <c r="H15" t="n">
-        <v>26.6</v>
+        <v>19.2</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-50.48</v>
+        <v>-53.43</v>
       </c>
       <c r="K15" t="n">
-        <v>-20.93</v>
+        <v>-23.7</v>
       </c>
       <c r="L15" t="n">
-        <v>54.65</v>
+        <v>58.46</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>3.06</v>
       </c>
       <c r="F16" t="n">
-        <v>10.36</v>
+        <v>5.35</v>
       </c>
       <c r="G16" t="n">
-        <v>136.3</v>
+        <v>127</v>
       </c>
       <c r="H16" t="n">
-        <v>17.8</v>
+        <v>27.6</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>52.85</v>
+        <v>49.44</v>
       </c>
       <c r="K16" t="n">
-        <v>-47.1</v>
+        <v>-43.78</v>
       </c>
       <c r="L16" t="n">
-        <v>70.8</v>
+        <v>66.04000000000001</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>3.35</v>
       </c>
       <c r="F17" t="n">
-        <v>10.07</v>
+        <v>10.29</v>
       </c>
       <c r="G17" t="n">
-        <v>114.3</v>
+        <v>121.2</v>
       </c>
       <c r="H17" t="n">
-        <v>30.8</v>
+        <v>16.6</v>
       </c>
       <c r="I17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>-53.1</v>
+        <v>-60.12</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.36</v>
+        <v>-10.11</v>
       </c>
       <c r="L17" t="n">
-        <v>53.37</v>
+        <v>60.96</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>3.57</v>
       </c>
       <c r="F18" t="n">
-        <v>9.949999999999999</v>
+        <v>7.27</v>
       </c>
       <c r="G18" t="n">
-        <v>129.2</v>
+        <v>118.8</v>
       </c>
       <c r="H18" t="n">
-        <v>19.5</v>
+        <v>24.1</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-85.02</v>
+        <v>-90.98</v>
       </c>
       <c r="K18" t="n">
-        <v>-21.59</v>
+        <v>-24.55</v>
       </c>
       <c r="L18" t="n">
-        <v>87.72</v>
+        <v>94.23</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>3.43</v>
       </c>
       <c r="F19" t="n">
-        <v>9.550000000000001</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>127.5</v>
+        <v>110.7</v>
       </c>
       <c r="H19" t="n">
-        <v>23.8</v>
+        <v>23.2</v>
       </c>
       <c r="I19" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-37.17</v>
+        <v>-43.95</v>
       </c>
       <c r="K19" t="n">
-        <v>32.96</v>
+        <v>45.75</v>
       </c>
       <c r="L19" t="n">
-        <v>49.68</v>
+        <v>63.44</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>3.56</v>
       </c>
       <c r="F20" t="n">
-        <v>10.71</v>
+        <v>8.43</v>
       </c>
       <c r="G20" t="n">
-        <v>125.1</v>
+        <v>133.9</v>
       </c>
       <c r="H20" t="n">
-        <v>22.3</v>
+        <v>22</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-81.55</v>
+        <v>-83.97</v>
       </c>
       <c r="K20" t="n">
-        <v>-16.98</v>
+        <v>-42.85</v>
       </c>
       <c r="L20" t="n">
-        <v>83.3</v>
+        <v>94.27</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>4.28</v>
       </c>
       <c r="F21" t="n">
-        <v>10.14</v>
+        <v>10.57</v>
       </c>
       <c r="G21" t="n">
-        <v>118.4</v>
+        <v>122.6</v>
       </c>
       <c r="H21" t="n">
+        <v>18.7</v>
+      </c>
+      <c r="I21" t="n">
         <v>28</v>
       </c>
-      <c r="I21" t="n">
-        <v>24</v>
-      </c>
       <c r="J21" t="n">
-        <v>37.1</v>
+        <v>59.42</v>
       </c>
       <c r="K21" t="n">
-        <v>90.84</v>
+        <v>80.51000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>98.12</v>
+        <v>100.06</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>2.81</v>
       </c>
       <c r="F22" t="n">
-        <v>9.92</v>
+        <v>7.93</v>
       </c>
       <c r="G22" t="n">
-        <v>132.1</v>
+        <v>118.1</v>
       </c>
       <c r="H22" t="n">
-        <v>25.7</v>
+        <v>25.5</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>8.81</v>
+        <v>27.6</v>
       </c>
       <c r="K22" t="n">
-        <v>79.12</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>79.61</v>
+        <v>91.18000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>3.64</v>
       </c>
       <c r="F23" t="n">
-        <v>10.9</v>
+        <v>10.82</v>
       </c>
       <c r="G23" t="n">
-        <v>130</v>
+        <v>137.7</v>
       </c>
       <c r="H23" t="n">
-        <v>22.5</v>
+        <v>24.4</v>
       </c>
       <c r="I23" t="n">
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-120.56</v>
+        <v>-136.28</v>
       </c>
       <c r="K23" t="n">
-        <v>69.53</v>
+        <v>61.93</v>
       </c>
       <c r="L23" t="n">
-        <v>139.17</v>
+        <v>149.69</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>4.17</v>
       </c>
       <c r="F24" t="n">
-        <v>10.15</v>
+        <v>11.54</v>
       </c>
       <c r="G24" t="n">
-        <v>108.9</v>
+        <v>122.6</v>
       </c>
       <c r="H24" t="n">
-        <v>26.2</v>
+        <v>13.9</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>20.39</v>
+        <v>48.61</v>
       </c>
       <c r="K24" t="n">
-        <v>175.31</v>
+        <v>187.48</v>
       </c>
       <c r="L24" t="n">
-        <v>176.49</v>
+        <v>193.68</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>3.34</v>
       </c>
       <c r="F25" t="n">
-        <v>10.77</v>
+        <v>7.75</v>
       </c>
       <c r="G25" t="n">
-        <v>134.5</v>
+        <v>135.1</v>
       </c>
       <c r="H25" t="n">
-        <v>20.2</v>
+        <v>26.7</v>
       </c>
       <c r="I25" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>-104.74</v>
+        <v>-107</v>
       </c>
       <c r="K25" t="n">
-        <v>63.87</v>
+        <v>52.18</v>
       </c>
       <c r="L25" t="n">
-        <v>122.68</v>
+        <v>119.04</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>3.38</v>
       </c>
       <c r="F26" t="n">
-        <v>10.82</v>
+        <v>8.34</v>
       </c>
       <c r="G26" t="n">
-        <v>121.1</v>
+        <v>136.1</v>
       </c>
       <c r="H26" t="n">
-        <v>22.9</v>
+        <v>20</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.28</v>
+        <v>9.75</v>
       </c>
       <c r="K26" t="n">
-        <v>-176.91</v>
+        <v>-200.18</v>
       </c>
       <c r="L26" t="n">
-        <v>177.48</v>
+        <v>200.42</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>4.08</v>
       </c>
       <c r="F27" t="n">
-        <v>10.41</v>
+        <v>11.96</v>
       </c>
       <c r="G27" t="n">
-        <v>124.1</v>
+        <v>127.9</v>
       </c>
       <c r="H27" t="n">
-        <v>27.6</v>
+        <v>21.5</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>184.68</v>
+        <v>203.87</v>
       </c>
       <c r="K27" t="n">
-        <v>-79.64</v>
+        <v>-104.18</v>
       </c>
       <c r="L27" t="n">
-        <v>201.12</v>
+        <v>228.94</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>3.6</v>
       </c>
       <c r="F28" t="n">
-        <v>10.66</v>
+        <v>6.58</v>
       </c>
       <c r="G28" t="n">
-        <v>127.1</v>
+        <v>132.9</v>
       </c>
       <c r="H28" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I28" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>172.1</v>
+        <v>209.33</v>
       </c>
       <c r="K28" t="n">
-        <v>-76.23999999999999</v>
+        <v>-109.25</v>
       </c>
       <c r="L28" t="n">
-        <v>188.23</v>
+        <v>236.12</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>3.64</v>
       </c>
       <c r="F29" t="n">
-        <v>10.17</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G29" t="n">
-        <v>129.9</v>
+        <v>123</v>
       </c>
       <c r="H29" t="n">
-        <v>31.2</v>
+        <v>24.4</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-66.7</v>
+        <v>-67.09</v>
       </c>
       <c r="K29" t="n">
-        <v>-35.83</v>
+        <v>-36.83</v>
       </c>
       <c r="L29" t="n">
-        <v>75.70999999999999</v>
+        <v>76.54000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>4.05</v>
       </c>
       <c r="F30" t="n">
-        <v>10.66</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>120.9</v>
+        <v>132.9</v>
       </c>
       <c r="H30" t="n">
-        <v>19.5</v>
+        <v>19.9</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-45.77</v>
+        <v>-51.23</v>
       </c>
       <c r="K30" t="n">
-        <v>-24.63</v>
+        <v>-29.9</v>
       </c>
       <c r="L30" t="n">
-        <v>51.98</v>
+        <v>59.32</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>4.54</v>
       </c>
       <c r="F31" t="n">
-        <v>10.14</v>
+        <v>11.96</v>
       </c>
       <c r="G31" t="n">
-        <v>126.5</v>
+        <v>122.5</v>
       </c>
       <c r="H31" t="n">
-        <v>16.3</v>
+        <v>22.7</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>61.5</v>
+        <v>63.28</v>
       </c>
       <c r="K31" t="n">
-        <v>17.34</v>
+        <v>16.83</v>
       </c>
       <c r="L31" t="n">
-        <v>63.9</v>
+        <v>65.48</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>3.53</v>
       </c>
       <c r="F32" t="n">
-        <v>10.46</v>
+        <v>10</v>
       </c>
       <c r="G32" t="n">
-        <v>133.5</v>
+        <v>128.8</v>
       </c>
       <c r="H32" t="n">
-        <v>25.8</v>
+        <v>26.2</v>
       </c>
       <c r="I32" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>14.16</v>
+        <v>23.82</v>
       </c>
       <c r="K32" t="n">
-        <v>41.49</v>
+        <v>42.85</v>
       </c>
       <c r="L32" t="n">
-        <v>43.84</v>
+        <v>49.02</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>4.07</v>
       </c>
       <c r="F33" t="n">
-        <v>10.09</v>
+        <v>10.45</v>
       </c>
       <c r="G33" t="n">
-        <v>127</v>
+        <v>121.5</v>
       </c>
       <c r="H33" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="I33" t="n">
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>44.27</v>
+        <v>51.86</v>
       </c>
       <c r="K33" t="n">
-        <v>-56.33</v>
+        <v>-62.99</v>
       </c>
       <c r="L33" t="n">
-        <v>71.64</v>
+        <v>81.59999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>4.11</v>
       </c>
       <c r="F34" t="n">
-        <v>10.74</v>
+        <v>11.82</v>
       </c>
       <c r="G34" t="n">
-        <v>132.8</v>
+        <v>134.4</v>
       </c>
       <c r="H34" t="n">
-        <v>26.6</v>
+        <v>25.8</v>
       </c>
       <c r="I34" t="n">
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>32.77</v>
+        <v>41.43</v>
       </c>
       <c r="K34" t="n">
-        <v>51.69</v>
+        <v>57.21</v>
       </c>
       <c r="L34" t="n">
-        <v>61.2</v>
+        <v>70.64</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>3.35</v>
       </c>
       <c r="F35" t="n">
-        <v>10.64</v>
+        <v>11.96</v>
       </c>
       <c r="G35" t="n">
-        <v>134.1</v>
+        <v>132.4</v>
       </c>
       <c r="H35" t="n">
-        <v>27.1</v>
+        <v>26.5</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.79</v>
+        <v>5.07</v>
       </c>
       <c r="K35" t="n">
-        <v>85.3</v>
+        <v>99.52</v>
       </c>
       <c r="L35" t="n">
-        <v>85.43000000000001</v>
+        <v>99.64</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>3.54</v>
       </c>
       <c r="F36" t="n">
-        <v>10.05</v>
+        <v>8.49</v>
       </c>
       <c r="G36" t="n">
-        <v>133</v>
+        <v>120.8</v>
       </c>
       <c r="H36" t="n">
-        <v>21.7</v>
+        <v>25.9</v>
       </c>
       <c r="I36" t="n">
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.8</v>
+        <v>7.61</v>
       </c>
       <c r="K36" t="n">
-        <v>-94.73999999999999</v>
+        <v>-106.27</v>
       </c>
       <c r="L36" t="n">
-        <v>94.81999999999999</v>
+        <v>106.54</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>3.06</v>
       </c>
       <c r="F37" t="n">
-        <v>10.64</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>131.7</v>
+        <v>132.6</v>
       </c>
       <c r="H37" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-80.59</v>
+        <v>-85.34</v>
       </c>
       <c r="K37" t="n">
-        <v>33.39</v>
+        <v>30.1</v>
       </c>
       <c r="L37" t="n">
-        <v>87.23</v>
+        <v>90.48999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>3.83</v>
       </c>
       <c r="F38" t="n">
-        <v>10.21</v>
+        <v>10.51</v>
       </c>
       <c r="G38" t="n">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H38" t="n">
-        <v>24.8</v>
+        <v>28.4</v>
       </c>
       <c r="I38" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>192.51</v>
+        <v>205.35</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.64</v>
+        <v>-14.72</v>
       </c>
       <c r="L38" t="n">
-        <v>192.57</v>
+        <v>205.88</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>4.07</v>
       </c>
       <c r="F39" t="n">
-        <v>10.2</v>
+        <v>10.47</v>
       </c>
       <c r="G39" t="n">
-        <v>136.7</v>
+        <v>123.7</v>
       </c>
       <c r="H39" t="n">
-        <v>26.9</v>
+        <v>27.8</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>85.23</v>
+        <v>135.61</v>
       </c>
       <c r="K39" t="n">
-        <v>62.54</v>
+        <v>37.34</v>
       </c>
       <c r="L39" t="n">
-        <v>105.72</v>
+        <v>140.66</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>4.18</v>
       </c>
       <c r="F40" t="n">
-        <v>10.84</v>
+        <v>10.63</v>
       </c>
       <c r="G40" t="n">
-        <v>134.4</v>
+        <v>136.6</v>
       </c>
       <c r="H40" t="n">
-        <v>22.7</v>
+        <v>26.6</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>10.86</v>
+        <v>26.01</v>
       </c>
       <c r="K40" t="n">
-        <v>-187.84</v>
+        <v>-196.16</v>
       </c>
       <c r="L40" t="n">
-        <v>188.16</v>
+        <v>197.87</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>4.13</v>
       </c>
       <c r="F41" t="n">
-        <v>10.25</v>
+        <v>10.35</v>
       </c>
       <c r="G41" t="n">
-        <v>125.9</v>
+        <v>124.6</v>
       </c>
       <c r="H41" t="n">
-        <v>23.8</v>
+        <v>22.4</v>
       </c>
       <c r="I41" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-148.6</v>
+        <v>-146.64</v>
       </c>
       <c r="K41" t="n">
-        <v>-85.03</v>
+        <v>-149.04</v>
       </c>
       <c r="L41" t="n">
-        <v>171.21</v>
+        <v>209.08</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>3.64</v>
       </c>
       <c r="F42" t="n">
-        <v>10.41</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>124.3</v>
+        <v>128</v>
       </c>
       <c r="H42" t="n">
-        <v>24.3</v>
+        <v>21.6</v>
       </c>
       <c r="I42" t="n">
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>194.33</v>
+        <v>224.34</v>
       </c>
       <c r="K42" t="n">
-        <v>-81.52</v>
+        <v>-105.67</v>
       </c>
       <c r="L42" t="n">
-        <v>210.74</v>
+        <v>247.99</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>4.15</v>
       </c>
       <c r="F43" t="n">
-        <v>10.99</v>
+        <v>11.96</v>
       </c>
       <c r="G43" t="n">
-        <v>136.4</v>
+        <v>139.5</v>
       </c>
       <c r="H43" t="n">
-        <v>27.4</v>
+        <v>27.6</v>
       </c>
       <c r="I43" t="n">
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>196.72</v>
+        <v>238.8</v>
       </c>
       <c r="K43" t="n">
-        <v>210.61</v>
+        <v>210.47</v>
       </c>
       <c r="L43" t="n">
-        <v>288.2</v>
+        <v>318.31</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>3.62</v>
       </c>
       <c r="F44" t="n">
-        <v>9.800000000000001</v>
+        <v>7.16</v>
       </c>
       <c r="G44" t="n">
-        <v>136.2</v>
+        <v>115.6</v>
       </c>
       <c r="H44" t="n">
-        <v>17.3</v>
+        <v>27.5</v>
       </c>
       <c r="I44" t="n">
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-39.29</v>
+        <v>-39.94</v>
       </c>
       <c r="K44" t="n">
-        <v>-64</v>
+        <v>-66.55</v>
       </c>
       <c r="L44" t="n">
-        <v>75.09999999999999</v>
+        <v>77.62</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>4.08</v>
       </c>
       <c r="F45" t="n">
-        <v>9.65</v>
+        <v>8.07</v>
       </c>
       <c r="G45" t="n">
-        <v>127.8</v>
+        <v>112.7</v>
       </c>
       <c r="H45" t="n">
-        <v>23.1</v>
+        <v>23.4</v>
       </c>
       <c r="I45" t="n">
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.4</v>
+        <v>-3.64</v>
       </c>
       <c r="K45" t="n">
-        <v>-47.25</v>
+        <v>-52.31</v>
       </c>
       <c r="L45" t="n">
-        <v>47.68</v>
+        <v>52.43</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>3.89</v>
       </c>
       <c r="F46" t="n">
-        <v>9.869999999999999</v>
+        <v>11.96</v>
       </c>
       <c r="G46" t="n">
-        <v>125.2</v>
+        <v>117.1</v>
       </c>
       <c r="H46" t="n">
-        <v>31.9</v>
+        <v>22</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>31.52</v>
+        <v>46.29</v>
       </c>
       <c r="K46" t="n">
-        <v>-10.11</v>
+        <v>-14.74</v>
       </c>
       <c r="L46" t="n">
-        <v>33.1</v>
+        <v>48.58</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>4.22</v>
       </c>
       <c r="F47" t="n">
-        <v>10.19</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>140</v>
+        <v>123.5</v>
       </c>
       <c r="H47" t="n">
-        <v>21.3</v>
+        <v>29.5</v>
       </c>
       <c r="I47" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>37.5</v>
+        <v>41.82</v>
       </c>
       <c r="K47" t="n">
-        <v>67.58</v>
+        <v>68.56</v>
       </c>
       <c r="L47" t="n">
-        <v>77.28</v>
+        <v>80.31</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>4.66</v>
       </c>
       <c r="F48" t="n">
-        <v>11.27</v>
+        <v>9.58</v>
       </c>
       <c r="G48" t="n">
-        <v>122.1</v>
+        <v>145.2</v>
       </c>
       <c r="H48" t="n">
-        <v>16.3</v>
+        <v>20.5</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>24.14</v>
+        <v>23.66</v>
       </c>
       <c r="K48" t="n">
-        <v>-112.65</v>
+        <v>-109.66</v>
       </c>
       <c r="L48" t="n">
-        <v>115.21</v>
+        <v>112.18</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>3.58</v>
       </c>
       <c r="F49" t="n">
-        <v>9.6</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>121.2</v>
+        <v>111.7</v>
       </c>
       <c r="H49" t="n">
-        <v>21.8</v>
+        <v>20</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.33</v>
+        <v>-11.99</v>
       </c>
       <c r="K49" t="n">
-        <v>-77.61</v>
+        <v>-93.19</v>
       </c>
       <c r="L49" t="n">
-        <v>78.59</v>
+        <v>93.95999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>4.06</v>
       </c>
       <c r="F50" t="n">
-        <v>10.32</v>
+        <v>11.96</v>
       </c>
       <c r="G50" t="n">
-        <v>132.3</v>
+        <v>126.1</v>
       </c>
       <c r="H50" t="n">
-        <v>28.9</v>
+        <v>25.6</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>14.19</v>
+        <v>31.05</v>
       </c>
       <c r="K50" t="n">
-        <v>-98.06</v>
+        <v>-110.48</v>
       </c>
       <c r="L50" t="n">
-        <v>99.08</v>
+        <v>114.76</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>4.07</v>
       </c>
       <c r="F51" t="n">
-        <v>10.65</v>
+        <v>11.96</v>
       </c>
       <c r="G51" t="n">
-        <v>122.3</v>
+        <v>132.8</v>
       </c>
       <c r="H51" t="n">
-        <v>26.5</v>
+        <v>20.6</v>
       </c>
       <c r="I51" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-78.58</v>
+        <v>-72.73999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-65.11</v>
+        <v>-87.75</v>
       </c>
       <c r="L51" t="n">
-        <v>102.05</v>
+        <v>113.98</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>4.29</v>
       </c>
       <c r="F52" t="n">
-        <v>10.87</v>
+        <v>8.56</v>
       </c>
       <c r="G52" t="n">
-        <v>140.8</v>
+        <v>137</v>
       </c>
       <c r="H52" t="n">
-        <v>16.1</v>
+        <v>29.9</v>
       </c>
       <c r="I52" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-39.34</v>
+        <v>-17.62</v>
       </c>
       <c r="K52" t="n">
-        <v>69.78</v>
+        <v>57.32</v>
       </c>
       <c r="L52" t="n">
-        <v>80.09999999999999</v>
+        <v>59.97</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>3.87</v>
       </c>
       <c r="F53" t="n">
-        <v>10.43</v>
+        <v>8.01</v>
       </c>
       <c r="G53" t="n">
-        <v>146.4</v>
+        <v>128.2</v>
       </c>
       <c r="H53" t="n">
-        <v>16.3</v>
+        <v>32.6</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>6.76</v>
+        <v>41.47</v>
       </c>
       <c r="K53" t="n">
-        <v>-132.46</v>
+        <v>-157.22</v>
       </c>
       <c r="L53" t="n">
-        <v>132.64</v>
+        <v>162.6</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>3.99</v>
       </c>
       <c r="F54" t="n">
-        <v>10.59</v>
+        <v>10.35</v>
       </c>
       <c r="G54" t="n">
-        <v>121.7</v>
+        <v>131.5</v>
       </c>
       <c r="H54" t="n">
-        <v>22.5</v>
+        <v>20.3</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>83.38</v>
+        <v>130.01</v>
       </c>
       <c r="K54" t="n">
-        <v>100.97</v>
+        <v>82.61</v>
       </c>
       <c r="L54" t="n">
-        <v>130.95</v>
+        <v>154.04</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>4.04</v>
       </c>
       <c r="F55" t="n">
-        <v>10.62</v>
+        <v>11.96</v>
       </c>
       <c r="G55" t="n">
-        <v>112.7</v>
+        <v>132.1</v>
       </c>
       <c r="H55" t="n">
-        <v>19.5</v>
+        <v>15.8</v>
       </c>
       <c r="I55" t="n">
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-108.23</v>
+        <v>-119.17</v>
       </c>
       <c r="K55" t="n">
-        <v>95.31999999999999</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>144.22</v>
+        <v>151.91</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>4.06</v>
       </c>
       <c r="F56" t="n">
-        <v>10.37</v>
+        <v>11.96</v>
       </c>
       <c r="G56" t="n">
-        <v>114.8</v>
+        <v>127</v>
       </c>
       <c r="H56" t="n">
-        <v>31</v>
+        <v>16.9</v>
       </c>
       <c r="I56" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>97.56</v>
+        <v>133.37</v>
       </c>
       <c r="K56" t="n">
-        <v>-156.44</v>
+        <v>-199.3</v>
       </c>
       <c r="L56" t="n">
-        <v>184.37</v>
+        <v>239.81</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>4.39</v>
       </c>
       <c r="F57" t="n">
-        <v>10.5</v>
+        <v>11.96</v>
       </c>
       <c r="G57" t="n">
-        <v>114.9</v>
+        <v>129.6</v>
       </c>
       <c r="H57" t="n">
-        <v>21.6</v>
+        <v>16.9</v>
       </c>
       <c r="I57" t="n">
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-251.24</v>
+        <v>-253.75</v>
       </c>
       <c r="K57" t="n">
-        <v>-177.44</v>
+        <v>-220.05</v>
       </c>
       <c r="L57" t="n">
-        <v>307.58</v>
+        <v>335.87</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>3.88</v>
       </c>
       <c r="F58" t="n">
-        <v>10.59</v>
+        <v>11.54</v>
       </c>
       <c r="G58" t="n">
-        <v>124.9</v>
+        <v>131.5</v>
       </c>
       <c r="H58" t="n">
-        <v>26.1</v>
+        <v>21.9</v>
       </c>
       <c r="I58" t="n">
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-140.05</v>
+        <v>-167.67</v>
       </c>
       <c r="K58" t="n">
-        <v>100.07</v>
+        <v>85.91</v>
       </c>
       <c r="L58" t="n">
-        <v>172.13</v>
+        <v>188.4</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>4.22</v>
       </c>
       <c r="F59" t="n">
-        <v>10.74</v>
+        <v>11.36</v>
       </c>
       <c r="G59" t="n">
-        <v>127.6</v>
+        <v>134.6</v>
       </c>
       <c r="H59" t="n">
-        <v>24.7</v>
+        <v>23.3</v>
       </c>
       <c r="I59" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>64.8</v>
+        <v>71.51000000000001</v>
       </c>
       <c r="K59" t="n">
-        <v>26.71</v>
+        <v>28</v>
       </c>
       <c r="L59" t="n">
-        <v>70.09</v>
+        <v>76.79000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>4.75</v>
       </c>
       <c r="F60" t="n">
-        <v>9.76</v>
+        <v>11.96</v>
       </c>
       <c r="G60" t="n">
-        <v>122.3</v>
+        <v>115</v>
       </c>
       <c r="H60" t="n">
-        <v>30.3</v>
+        <v>20.6</v>
       </c>
       <c r="I60" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
         <v>-9.48</v>
       </c>
       <c r="K60" t="n">
-        <v>69.70999999999999</v>
+        <v>79.81</v>
       </c>
       <c r="L60" t="n">
-        <v>70.34999999999999</v>
+        <v>80.37</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>3.8</v>
       </c>
       <c r="F61" t="n">
-        <v>10.54</v>
+        <v>10.94</v>
       </c>
       <c r="G61" t="n">
-        <v>126.3</v>
+        <v>130.6</v>
       </c>
       <c r="H61" t="n">
-        <v>23.7</v>
+        <v>22.6</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>74.73999999999999</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>0.78</v>
+        <v>0.05</v>
       </c>
       <c r="L61" t="n">
-        <v>74.73999999999999</v>
+        <v>77.81999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>3.92</v>
       </c>
       <c r="F62" t="n">
-        <v>10.94</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="G62" t="n">
-        <v>142</v>
+        <v>138.5</v>
       </c>
       <c r="H62" t="n">
-        <v>19</v>
+        <v>30.5</v>
       </c>
       <c r="I62" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>30.62</v>
+        <v>36.73</v>
       </c>
       <c r="K62" t="n">
-        <v>-92.08</v>
+        <v>-107.01</v>
       </c>
       <c r="L62" t="n">
-        <v>97.04000000000001</v>
+        <v>113.13</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>3.85</v>
       </c>
       <c r="F63" t="n">
-        <v>10.65</v>
+        <v>11.02</v>
       </c>
       <c r="G63" t="n">
-        <v>125.2</v>
+        <v>132.6</v>
       </c>
       <c r="H63" t="n">
-        <v>20.6</v>
+        <v>22</v>
       </c>
       <c r="I63" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-61.15</v>
+        <v>-74.53</v>
       </c>
       <c r="K63" t="n">
-        <v>44.47</v>
+        <v>53.26</v>
       </c>
       <c r="L63" t="n">
-        <v>75.61</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>4.38</v>
       </c>
       <c r="F64" t="n">
-        <v>10.93</v>
+        <v>11.96</v>
       </c>
       <c r="G64" t="n">
-        <v>128.5</v>
+        <v>138.4</v>
       </c>
       <c r="H64" t="n">
-        <v>26.1</v>
+        <v>23.7</v>
       </c>
       <c r="I64" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>62.67</v>
+        <v>70.03</v>
       </c>
       <c r="K64" t="n">
-        <v>-87.5</v>
+        <v>-98.06</v>
       </c>
       <c r="L64" t="n">
-        <v>107.63</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>4.37</v>
       </c>
       <c r="F65" t="n">
-        <v>9.6</v>
+        <v>10.58</v>
       </c>
       <c r="G65" t="n">
-        <v>134.8</v>
+        <v>111.6</v>
       </c>
       <c r="H65" t="n">
-        <v>27.9</v>
+        <v>26.9</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>73.25</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-87.27</v>
+        <v>-87.55</v>
       </c>
       <c r="L65" t="n">
-        <v>113.94</v>
+        <v>125.49</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>3.95</v>
       </c>
       <c r="F66" t="n">
-        <v>10.72</v>
+        <v>10.26</v>
       </c>
       <c r="G66" t="n">
-        <v>126.3</v>
+        <v>134.1</v>
       </c>
       <c r="H66" t="n">
-        <v>21.9</v>
+        <v>22.6</v>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-98.69</v>
+        <v>-103.91</v>
       </c>
       <c r="K66" t="n">
-        <v>18.23</v>
+        <v>8.18</v>
       </c>
       <c r="L66" t="n">
-        <v>100.36</v>
+        <v>104.23</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>4.15</v>
       </c>
       <c r="F67" t="n">
-        <v>10.62</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G67" t="n">
-        <v>131.3</v>
+        <v>132.2</v>
       </c>
       <c r="H67" t="n">
-        <v>25.8</v>
+        <v>25.1</v>
       </c>
       <c r="I67" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>19.74</v>
+        <v>30.73</v>
       </c>
       <c r="K67" t="n">
-        <v>-114.95</v>
+        <v>-131.95</v>
       </c>
       <c r="L67" t="n">
-        <v>116.63</v>
+        <v>135.48</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>3.92</v>
       </c>
       <c r="F68" t="n">
-        <v>9.98</v>
+        <v>11.16</v>
       </c>
       <c r="G68" t="n">
-        <v>114.7</v>
+        <v>119.2</v>
       </c>
       <c r="H68" t="n">
-        <v>24.3</v>
+        <v>16.8</v>
       </c>
       <c r="I68" t="n">
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>114.95</v>
+        <v>139.6</v>
       </c>
       <c r="K68" t="n">
-        <v>-92.12</v>
+        <v>-107.63</v>
       </c>
       <c r="L68" t="n">
-        <v>147.31</v>
+        <v>176.27</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>4.3</v>
       </c>
       <c r="F69" t="n">
-        <v>10.14</v>
+        <v>11.41</v>
       </c>
       <c r="G69" t="n">
-        <v>116.9</v>
+        <v>122.5</v>
       </c>
       <c r="H69" t="n">
-        <v>24.4</v>
+        <v>17.9</v>
       </c>
       <c r="I69" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>162.65</v>
+        <v>206.1</v>
       </c>
       <c r="K69" t="n">
-        <v>76.18000000000001</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>179.6</v>
+        <v>217.74</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>4.63</v>
       </c>
       <c r="F70" t="n">
-        <v>11.37</v>
+        <v>11.23</v>
       </c>
       <c r="G70" t="n">
-        <v>125.2</v>
+        <v>147</v>
       </c>
       <c r="H70" t="n">
-        <v>19.5</v>
+        <v>22.1</v>
       </c>
       <c r="I70" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>131.05</v>
+        <v>167.73</v>
       </c>
       <c r="K70" t="n">
-        <v>41.46</v>
+        <v>7.47</v>
       </c>
       <c r="L70" t="n">
-        <v>137.45</v>
+        <v>167.9</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>4.39</v>
       </c>
       <c r="F71" t="n">
-        <v>9.32</v>
+        <v>11.96</v>
       </c>
       <c r="G71" t="n">
-        <v>118.1</v>
+        <v>106.1</v>
       </c>
       <c r="H71" t="n">
-        <v>23.2</v>
+        <v>18.5</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-68.12</v>
+        <v>-39.08</v>
       </c>
       <c r="K71" t="n">
-        <v>-314.94</v>
+        <v>-332.89</v>
       </c>
       <c r="L71" t="n">
-        <v>322.22</v>
+        <v>335.18</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>4.42</v>
       </c>
       <c r="F72" t="n">
-        <v>10.03</v>
+        <v>11.96</v>
       </c>
       <c r="G72" t="n">
-        <v>136.6</v>
+        <v>120.3</v>
       </c>
       <c r="H72" t="n">
-        <v>26.4</v>
+        <v>27.8</v>
       </c>
       <c r="I72" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-49.08</v>
+        <v>9.43</v>
       </c>
       <c r="K72" t="n">
-        <v>192.46</v>
+        <v>219.26</v>
       </c>
       <c r="L72" t="n">
-        <v>198.62</v>
+        <v>219.47</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>3.58</v>
       </c>
       <c r="F73" t="n">
-        <v>10.83</v>
+        <v>11.33</v>
       </c>
       <c r="G73" t="n">
-        <v>133.4</v>
+        <v>136.2</v>
       </c>
       <c r="H73" t="n">
-        <v>26.9</v>
+        <v>26.1</v>
       </c>
       <c r="I73" t="n">
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>249.58</v>
+        <v>297.93</v>
       </c>
       <c r="K73" t="n">
-        <v>30</v>
+        <v>6.57</v>
       </c>
       <c r="L73" t="n">
-        <v>251.38</v>
+        <v>298</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>4.76</v>
       </c>
       <c r="F74" t="n">
-        <v>10.03</v>
+        <v>10.44</v>
       </c>
       <c r="G74" t="n">
-        <v>142</v>
+        <v>120.3</v>
       </c>
       <c r="H74" t="n">
-        <v>16.3</v>
+        <v>30.4</v>
       </c>
       <c r="I74" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>35.43</v>
+        <v>37.69</v>
       </c>
       <c r="K74" t="n">
-        <v>48.08</v>
+        <v>48.19</v>
       </c>
       <c r="L74" t="n">
-        <v>59.73</v>
+        <v>61.18</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>4.68</v>
       </c>
       <c r="F75" t="n">
-        <v>9.67</v>
+        <v>11.33</v>
       </c>
       <c r="G75" t="n">
-        <v>133.5</v>
+        <v>113.2</v>
       </c>
       <c r="H75" t="n">
-        <v>26.1</v>
+        <v>26.2</v>
       </c>
       <c r="I75" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-86.8</v>
+        <v>-98.2</v>
       </c>
       <c r="K75" t="n">
-        <v>35.63</v>
+        <v>40.81</v>
       </c>
       <c r="L75" t="n">
-        <v>93.83</v>
+        <v>106.34</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>4.12</v>
       </c>
       <c r="F76" t="n">
-        <v>10.58</v>
+        <v>11.96</v>
       </c>
       <c r="G76" t="n">
-        <v>127.4</v>
+        <v>131.3</v>
       </c>
       <c r="H76" t="n">
-        <v>25.3</v>
+        <v>23.2</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>28.13</v>
+        <v>30.43</v>
       </c>
       <c r="K76" t="n">
-        <v>82.58</v>
+        <v>86.81</v>
       </c>
       <c r="L76" t="n">
-        <v>87.23999999999999</v>
+        <v>91.98999999999999</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>3.89</v>
       </c>
       <c r="F77" t="n">
-        <v>10.03</v>
+        <v>10.17</v>
       </c>
       <c r="G77" t="n">
-        <v>124.7</v>
+        <v>120.3</v>
       </c>
       <c r="H77" t="n">
-        <v>21.4</v>
+        <v>21.8</v>
       </c>
       <c r="I77" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-80.23</v>
+        <v>-80.88</v>
       </c>
       <c r="K77" t="n">
-        <v>25.32</v>
+        <v>25.04</v>
       </c>
       <c r="L77" t="n">
-        <v>84.13</v>
+        <v>84.67</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>4.56</v>
       </c>
       <c r="F78" t="n">
-        <v>10.42</v>
+        <v>11.96</v>
       </c>
       <c r="G78" t="n">
-        <v>135.3</v>
+        <v>128.1</v>
       </c>
       <c r="H78" t="n">
-        <v>25.2</v>
+        <v>27.1</v>
       </c>
       <c r="I78" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>47.35</v>
+        <v>53.81</v>
       </c>
       <c r="K78" t="n">
-        <v>50.46</v>
+        <v>49.51</v>
       </c>
       <c r="L78" t="n">
-        <v>69.2</v>
+        <v>73.12</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>4.65</v>
       </c>
       <c r="F79" t="n">
-        <v>10.69</v>
+        <v>11.96</v>
       </c>
       <c r="G79" t="n">
-        <v>132.2</v>
+        <v>133.5</v>
       </c>
       <c r="H79" t="n">
-        <v>19</v>
+        <v>25.5</v>
       </c>
       <c r="I79" t="n">
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-56.03</v>
+        <v>-62.79</v>
       </c>
       <c r="K79" t="n">
-        <v>45.56</v>
+        <v>50.33</v>
       </c>
       <c r="L79" t="n">
-        <v>72.20999999999999</v>
+        <v>80.47</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>4.32</v>
       </c>
       <c r="F80" t="n">
-        <v>10.49</v>
+        <v>11.96</v>
       </c>
       <c r="G80" t="n">
-        <v>135.7</v>
+        <v>129.6</v>
       </c>
       <c r="H80" t="n">
-        <v>30.4</v>
+        <v>27.3</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>49.6</v>
+        <v>62.68</v>
       </c>
       <c r="K80" t="n">
-        <v>-87.44</v>
+        <v>-91.26000000000001</v>
       </c>
       <c r="L80" t="n">
-        <v>100.53</v>
+        <v>110.71</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>4.14</v>
       </c>
       <c r="F81" t="n">
-        <v>10.22</v>
+        <v>11.56</v>
       </c>
       <c r="G81" t="n">
-        <v>116.4</v>
+        <v>124.1</v>
       </c>
       <c r="H81" t="n">
-        <v>25.2</v>
+        <v>17.6</v>
       </c>
       <c r="I81" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>89.22</v>
+        <v>112.17</v>
       </c>
       <c r="K81" t="n">
-        <v>-8.65</v>
+        <v>-22.15</v>
       </c>
       <c r="L81" t="n">
-        <v>89.63</v>
+        <v>114.33</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>4.45</v>
       </c>
       <c r="F82" t="n">
-        <v>10.6</v>
+        <v>11.01</v>
       </c>
       <c r="G82" t="n">
-        <v>127.2</v>
+        <v>131.8</v>
       </c>
       <c r="H82" t="n">
-        <v>19.7</v>
+        <v>23.1</v>
       </c>
       <c r="I82" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-100.85</v>
+        <v>-90.95</v>
       </c>
       <c r="K82" t="n">
-        <v>-40.09</v>
+        <v>-59.12</v>
       </c>
       <c r="L82" t="n">
-        <v>108.52</v>
+        <v>108.48</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>4.89</v>
       </c>
       <c r="F83" t="n">
-        <v>10.4</v>
+        <v>11.96</v>
       </c>
       <c r="G83" t="n">
-        <v>122</v>
+        <v>127.8</v>
       </c>
       <c r="H83" t="n">
-        <v>19.2</v>
+        <v>20.4</v>
       </c>
       <c r="I83" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>131.52</v>
+        <v>173.72</v>
       </c>
       <c r="K83" t="n">
-        <v>53.49</v>
+        <v>28.14</v>
       </c>
       <c r="L83" t="n">
-        <v>141.98</v>
+        <v>175.98</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>4.27</v>
       </c>
       <c r="F84" t="n">
-        <v>9.880000000000001</v>
+        <v>11.96</v>
       </c>
       <c r="G84" t="n">
-        <v>123.2</v>
+        <v>117.4</v>
       </c>
       <c r="H84" t="n">
-        <v>31.5</v>
+        <v>21.1</v>
       </c>
       <c r="I84" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-32.64</v>
+        <v>0.38</v>
       </c>
       <c r="K84" t="n">
-        <v>125.91</v>
+        <v>150.11</v>
       </c>
       <c r="L84" t="n">
-        <v>130.07</v>
+        <v>150.11</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>4.2</v>
       </c>
       <c r="F85" t="n">
-        <v>10.1</v>
+        <v>11.77</v>
       </c>
       <c r="G85" t="n">
-        <v>121.6</v>
+        <v>121.8</v>
       </c>
       <c r="H85" t="n">
-        <v>27.7</v>
+        <v>20.3</v>
       </c>
       <c r="I85" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>108.77</v>
+        <v>139.14</v>
       </c>
       <c r="K85" t="n">
-        <v>-46.05</v>
+        <v>-65.93000000000001</v>
       </c>
       <c r="L85" t="n">
-        <v>118.11</v>
+        <v>153.97</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>4.5</v>
       </c>
       <c r="F86" t="n">
-        <v>10.19</v>
+        <v>10.42</v>
       </c>
       <c r="G86" t="n">
-        <v>125</v>
+        <v>123.6</v>
       </c>
       <c r="H86" t="n">
-        <v>17.6</v>
+        <v>21.9</v>
       </c>
       <c r="I86" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>155.65</v>
+        <v>180.04</v>
       </c>
       <c r="K86" t="n">
-        <v>-167.16</v>
+        <v>-176.65</v>
       </c>
       <c r="L86" t="n">
-        <v>228.4</v>
+        <v>252.23</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>3.74</v>
       </c>
       <c r="F87" t="n">
-        <v>9.529999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="G87" t="n">
-        <v>134.1</v>
+        <v>110.3</v>
       </c>
       <c r="H87" t="n">
-        <v>25.3</v>
+        <v>26.5</v>
       </c>
       <c r="I87" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>70.51000000000001</v>
+        <v>114.43</v>
       </c>
       <c r="K87" t="n">
-        <v>-223.19</v>
+        <v>-243.1</v>
       </c>
       <c r="L87" t="n">
-        <v>234.06</v>
+        <v>268.68</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>4.67</v>
       </c>
       <c r="F88" t="n">
-        <v>9.48</v>
+        <v>11.96</v>
       </c>
       <c r="G88" t="n">
-        <v>121.5</v>
+        <v>109.2</v>
       </c>
       <c r="H88" t="n">
-        <v>22.7</v>
+        <v>20.2</v>
       </c>
       <c r="I88" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>295.34</v>
+        <v>359.99</v>
       </c>
       <c r="K88" t="n">
-        <v>225.08</v>
+        <v>251.67</v>
       </c>
       <c r="L88" t="n">
-        <v>371.33</v>
+        <v>439.24</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-10.xlsx
+++ b/output/2024-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-29.18</v>
+        <v>-28.54</v>
       </c>
       <c r="K14" t="n">
-        <v>48.68</v>
+        <v>47.61</v>
       </c>
       <c r="L14" t="n">
-        <v>56.75</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>26</v>
       </c>
       <c r="J15" t="n">
-        <v>-53.43</v>
+        <v>-51.14</v>
       </c>
       <c r="K15" t="n">
-        <v>-23.7</v>
+        <v>-22.69</v>
       </c>
       <c r="L15" t="n">
-        <v>58.46</v>
+        <v>55.95</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>27</v>
       </c>
       <c r="J16" t="n">
-        <v>49.44</v>
+        <v>46.29</v>
       </c>
       <c r="K16" t="n">
-        <v>-43.78</v>
+        <v>-40.99</v>
       </c>
       <c r="L16" t="n">
-        <v>66.04000000000001</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>-60.12</v>
+        <v>-54.86</v>
       </c>
       <c r="K17" t="n">
-        <v>-10.11</v>
+        <v>-9.23</v>
       </c>
       <c r="L17" t="n">
-        <v>60.96</v>
+        <v>55.63</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-90.98</v>
+        <v>-92.61</v>
       </c>
       <c r="K18" t="n">
-        <v>-24.55</v>
+        <v>-24.99</v>
       </c>
       <c r="L18" t="n">
-        <v>94.23</v>
+        <v>95.92</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-43.95</v>
+        <v>-45.6</v>
       </c>
       <c r="K19" t="n">
-        <v>45.75</v>
+        <v>47.46</v>
       </c>
       <c r="L19" t="n">
-        <v>63.44</v>
+        <v>65.81999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-83.97</v>
+        <v>-87.15000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-42.85</v>
+        <v>-44.47</v>
       </c>
       <c r="L20" t="n">
-        <v>94.27</v>
+        <v>97.84</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>28</v>
       </c>
       <c r="J21" t="n">
-        <v>59.42</v>
+        <v>54.16</v>
       </c>
       <c r="K21" t="n">
-        <v>80.51000000000001</v>
+        <v>73.38</v>
       </c>
       <c r="L21" t="n">
-        <v>100.06</v>
+        <v>91.20999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>27.6</v>
+        <v>28.14</v>
       </c>
       <c r="K22" t="n">
-        <v>86.90000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>91.18000000000001</v>
+        <v>92.95999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-136.28</v>
+        <v>-127.64</v>
       </c>
       <c r="K23" t="n">
-        <v>61.93</v>
+        <v>58.01</v>
       </c>
       <c r="L23" t="n">
-        <v>149.69</v>
+        <v>140.2</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>23</v>
       </c>
       <c r="J24" t="n">
-        <v>48.61</v>
+        <v>49.62</v>
       </c>
       <c r="K24" t="n">
-        <v>187.48</v>
+        <v>191.36</v>
       </c>
       <c r="L24" t="n">
-        <v>193.68</v>
+        <v>197.69</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>-107</v>
+        <v>-97.7</v>
       </c>
       <c r="K25" t="n">
-        <v>52.18</v>
+        <v>47.65</v>
       </c>
       <c r="L25" t="n">
-        <v>119.04</v>
+        <v>108.7</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>9.75</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>-200.18</v>
+        <v>-187.61</v>
       </c>
       <c r="L26" t="n">
-        <v>200.42</v>
+        <v>187.84</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>203.87</v>
+        <v>192.07</v>
       </c>
       <c r="K27" t="n">
-        <v>-104.18</v>
+        <v>-98.15000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>228.94</v>
+        <v>215.69</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>209.33</v>
+        <v>218.02</v>
       </c>
       <c r="K28" t="n">
-        <v>-109.25</v>
+        <v>-113.78</v>
       </c>
       <c r="L28" t="n">
-        <v>236.12</v>
+        <v>245.92</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-67.09</v>
+        <v>-64.18000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>-36.83</v>
+        <v>-35.23</v>
       </c>
       <c r="L29" t="n">
-        <v>76.54000000000001</v>
+        <v>73.20999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>22</v>
       </c>
       <c r="J30" t="n">
-        <v>-51.23</v>
+        <v>-52.99</v>
       </c>
       <c r="K30" t="n">
-        <v>-29.9</v>
+        <v>-30.94</v>
       </c>
       <c r="L30" t="n">
-        <v>59.32</v>
+        <v>61.36</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>63.28</v>
+        <v>57.43</v>
       </c>
       <c r="K31" t="n">
-        <v>16.83</v>
+        <v>15.28</v>
       </c>
       <c r="L31" t="n">
-        <v>65.48</v>
+        <v>59.42</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>23.82</v>
+        <v>23.3</v>
       </c>
       <c r="K32" t="n">
-        <v>42.85</v>
+        <v>41.91</v>
       </c>
       <c r="L32" t="n">
-        <v>49.02</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>51.86</v>
+        <v>53.65</v>
       </c>
       <c r="K33" t="n">
-        <v>-62.99</v>
+        <v>-65.16</v>
       </c>
       <c r="L33" t="n">
-        <v>81.59999999999999</v>
+        <v>84.40000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>41.43</v>
+        <v>37.67</v>
       </c>
       <c r="K34" t="n">
-        <v>57.21</v>
+        <v>52.02</v>
       </c>
       <c r="L34" t="n">
-        <v>70.64</v>
+        <v>64.23</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>28</v>
       </c>
       <c r="J35" t="n">
-        <v>5.07</v>
+        <v>4.63</v>
       </c>
       <c r="K35" t="n">
-        <v>99.52</v>
+        <v>90.84</v>
       </c>
       <c r="L35" t="n">
-        <v>99.64</v>
+        <v>90.95999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>7.61</v>
+        <v>7.29</v>
       </c>
       <c r="K36" t="n">
-        <v>-106.27</v>
+        <v>-101.78</v>
       </c>
       <c r="L36" t="n">
-        <v>106.54</v>
+        <v>102.04</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-85.34</v>
+        <v>-81.79000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>30.1</v>
+        <v>28.85</v>
       </c>
       <c r="L37" t="n">
-        <v>90.48999999999999</v>
+        <v>86.72</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>205.35</v>
+        <v>187.63</v>
       </c>
       <c r="K38" t="n">
-        <v>-14.72</v>
+        <v>-13.45</v>
       </c>
       <c r="L38" t="n">
-        <v>205.88</v>
+        <v>188.11</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>135.61</v>
+        <v>138.4</v>
       </c>
       <c r="K39" t="n">
-        <v>37.34</v>
+        <v>38.11</v>
       </c>
       <c r="L39" t="n">
-        <v>140.66</v>
+        <v>143.55</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>26.01</v>
+        <v>24.37</v>
       </c>
       <c r="K40" t="n">
-        <v>-196.16</v>
+        <v>-183.83</v>
       </c>
       <c r="L40" t="n">
-        <v>197.87</v>
+        <v>185.44</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-146.64</v>
+        <v>-150.52</v>
       </c>
       <c r="K41" t="n">
-        <v>-149.04</v>
+        <v>-152.97</v>
       </c>
       <c r="L41" t="n">
-        <v>209.08</v>
+        <v>214.61</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>224.34</v>
+        <v>220.48</v>
       </c>
       <c r="K42" t="n">
-        <v>-105.67</v>
+        <v>-103.85</v>
       </c>
       <c r="L42" t="n">
-        <v>247.99</v>
+        <v>243.71</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>238.8</v>
+        <v>240.43</v>
       </c>
       <c r="K43" t="n">
-        <v>210.47</v>
+        <v>211.9</v>
       </c>
       <c r="L43" t="n">
-        <v>318.31</v>
+        <v>320.48</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-39.94</v>
+        <v>-36.4</v>
       </c>
       <c r="K44" t="n">
-        <v>-66.55</v>
+        <v>-60.65</v>
       </c>
       <c r="L44" t="n">
-        <v>77.62</v>
+        <v>70.73999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.64</v>
+        <v>-3.69</v>
       </c>
       <c r="K45" t="n">
-        <v>-52.31</v>
+        <v>-53.12</v>
       </c>
       <c r="L45" t="n">
-        <v>52.43</v>
+        <v>53.25</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>46.29</v>
+        <v>47.92</v>
       </c>
       <c r="K46" t="n">
-        <v>-14.74</v>
+        <v>-15.26</v>
       </c>
       <c r="L46" t="n">
-        <v>48.58</v>
+        <v>50.29</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>41.82</v>
+        <v>38</v>
       </c>
       <c r="K47" t="n">
-        <v>68.56</v>
+        <v>62.31</v>
       </c>
       <c r="L47" t="n">
-        <v>80.31</v>
+        <v>72.98999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>23.66</v>
+        <v>21.47</v>
       </c>
       <c r="K48" t="n">
-        <v>-109.66</v>
+        <v>-99.47</v>
       </c>
       <c r="L48" t="n">
-        <v>112.18</v>
+        <v>101.76</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>-11.99</v>
+        <v>-12.2</v>
       </c>
       <c r="K49" t="n">
-        <v>-93.19</v>
+        <v>-94.87</v>
       </c>
       <c r="L49" t="n">
-        <v>93.95999999999999</v>
+        <v>95.65000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>31.05</v>
+        <v>29.71</v>
       </c>
       <c r="K50" t="n">
-        <v>-110.48</v>
+        <v>-105.73</v>
       </c>
       <c r="L50" t="n">
-        <v>114.76</v>
+        <v>109.83</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-72.73999999999999</v>
+        <v>-71.15000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-87.75</v>
+        <v>-85.84</v>
       </c>
       <c r="L51" t="n">
-        <v>113.98</v>
+        <v>111.5</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-17.62</v>
+        <v>-17.94</v>
       </c>
       <c r="K52" t="n">
-        <v>57.32</v>
+        <v>58.35</v>
       </c>
       <c r="L52" t="n">
-        <v>59.97</v>
+        <v>61.04</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>22</v>
       </c>
       <c r="J53" t="n">
-        <v>41.47</v>
+        <v>43.1</v>
       </c>
       <c r="K53" t="n">
-        <v>-157.22</v>
+        <v>-163.39</v>
       </c>
       <c r="L53" t="n">
-        <v>162.6</v>
+        <v>168.98</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>130.01</v>
+        <v>135.13</v>
       </c>
       <c r="K54" t="n">
-        <v>82.61</v>
+        <v>85.86</v>
       </c>
       <c r="L54" t="n">
-        <v>154.04</v>
+        <v>160.1</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-119.17</v>
+        <v>-111.66</v>
       </c>
       <c r="K55" t="n">
-        <v>94.20999999999999</v>
+        <v>88.28</v>
       </c>
       <c r="L55" t="n">
-        <v>151.91</v>
+        <v>142.34</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>133.37</v>
+        <v>131.46</v>
       </c>
       <c r="K56" t="n">
-        <v>-199.3</v>
+        <v>-196.45</v>
       </c>
       <c r="L56" t="n">
-        <v>239.81</v>
+        <v>236.38</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-253.75</v>
+        <v>-257.34</v>
       </c>
       <c r="K57" t="n">
-        <v>-220.05</v>
+        <v>-223.16</v>
       </c>
       <c r="L57" t="n">
-        <v>335.87</v>
+        <v>340.62</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-167.67</v>
+        <v>-174.99</v>
       </c>
       <c r="K58" t="n">
-        <v>85.91</v>
+        <v>89.66</v>
       </c>
       <c r="L58" t="n">
-        <v>188.4</v>
+        <v>196.63</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="J59" t="n">
-        <v>71.51000000000001</v>
+        <v>72.56999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>28</v>
+        <v>28.42</v>
       </c>
       <c r="L59" t="n">
-        <v>76.79000000000001</v>
+        <v>77.94</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.48</v>
+        <v>-9.59</v>
       </c>
       <c r="K60" t="n">
-        <v>79.81</v>
+        <v>80.81</v>
       </c>
       <c r="L60" t="n">
-        <v>80.37</v>
+        <v>81.37</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>77.81999999999999</v>
+        <v>74.37</v>
       </c>
       <c r="K61" t="n">
         <v>0.05</v>
       </c>
       <c r="L61" t="n">
-        <v>77.81999999999999</v>
+        <v>74.37</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>23</v>
       </c>
       <c r="J62" t="n">
-        <v>36.73</v>
+        <v>37.33</v>
       </c>
       <c r="K62" t="n">
-        <v>-107.01</v>
+        <v>-108.75</v>
       </c>
       <c r="L62" t="n">
-        <v>113.13</v>
+        <v>114.98</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>-74.53</v>
+        <v>-74.31</v>
       </c>
       <c r="K63" t="n">
-        <v>53.26</v>
+        <v>53.1</v>
       </c>
       <c r="L63" t="n">
-        <v>91.59999999999999</v>
+        <v>91.34</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>70.03</v>
+        <v>69.66</v>
       </c>
       <c r="K64" t="n">
-        <v>-98.06</v>
+        <v>-97.54000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>120.5</v>
+        <v>119.86</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>89.90000000000001</v>
+        <v>86</v>
       </c>
       <c r="K65" t="n">
-        <v>-87.55</v>
+        <v>-83.75</v>
       </c>
       <c r="L65" t="n">
-        <v>125.49</v>
+        <v>120.04</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-103.91</v>
+        <v>-94.76000000000001</v>
       </c>
       <c r="K66" t="n">
-        <v>8.18</v>
+        <v>7.46</v>
       </c>
       <c r="L66" t="n">
-        <v>104.23</v>
+        <v>95.06</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>30.73</v>
+        <v>30.06</v>
       </c>
       <c r="K67" t="n">
-        <v>-131.95</v>
+        <v>-129.06</v>
       </c>
       <c r="L67" t="n">
-        <v>135.48</v>
+        <v>132.52</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>139.6</v>
+        <v>127.56</v>
       </c>
       <c r="K68" t="n">
-        <v>-107.63</v>
+        <v>-98.34999999999999</v>
       </c>
       <c r="L68" t="n">
-        <v>176.27</v>
+        <v>161.07</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>22</v>
       </c>
       <c r="J69" t="n">
-        <v>206.1</v>
+        <v>214.28</v>
       </c>
       <c r="K69" t="n">
-        <v>70.26000000000001</v>
+        <v>73.05</v>
       </c>
       <c r="L69" t="n">
-        <v>217.74</v>
+        <v>226.39</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>167.73</v>
+        <v>172.37</v>
       </c>
       <c r="K70" t="n">
-        <v>7.47</v>
+        <v>7.68</v>
       </c>
       <c r="L70" t="n">
-        <v>167.9</v>
+        <v>172.54</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>24</v>
       </c>
       <c r="J71" t="n">
-        <v>-39.08</v>
+        <v>-39.63</v>
       </c>
       <c r="K71" t="n">
-        <v>-332.89</v>
+        <v>-337.6</v>
       </c>
       <c r="L71" t="n">
-        <v>335.18</v>
+        <v>339.92</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>9.43</v>
+        <v>9.17</v>
       </c>
       <c r="K72" t="n">
-        <v>219.26</v>
+        <v>213.15</v>
       </c>
       <c r="L72" t="n">
-        <v>219.47</v>
+        <v>213.35</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>297.93</v>
+        <v>310.25</v>
       </c>
       <c r="K73" t="n">
-        <v>6.57</v>
+        <v>6.84</v>
       </c>
       <c r="L73" t="n">
-        <v>298</v>
+        <v>310.33</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>37.69</v>
+        <v>34.17</v>
       </c>
       <c r="K74" t="n">
-        <v>48.19</v>
+        <v>43.69</v>
       </c>
       <c r="L74" t="n">
-        <v>61.18</v>
+        <v>55.46</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>23</v>
       </c>
       <c r="J75" t="n">
-        <v>-98.2</v>
+        <v>-99.45</v>
       </c>
       <c r="K75" t="n">
-        <v>40.81</v>
+        <v>41.34</v>
       </c>
       <c r="L75" t="n">
-        <v>106.34</v>
+        <v>107.7</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="J76" t="n">
-        <v>30.43</v>
+        <v>28.37</v>
       </c>
       <c r="K76" t="n">
-        <v>86.81</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>91.98999999999999</v>
+        <v>85.76000000000001</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>26</v>
       </c>
       <c r="J77" t="n">
-        <v>-80.88</v>
+        <v>-77.27</v>
       </c>
       <c r="K77" t="n">
-        <v>25.04</v>
+        <v>23.92</v>
       </c>
       <c r="L77" t="n">
-        <v>84.67</v>
+        <v>80.89</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>53.81</v>
+        <v>50.07</v>
       </c>
       <c r="K78" t="n">
-        <v>49.51</v>
+        <v>46.07</v>
       </c>
       <c r="L78" t="n">
-        <v>73.12</v>
+        <v>68.04000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-62.79</v>
+        <v>-63.61</v>
       </c>
       <c r="K79" t="n">
-        <v>50.33</v>
+        <v>50.98</v>
       </c>
       <c r="L79" t="n">
-        <v>80.47</v>
+        <v>81.52</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>62.68</v>
+        <v>58.58</v>
       </c>
       <c r="K80" t="n">
-        <v>-91.26000000000001</v>
+        <v>-85.28</v>
       </c>
       <c r="L80" t="n">
-        <v>110.71</v>
+        <v>103.46</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>112.17</v>
+        <v>109.71</v>
       </c>
       <c r="K81" t="n">
-        <v>-22.15</v>
+        <v>-21.67</v>
       </c>
       <c r="L81" t="n">
-        <v>114.33</v>
+        <v>111.83</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>-90.95</v>
+        <v>-84.98</v>
       </c>
       <c r="K82" t="n">
-        <v>-59.12</v>
+        <v>-55.24</v>
       </c>
       <c r="L82" t="n">
-        <v>108.48</v>
+        <v>101.36</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>173.72</v>
+        <v>178.67</v>
       </c>
       <c r="K83" t="n">
-        <v>28.14</v>
+        <v>28.94</v>
       </c>
       <c r="L83" t="n">
-        <v>175.98</v>
+        <v>181</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="K84" t="n">
-        <v>150.11</v>
+        <v>150.29</v>
       </c>
       <c r="L84" t="n">
-        <v>150.11</v>
+        <v>150.29</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>25</v>
       </c>
       <c r="J85" t="n">
-        <v>139.14</v>
+        <v>136.45</v>
       </c>
       <c r="K85" t="n">
-        <v>-65.93000000000001</v>
+        <v>-64.66</v>
       </c>
       <c r="L85" t="n">
-        <v>153.97</v>
+        <v>151</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>180.04</v>
+        <v>179.01</v>
       </c>
       <c r="K86" t="n">
-        <v>-176.65</v>
+        <v>-175.65</v>
       </c>
       <c r="L86" t="n">
-        <v>252.23</v>
+        <v>250.79</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>114.43</v>
+        <v>117.14</v>
       </c>
       <c r="K87" t="n">
-        <v>-243.1</v>
+        <v>-248.86</v>
       </c>
       <c r="L87" t="n">
-        <v>268.68</v>
+        <v>275.05</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>359.99</v>
+        <v>365.84</v>
       </c>
       <c r="K88" t="n">
-        <v>251.67</v>
+        <v>255.77</v>
       </c>
       <c r="L88" t="n">
-        <v>439.24</v>
+        <v>446.38</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-10.xlsx
+++ b/output/2024-09-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.56</v>
+        <v>3.79</v>
       </c>
       <c r="F14" t="n">
-        <v>7.01</v>
+        <v>9.33</v>
       </c>
       <c r="G14" t="n">
-        <v>130.5</v>
+        <v>122.3</v>
       </c>
       <c r="H14" t="n">
-        <v>18.8</v>
+        <v>73.8</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-28.54</v>
+        <v>63.97</v>
       </c>
       <c r="K14" t="n">
-        <v>47.61</v>
+        <v>5.17</v>
       </c>
       <c r="L14" t="n">
-        <v>55.51</v>
+        <v>64.18000000000001</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:39:09</t>
+          <t>06:37:55</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.51</v>
+        <v>3.37</v>
       </c>
       <c r="F15" t="n">
-        <v>8.16</v>
+        <v>7.8</v>
       </c>
       <c r="G15" t="n">
-        <v>129.4</v>
+        <v>116.2</v>
       </c>
       <c r="H15" t="n">
-        <v>19.2</v>
+        <v>54.9</v>
       </c>
       <c r="I15" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J15" t="n">
-        <v>-51.14</v>
+        <v>-7.73</v>
       </c>
       <c r="K15" t="n">
-        <v>-22.69</v>
+        <v>63.63</v>
       </c>
       <c r="L15" t="n">
-        <v>55.95</v>
+        <v>64.09999999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:40:40</t>
+          <t>06:39:04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.06</v>
+        <v>3.76</v>
       </c>
       <c r="F16" t="n">
-        <v>5.35</v>
+        <v>7.8</v>
       </c>
       <c r="G16" t="n">
-        <v>127</v>
+        <v>126.9</v>
       </c>
       <c r="H16" t="n">
-        <v>27.6</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J16" t="n">
-        <v>46.29</v>
+        <v>1.11</v>
       </c>
       <c r="K16" t="n">
-        <v>-40.99</v>
+        <v>-76.36</v>
       </c>
       <c r="L16" t="n">
-        <v>61.83</v>
+        <v>76.37</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:45:08</t>
+          <t>06:42:51</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.35</v>
+        <v>3.96</v>
       </c>
       <c r="F17" t="n">
-        <v>10.29</v>
+        <v>11.31</v>
       </c>
       <c r="G17" t="n">
-        <v>121.2</v>
+        <v>126.2</v>
       </c>
       <c r="H17" t="n">
-        <v>16.6</v>
+        <v>41.8</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-54.86</v>
+        <v>-19.64</v>
       </c>
       <c r="K17" t="n">
-        <v>-9.23</v>
+        <v>-75.27</v>
       </c>
       <c r="L17" t="n">
-        <v>55.63</v>
+        <v>77.79000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:46:01</t>
+          <t>06:44:34</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.57</v>
+        <v>3.15</v>
       </c>
       <c r="F18" t="n">
-        <v>7.27</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>118.8</v>
+        <v>133.4</v>
       </c>
       <c r="H18" t="n">
-        <v>24.1</v>
+        <v>68.7</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J18" t="n">
-        <v>-92.61</v>
+        <v>-48.52</v>
       </c>
       <c r="K18" t="n">
-        <v>-24.99</v>
+        <v>58.27</v>
       </c>
       <c r="L18" t="n">
-        <v>95.92</v>
+        <v>75.81999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:48:17</t>
+          <t>06:46:46</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.43</v>
+        <v>3.93</v>
       </c>
       <c r="F19" t="n">
-        <v>8.359999999999999</v>
+        <v>11.19</v>
       </c>
       <c r="G19" t="n">
-        <v>110.7</v>
+        <v>133.1</v>
       </c>
       <c r="H19" t="n">
-        <v>23.2</v>
+        <v>69</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J19" t="n">
-        <v>-45.6</v>
+        <v>-85.17</v>
       </c>
       <c r="K19" t="n">
-        <v>47.46</v>
+        <v>109.2</v>
       </c>
       <c r="L19" t="n">
-        <v>65.81999999999999</v>
+        <v>138.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:53:29</t>
+          <t>06:51:56</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.56</v>
+        <v>3.49</v>
       </c>
       <c r="F20" t="n">
-        <v>8.43</v>
+        <v>9.09</v>
       </c>
       <c r="G20" t="n">
-        <v>133.9</v>
+        <v>136.2</v>
       </c>
       <c r="H20" t="n">
-        <v>22</v>
+        <v>60</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J20" t="n">
-        <v>-87.15000000000001</v>
+        <v>27.14</v>
       </c>
       <c r="K20" t="n">
-        <v>-44.47</v>
+        <v>-135.25</v>
       </c>
       <c r="L20" t="n">
-        <v>97.84</v>
+        <v>137.94</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:55:53</t>
+          <t>06:54:06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>4.28</v>
+        <v>3.35</v>
       </c>
       <c r="F21" t="n">
-        <v>10.57</v>
+        <v>6.56</v>
       </c>
       <c r="G21" t="n">
-        <v>122.6</v>
+        <v>119.4</v>
       </c>
       <c r="H21" t="n">
-        <v>18.7</v>
+        <v>52.1</v>
       </c>
       <c r="I21" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>54.16</v>
+        <v>90.59</v>
       </c>
       <c r="K21" t="n">
-        <v>73.38</v>
+        <v>2.4</v>
       </c>
       <c r="L21" t="n">
-        <v>91.20999999999999</v>
+        <v>90.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:57:50</t>
+          <t>06:55:13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.81</v>
+        <v>3.34</v>
       </c>
       <c r="F22" t="n">
-        <v>7.93</v>
+        <v>7.32</v>
       </c>
       <c r="G22" t="n">
-        <v>118.1</v>
+        <v>128.2</v>
       </c>
       <c r="H22" t="n">
-        <v>25.5</v>
+        <v>64.3</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>28.14</v>
+        <v>-0.53</v>
       </c>
       <c r="K22" t="n">
-        <v>88.59999999999999</v>
+        <v>-120.68</v>
       </c>
       <c r="L22" t="n">
-        <v>92.95999999999999</v>
+        <v>120.68</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:03:00</t>
+          <t>07:00:47</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>3.64</v>
+        <v>4.07</v>
       </c>
       <c r="F23" t="n">
-        <v>10.82</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="G23" t="n">
-        <v>137.7</v>
+        <v>130.4</v>
       </c>
       <c r="H23" t="n">
-        <v>24.4</v>
+        <v>47.1</v>
       </c>
       <c r="I23" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J23" t="n">
-        <v>-127.64</v>
+        <v>-174.58</v>
       </c>
       <c r="K23" t="n">
-        <v>58.01</v>
+        <v>-176.57</v>
       </c>
       <c r="L23" t="n">
-        <v>140.2</v>
+        <v>248.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:05:08</t>
+          <t>07:01:43</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>4.17</v>
+        <v>3.59</v>
       </c>
       <c r="F24" t="n">
-        <v>11.54</v>
+        <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>122.6</v>
+        <v>128.5</v>
       </c>
       <c r="H24" t="n">
-        <v>13.9</v>
+        <v>53.8</v>
       </c>
       <c r="I24" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J24" t="n">
-        <v>49.62</v>
+        <v>208.64</v>
       </c>
       <c r="K24" t="n">
-        <v>191.36</v>
+        <v>110.98</v>
       </c>
       <c r="L24" t="n">
-        <v>197.69</v>
+        <v>236.32</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:06:07</t>
+          <t>07:03:26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>3.34</v>
+        <v>4.01</v>
       </c>
       <c r="F25" t="n">
-        <v>7.75</v>
+        <v>10.14</v>
       </c>
       <c r="G25" t="n">
-        <v>135.1</v>
+        <v>149.1</v>
       </c>
       <c r="H25" t="n">
-        <v>26.7</v>
+        <v>69.2</v>
       </c>
       <c r="I25" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-97.7</v>
+        <v>-155.41</v>
       </c>
       <c r="K25" t="n">
-        <v>47.65</v>
+        <v>-253.61</v>
       </c>
       <c r="L25" t="n">
-        <v>108.7</v>
+        <v>297.44</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:11:52</t>
+          <t>07:09:47</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.38</v>
+        <v>3.46</v>
       </c>
       <c r="F26" t="n">
-        <v>8.34</v>
+        <v>7.61</v>
       </c>
       <c r="G26" t="n">
-        <v>136.1</v>
+        <v>128.3</v>
       </c>
       <c r="H26" t="n">
-        <v>20</v>
+        <v>57.7</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J26" t="n">
-        <v>9.140000000000001</v>
+        <v>194.92</v>
       </c>
       <c r="K26" t="n">
-        <v>-187.61</v>
+        <v>-182.46</v>
       </c>
       <c r="L26" t="n">
-        <v>187.84</v>
+        <v>266.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:13:47</t>
+          <t>07:12:09</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>4.08</v>
+        <v>3.56</v>
       </c>
       <c r="F27" t="n">
-        <v>11.96</v>
+        <v>8.9</v>
       </c>
       <c r="G27" t="n">
-        <v>127.9</v>
+        <v>128.9</v>
       </c>
       <c r="H27" t="n">
-        <v>21.5</v>
+        <v>57</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J27" t="n">
-        <v>192.07</v>
+        <v>-127.3</v>
       </c>
       <c r="K27" t="n">
-        <v>-98.15000000000001</v>
+        <v>-149.03</v>
       </c>
       <c r="L27" t="n">
-        <v>215.69</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:15:44</t>
+          <t>07:14:00</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>3.6</v>
+        <v>4.74</v>
       </c>
       <c r="F28" t="n">
-        <v>6.58</v>
+        <v>11.96</v>
       </c>
       <c r="G28" t="n">
-        <v>132.9</v>
+        <v>148.6</v>
       </c>
       <c r="H28" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="I28" t="n">
         <v>23</v>
       </c>
-      <c r="I28" t="n">
-        <v>22</v>
-      </c>
       <c r="J28" t="n">
-        <v>218.02</v>
+        <v>-226.83</v>
       </c>
       <c r="K28" t="n">
-        <v>-113.78</v>
+        <v>-159.13</v>
       </c>
       <c r="L28" t="n">
-        <v>245.92</v>
+        <v>277.09</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:26:20</t>
+          <t>07:24:24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>3.64</v>
+        <v>4.11</v>
       </c>
       <c r="F29" t="n">
-        <v>8.609999999999999</v>
+        <v>11.95</v>
       </c>
       <c r="G29" t="n">
-        <v>123</v>
+        <v>132.7</v>
       </c>
       <c r="H29" t="n">
-        <v>24.4</v>
+        <v>2.3</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>-64.18000000000001</v>
+        <v>51.72</v>
       </c>
       <c r="K29" t="n">
-        <v>-35.23</v>
+        <v>-42.96</v>
       </c>
       <c r="L29" t="n">
-        <v>73.20999999999999</v>
+        <v>67.23999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:27:25</t>
+          <t>07:26:44</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.05</v>
+        <v>4.19</v>
       </c>
       <c r="F30" t="n">
-        <v>8.789999999999999</v>
+        <v>11.96</v>
       </c>
       <c r="G30" t="n">
-        <v>132.9</v>
+        <v>129.8</v>
       </c>
       <c r="H30" t="n">
-        <v>19.9</v>
+        <v>46.6</v>
       </c>
       <c r="I30" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-52.99</v>
+        <v>83.28</v>
       </c>
       <c r="K30" t="n">
-        <v>-30.94</v>
+        <v>13.45</v>
       </c>
       <c r="L30" t="n">
-        <v>61.36</v>
+        <v>84.34999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:29:43</t>
+          <t>07:28:28</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.54</v>
+        <v>4.26</v>
       </c>
       <c r="F31" t="n">
         <v>11.96</v>
       </c>
       <c r="G31" t="n">
-        <v>122.5</v>
+        <v>138.3</v>
       </c>
       <c r="H31" t="n">
-        <v>22.7</v>
+        <v>28.2</v>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>57.43</v>
+        <v>-37.19</v>
       </c>
       <c r="K31" t="n">
-        <v>15.28</v>
+        <v>22.62</v>
       </c>
       <c r="L31" t="n">
-        <v>59.42</v>
+        <v>43.53</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:33:56</t>
+          <t>07:34:09</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.53</v>
+        <v>4.08</v>
       </c>
       <c r="F32" t="n">
-        <v>10</v>
+        <v>9.43</v>
       </c>
       <c r="G32" t="n">
-        <v>128.8</v>
+        <v>138.2</v>
       </c>
       <c r="H32" t="n">
-        <v>26.2</v>
+        <v>56.8</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>23.3</v>
+        <v>-76.95</v>
       </c>
       <c r="K32" t="n">
-        <v>41.91</v>
+        <v>-55.07</v>
       </c>
       <c r="L32" t="n">
-        <v>47.96</v>
+        <v>94.63</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:35:34</t>
+          <t>07:35:36</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>4.07</v>
+        <v>3.45</v>
       </c>
       <c r="F33" t="n">
-        <v>10.45</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="G33" t="n">
-        <v>121.5</v>
+        <v>130.2</v>
       </c>
       <c r="H33" t="n">
-        <v>23</v>
+        <v>38.3</v>
       </c>
       <c r="I33" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J33" t="n">
-        <v>53.65</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-65.16</v>
+        <v>-1.05</v>
       </c>
       <c r="L33" t="n">
-        <v>84.40000000000001</v>
+        <v>82.43000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:37:21</t>
+          <t>07:37:22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>4.11</v>
+        <v>3.43</v>
       </c>
       <c r="F34" t="n">
-        <v>11.82</v>
+        <v>8.48</v>
       </c>
       <c r="G34" t="n">
-        <v>134.4</v>
+        <v>127.7</v>
       </c>
       <c r="H34" t="n">
-        <v>25.8</v>
+        <v>64.7</v>
       </c>
       <c r="I34" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J34" t="n">
-        <v>37.67</v>
+        <v>101.15</v>
       </c>
       <c r="K34" t="n">
-        <v>52.02</v>
+        <v>9.67</v>
       </c>
       <c r="L34" t="n">
-        <v>64.23</v>
+        <v>101.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:43:24</t>
+          <t>07:41:51</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="F35" t="n">
-        <v>11.96</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>132.4</v>
+        <v>126.9</v>
       </c>
       <c r="H35" t="n">
-        <v>26.5</v>
+        <v>45.7</v>
       </c>
       <c r="I35" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J35" t="n">
-        <v>4.63</v>
+        <v>76.66</v>
       </c>
       <c r="K35" t="n">
-        <v>90.84</v>
+        <v>-46.2</v>
       </c>
       <c r="L35" t="n">
-        <v>90.95999999999999</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:44:20</t>
+          <t>07:44:27</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>3.54</v>
+        <v>4.65</v>
       </c>
       <c r="F36" t="n">
-        <v>8.49</v>
+        <v>10.62</v>
       </c>
       <c r="G36" t="n">
-        <v>120.8</v>
+        <v>142.7</v>
       </c>
       <c r="H36" t="n">
-        <v>25.9</v>
+        <v>53.8</v>
       </c>
       <c r="I36" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J36" t="n">
-        <v>7.29</v>
+        <v>164.4</v>
       </c>
       <c r="K36" t="n">
-        <v>-101.78</v>
+        <v>-7.14</v>
       </c>
       <c r="L36" t="n">
-        <v>102.04</v>
+        <v>164.55</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:45:54</t>
+          <t>07:46:38</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>3.06</v>
+        <v>4.19</v>
       </c>
       <c r="F37" t="n">
-        <v>8.300000000000001</v>
+        <v>11.96</v>
       </c>
       <c r="G37" t="n">
-        <v>132.6</v>
+        <v>135.1</v>
       </c>
       <c r="H37" t="n">
-        <v>25.3</v>
+        <v>28.5</v>
       </c>
       <c r="I37" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J37" t="n">
-        <v>-81.79000000000001</v>
+        <v>-142.6</v>
       </c>
       <c r="K37" t="n">
-        <v>28.85</v>
+        <v>108.3</v>
       </c>
       <c r="L37" t="n">
-        <v>86.72</v>
+        <v>179.06</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:51:18</t>
+          <t>07:52:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>3.83</v>
+        <v>4.35</v>
       </c>
       <c r="F38" t="n">
-        <v>10.51</v>
+        <v>11.96</v>
       </c>
       <c r="G38" t="n">
-        <v>124</v>
+        <v>122.5</v>
       </c>
       <c r="H38" t="n">
-        <v>28.4</v>
+        <v>63.7</v>
       </c>
       <c r="I38" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J38" t="n">
-        <v>187.63</v>
+        <v>167.04</v>
       </c>
       <c r="K38" t="n">
-        <v>-13.45</v>
+        <v>-48.57</v>
       </c>
       <c r="L38" t="n">
-        <v>188.11</v>
+        <v>173.95</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:53:02</t>
+          <t>07:53:23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.07</v>
+        <v>4.03</v>
       </c>
       <c r="F39" t="n">
-        <v>10.47</v>
+        <v>11.96</v>
       </c>
       <c r="G39" t="n">
-        <v>123.7</v>
+        <v>131.8</v>
       </c>
       <c r="H39" t="n">
-        <v>27.8</v>
+        <v>58.9</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J39" t="n">
-        <v>138.4</v>
+        <v>46.74</v>
       </c>
       <c r="K39" t="n">
-        <v>38.11</v>
+        <v>215.64</v>
       </c>
       <c r="L39" t="n">
-        <v>143.55</v>
+        <v>220.65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:54:43</t>
+          <t>07:55:36</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>4.18</v>
+        <v>3.71</v>
       </c>
       <c r="F40" t="n">
-        <v>10.63</v>
+        <v>11.96</v>
       </c>
       <c r="G40" t="n">
-        <v>136.6</v>
+        <v>133.4</v>
       </c>
       <c r="H40" t="n">
-        <v>26.6</v>
+        <v>9.4</v>
       </c>
       <c r="I40" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>24.37</v>
+        <v>191.11</v>
       </c>
       <c r="K40" t="n">
-        <v>-183.83</v>
+        <v>159.13</v>
       </c>
       <c r="L40" t="n">
-        <v>185.44</v>
+        <v>248.68</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>07:59:20</t>
+          <t>08:00:20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.13</v>
+        <v>4.07</v>
       </c>
       <c r="F41" t="n">
-        <v>10.35</v>
+        <v>10.61</v>
       </c>
       <c r="G41" t="n">
-        <v>124.6</v>
+        <v>129.2</v>
       </c>
       <c r="H41" t="n">
-        <v>22.4</v>
+        <v>19.2</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J41" t="n">
-        <v>-150.52</v>
+        <v>-119.21</v>
       </c>
       <c r="K41" t="n">
-        <v>-152.97</v>
+        <v>-128.47</v>
       </c>
       <c r="L41" t="n">
-        <v>214.61</v>
+        <v>175.26</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:00:47</t>
+          <t>08:01:47</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>3.64</v>
+        <v>4.55</v>
       </c>
       <c r="F42" t="n">
-        <v>9.859999999999999</v>
+        <v>11.96</v>
       </c>
       <c r="G42" t="n">
-        <v>128</v>
+        <v>124.9</v>
       </c>
       <c r="H42" t="n">
-        <v>21.6</v>
+        <v>41.1</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>220.48</v>
+        <v>251.46</v>
       </c>
       <c r="K42" t="n">
-        <v>-103.85</v>
+        <v>-227.64</v>
       </c>
       <c r="L42" t="n">
-        <v>243.71</v>
+        <v>339.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:01:42</t>
+          <t>08:03:40</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>4.15</v>
+        <v>3.87</v>
       </c>
       <c r="F43" t="n">
-        <v>11.96</v>
+        <v>8.57</v>
       </c>
       <c r="G43" t="n">
-        <v>139.5</v>
+        <v>120.5</v>
       </c>
       <c r="H43" t="n">
-        <v>27.6</v>
+        <v>86.5</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J43" t="n">
-        <v>240.43</v>
+        <v>132.41</v>
       </c>
       <c r="K43" t="n">
-        <v>211.9</v>
+        <v>-111.02</v>
       </c>
       <c r="L43" t="n">
-        <v>320.48</v>
+        <v>172.79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:13:11</t>
+          <t>08:15:34</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>3.62</v>
+        <v>4.33</v>
       </c>
       <c r="F44" t="n">
-        <v>7.16</v>
+        <v>11.92</v>
       </c>
       <c r="G44" t="n">
-        <v>115.6</v>
+        <v>133.4</v>
       </c>
       <c r="H44" t="n">
-        <v>27.5</v>
+        <v>26</v>
       </c>
       <c r="I44" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J44" t="n">
-        <v>-36.4</v>
+        <v>46.17</v>
       </c>
       <c r="K44" t="n">
-        <v>-60.65</v>
+        <v>84.48999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>70.73999999999999</v>
+        <v>96.28</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:13:59</t>
+          <t>08:18:02</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.08</v>
+        <v>4.27</v>
       </c>
       <c r="F45" t="n">
-        <v>8.07</v>
+        <v>11.96</v>
       </c>
       <c r="G45" t="n">
-        <v>112.7</v>
+        <v>123.9</v>
       </c>
       <c r="H45" t="n">
-        <v>23.4</v>
+        <v>9.9</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>-3.69</v>
+        <v>-45.27</v>
       </c>
       <c r="K45" t="n">
-        <v>-53.12</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>53.25</v>
+        <v>89.09999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:16:12</t>
+          <t>08:19:25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1972,31 +1972,31 @@
         <v>3.89</v>
       </c>
       <c r="F46" t="n">
-        <v>11.96</v>
+        <v>10.81</v>
       </c>
       <c r="G46" t="n">
-        <v>117.1</v>
+        <v>127.1</v>
       </c>
       <c r="H46" t="n">
-        <v>22</v>
+        <v>9.9</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J46" t="n">
-        <v>47.92</v>
+        <v>29.88</v>
       </c>
       <c r="K46" t="n">
-        <v>-15.26</v>
+        <v>62.87</v>
       </c>
       <c r="L46" t="n">
-        <v>50.29</v>
+        <v>69.61</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:20:45</t>
+          <t>08:23:43</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.22</v>
+        <v>4.01</v>
       </c>
       <c r="F47" t="n">
-        <v>8.460000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="G47" t="n">
-        <v>123.5</v>
+        <v>141.6</v>
       </c>
       <c r="H47" t="n">
-        <v>29.5</v>
+        <v>88</v>
       </c>
       <c r="I47" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J47" t="n">
-        <v>38</v>
+        <v>-75.37</v>
       </c>
       <c r="K47" t="n">
-        <v>62.31</v>
+        <v>81.13</v>
       </c>
       <c r="L47" t="n">
-        <v>72.98999999999999</v>
+        <v>110.74</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:22:07</t>
+          <t>08:25:45</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.66</v>
+        <v>4.3</v>
       </c>
       <c r="F48" t="n">
-        <v>9.58</v>
+        <v>11.96</v>
       </c>
       <c r="G48" t="n">
-        <v>145.2</v>
+        <v>116.1</v>
       </c>
       <c r="H48" t="n">
-        <v>20.5</v>
+        <v>76.90000000000001</v>
       </c>
       <c r="I48" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J48" t="n">
-        <v>21.47</v>
+        <v>6.16</v>
       </c>
       <c r="K48" t="n">
-        <v>-99.47</v>
+        <v>-81.84999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>101.76</v>
+        <v>82.08</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:23:50</t>
+          <t>08:28:01</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.58</v>
+        <v>3.89</v>
       </c>
       <c r="F49" t="n">
-        <v>9.529999999999999</v>
+        <v>10.58</v>
       </c>
       <c r="G49" t="n">
-        <v>111.7</v>
+        <v>136.6</v>
       </c>
       <c r="H49" t="n">
-        <v>20</v>
+        <v>42.8</v>
       </c>
       <c r="I49" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.2</v>
+        <v>-79.3</v>
       </c>
       <c r="K49" t="n">
-        <v>-94.87</v>
+        <v>-46.37</v>
       </c>
       <c r="L49" t="n">
-        <v>95.65000000000001</v>
+        <v>91.86</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:27:48</t>
+          <t>08:33:47</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.06</v>
+        <v>4.53</v>
       </c>
       <c r="F50" t="n">
-        <v>11.96</v>
+        <v>11.74</v>
       </c>
       <c r="G50" t="n">
-        <v>126.1</v>
+        <v>134.6</v>
       </c>
       <c r="H50" t="n">
-        <v>25.6</v>
+        <v>98.7</v>
       </c>
       <c r="I50" t="n">
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>29.71</v>
+        <v>87.59</v>
       </c>
       <c r="K50" t="n">
-        <v>-105.73</v>
+        <v>-108.14</v>
       </c>
       <c r="L50" t="n">
-        <v>109.83</v>
+        <v>139.16</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:29:11</t>
+          <t>08:34:57</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>4.07</v>
+        <v>3.95</v>
       </c>
       <c r="F51" t="n">
-        <v>11.96</v>
+        <v>10.04</v>
       </c>
       <c r="G51" t="n">
-        <v>132.8</v>
+        <v>113.6</v>
       </c>
       <c r="H51" t="n">
-        <v>20.6</v>
+        <v>61</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J51" t="n">
-        <v>-71.15000000000001</v>
+        <v>-124.22</v>
       </c>
       <c r="K51" t="n">
-        <v>-85.84</v>
+        <v>-3.09</v>
       </c>
       <c r="L51" t="n">
-        <v>111.5</v>
+        <v>124.26</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:31:13</t>
+          <t>08:36:44</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>4.29</v>
+        <v>3.9</v>
       </c>
       <c r="F52" t="n">
-        <v>8.56</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>137</v>
+        <v>133.8</v>
       </c>
       <c r="H52" t="n">
-        <v>29.9</v>
+        <v>44.8</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-17.94</v>
+        <v>-60.75</v>
       </c>
       <c r="K52" t="n">
-        <v>58.35</v>
+        <v>-104.06</v>
       </c>
       <c r="L52" t="n">
-        <v>61.04</v>
+        <v>120.49</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:37:07</t>
+          <t>08:42:31</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>3.87</v>
+        <v>4.07</v>
       </c>
       <c r="F53" t="n">
-        <v>8.01</v>
+        <v>10.74</v>
       </c>
       <c r="G53" t="n">
-        <v>128.2</v>
+        <v>136.3</v>
       </c>
       <c r="H53" t="n">
-        <v>32.6</v>
+        <v>55.4</v>
       </c>
       <c r="I53" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J53" t="n">
-        <v>43.1</v>
+        <v>183.74</v>
       </c>
       <c r="K53" t="n">
-        <v>-163.39</v>
+        <v>200.41</v>
       </c>
       <c r="L53" t="n">
-        <v>168.98</v>
+        <v>271.89</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:38:20</t>
+          <t>08:43:26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.99</v>
+        <v>3.43</v>
       </c>
       <c r="F54" t="n">
-        <v>10.35</v>
+        <v>8.08</v>
       </c>
       <c r="G54" t="n">
-        <v>131.5</v>
+        <v>119.5</v>
       </c>
       <c r="H54" t="n">
-        <v>20.3</v>
+        <v>45.7</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="J54" t="n">
-        <v>135.13</v>
+        <v>227.73</v>
       </c>
       <c r="K54" t="n">
-        <v>85.86</v>
+        <v>1.85</v>
       </c>
       <c r="L54" t="n">
-        <v>160.1</v>
+        <v>227.73</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:39:33</t>
+          <t>08:44:58</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>4.04</v>
+        <v>3.15</v>
       </c>
       <c r="F55" t="n">
-        <v>11.96</v>
+        <v>7.81</v>
       </c>
       <c r="G55" t="n">
-        <v>132.1</v>
+        <v>124.9</v>
       </c>
       <c r="H55" t="n">
-        <v>15.8</v>
+        <v>34.1</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J55" t="n">
-        <v>-111.66</v>
+        <v>138.02</v>
       </c>
       <c r="K55" t="n">
-        <v>88.28</v>
+        <v>-74.84</v>
       </c>
       <c r="L55" t="n">
-        <v>142.34</v>
+        <v>157</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:44:02</t>
+          <t>08:48:31</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.06</v>
+        <v>4.63</v>
       </c>
       <c r="F56" t="n">
         <v>11.96</v>
       </c>
       <c r="G56" t="n">
-        <v>127</v>
+        <v>144.8</v>
       </c>
       <c r="H56" t="n">
-        <v>16.9</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>131.46</v>
+        <v>306.82</v>
       </c>
       <c r="K56" t="n">
-        <v>-196.45</v>
+        <v>10.15</v>
       </c>
       <c r="L56" t="n">
-        <v>236.38</v>
+        <v>306.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:45:26</t>
+          <t>08:49:30</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.39</v>
+        <v>4.47</v>
       </c>
       <c r="F57" t="n">
         <v>11.96</v>
       </c>
       <c r="G57" t="n">
-        <v>129.6</v>
+        <v>130.8</v>
       </c>
       <c r="H57" t="n">
-        <v>16.9</v>
+        <v>27.8</v>
       </c>
       <c r="I57" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J57" t="n">
-        <v>-257.34</v>
+        <v>-177.38</v>
       </c>
       <c r="K57" t="n">
-        <v>-223.16</v>
+        <v>-152.98</v>
       </c>
       <c r="L57" t="n">
-        <v>340.62</v>
+        <v>234.23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:47:05</t>
+          <t>08:50:54</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>3.88</v>
+        <v>4.51</v>
       </c>
       <c r="F58" t="n">
-        <v>11.54</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="G58" t="n">
-        <v>131.5</v>
+        <v>114.7</v>
       </c>
       <c r="H58" t="n">
-        <v>21.9</v>
+        <v>42.3</v>
       </c>
       <c r="I58" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>-174.99</v>
+        <v>188.56</v>
       </c>
       <c r="K58" t="n">
-        <v>89.66</v>
+        <v>77.84</v>
       </c>
       <c r="L58" t="n">
-        <v>196.63</v>
+        <v>203.99</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:59:19</t>
+          <t>08:59:39</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.22</v>
+        <v>4.21</v>
       </c>
       <c r="F59" t="n">
-        <v>11.36</v>
+        <v>11.96</v>
       </c>
       <c r="G59" t="n">
-        <v>134.6</v>
+        <v>129.4</v>
       </c>
       <c r="H59" t="n">
-        <v>23.3</v>
+        <v>55.4</v>
       </c>
       <c r="I59" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J59" t="n">
-        <v>72.56999999999999</v>
+        <v>-74.69</v>
       </c>
       <c r="K59" t="n">
-        <v>28.42</v>
+        <v>12.68</v>
       </c>
       <c r="L59" t="n">
-        <v>77.94</v>
+        <v>75.76000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:01:55</t>
+          <t>09:01:10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.75</v>
+        <v>4.55</v>
       </c>
       <c r="F60" t="n">
         <v>11.96</v>
       </c>
       <c r="G60" t="n">
-        <v>115</v>
+        <v>121.9</v>
       </c>
       <c r="H60" t="n">
-        <v>20.6</v>
+        <v>28.1</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.59</v>
+        <v>110.9</v>
       </c>
       <c r="K60" t="n">
-        <v>80.81</v>
+        <v>-10.11</v>
       </c>
       <c r="L60" t="n">
-        <v>81.37</v>
+        <v>111.36</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:03:31</t>
+          <t>09:03:15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>3.8</v>
+        <v>4.44</v>
       </c>
       <c r="F61" t="n">
-        <v>10.94</v>
+        <v>10.28</v>
       </c>
       <c r="G61" t="n">
-        <v>130.6</v>
+        <v>115.6</v>
       </c>
       <c r="H61" t="n">
-        <v>22.6</v>
+        <v>36.6</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J61" t="n">
-        <v>74.37</v>
+        <v>60.38</v>
       </c>
       <c r="K61" t="n">
-        <v>0.05</v>
+        <v>-54.4</v>
       </c>
       <c r="L61" t="n">
-        <v>74.37</v>
+        <v>81.28</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:07:36</t>
+          <t>09:08:16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2644,31 +2644,31 @@
         <v>3.92</v>
       </c>
       <c r="F62" t="n">
-        <v>8.960000000000001</v>
+        <v>11.66</v>
       </c>
       <c r="G62" t="n">
-        <v>138.5</v>
+        <v>136.7</v>
       </c>
       <c r="H62" t="n">
-        <v>30.5</v>
+        <v>30.8</v>
       </c>
       <c r="I62" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>37.33</v>
+        <v>-60.15</v>
       </c>
       <c r="K62" t="n">
-        <v>-108.75</v>
+        <v>-40</v>
       </c>
       <c r="L62" t="n">
-        <v>114.98</v>
+        <v>72.23999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:09:10</t>
+          <t>09:09:12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>3.85</v>
+        <v>4.15</v>
       </c>
       <c r="F63" t="n">
-        <v>11.02</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="G63" t="n">
-        <v>132.6</v>
+        <v>134.8</v>
       </c>
       <c r="H63" t="n">
-        <v>22</v>
+        <v>49.5</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J63" t="n">
-        <v>-74.31</v>
+        <v>86.8</v>
       </c>
       <c r="K63" t="n">
-        <v>53.1</v>
+        <v>-28.36</v>
       </c>
       <c r="L63" t="n">
-        <v>91.34</v>
+        <v>91.31999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:10:42</t>
+          <t>09:11:37</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.38</v>
+        <v>4.72</v>
       </c>
       <c r="F64" t="n">
-        <v>11.96</v>
+        <v>10.03</v>
       </c>
       <c r="G64" t="n">
-        <v>138.4</v>
+        <v>142.5</v>
       </c>
       <c r="H64" t="n">
-        <v>23.7</v>
+        <v>62.4</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J64" t="n">
-        <v>69.66</v>
+        <v>146.72</v>
       </c>
       <c r="K64" t="n">
-        <v>-97.54000000000001</v>
+        <v>45.94</v>
       </c>
       <c r="L64" t="n">
-        <v>119.86</v>
+        <v>153.75</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:14:39</t>
+          <t>09:15:06</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.37</v>
+        <v>4.47</v>
       </c>
       <c r="F65" t="n">
-        <v>10.58</v>
+        <v>10.7</v>
       </c>
       <c r="G65" t="n">
-        <v>111.6</v>
+        <v>138.2</v>
       </c>
       <c r="H65" t="n">
-        <v>26.9</v>
+        <v>52.1</v>
       </c>
       <c r="I65" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="J65" t="n">
-        <v>86</v>
+        <v>141.77</v>
       </c>
       <c r="K65" t="n">
-        <v>-83.75</v>
+        <v>42.73</v>
       </c>
       <c r="L65" t="n">
-        <v>120.04</v>
+        <v>148.07</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:16:36</t>
+          <t>09:16:27</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.95</v>
+        <v>3.77</v>
       </c>
       <c r="F66" t="n">
-        <v>10.26</v>
+        <v>10.28</v>
       </c>
       <c r="G66" t="n">
-        <v>134.1</v>
+        <v>121.2</v>
       </c>
       <c r="H66" t="n">
-        <v>22.6</v>
+        <v>66.8</v>
       </c>
       <c r="I66" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J66" t="n">
-        <v>-94.76000000000001</v>
+        <v>139.2</v>
       </c>
       <c r="K66" t="n">
-        <v>7.46</v>
+        <v>-16.56</v>
       </c>
       <c r="L66" t="n">
-        <v>95.06</v>
+        <v>140.18</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:19:15</t>
+          <t>09:19:03</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.15</v>
+        <v>4.78</v>
       </c>
       <c r="F67" t="n">
-        <v>8.859999999999999</v>
+        <v>11.96</v>
       </c>
       <c r="G67" t="n">
-        <v>132.2</v>
+        <v>113.9</v>
       </c>
       <c r="H67" t="n">
-        <v>25.1</v>
+        <v>39</v>
       </c>
       <c r="I67" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J67" t="n">
-        <v>30.06</v>
+        <v>221.3</v>
       </c>
       <c r="K67" t="n">
-        <v>-129.06</v>
+        <v>-19.41</v>
       </c>
       <c r="L67" t="n">
-        <v>132.52</v>
+        <v>222.15</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:23:19</t>
+          <t>09:23:35</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>3.92</v>
+        <v>4.08</v>
       </c>
       <c r="F68" t="n">
-        <v>11.16</v>
+        <v>11.96</v>
       </c>
       <c r="G68" t="n">
-        <v>119.2</v>
+        <v>133.8</v>
       </c>
       <c r="H68" t="n">
-        <v>16.8</v>
+        <v>30.9</v>
       </c>
       <c r="I68" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J68" t="n">
-        <v>127.56</v>
+        <v>221.38</v>
       </c>
       <c r="K68" t="n">
-        <v>-98.34999999999999</v>
+        <v>78.73</v>
       </c>
       <c r="L68" t="n">
-        <v>161.07</v>
+        <v>234.96</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:25:16</t>
+          <t>09:25:09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.3</v>
+        <v>4.16</v>
       </c>
       <c r="F69" t="n">
-        <v>11.41</v>
+        <v>11.39</v>
       </c>
       <c r="G69" t="n">
-        <v>122.5</v>
+        <v>121.4</v>
       </c>
       <c r="H69" t="n">
-        <v>17.9</v>
+        <v>35.1</v>
       </c>
       <c r="I69" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J69" t="n">
-        <v>214.28</v>
+        <v>382.13</v>
       </c>
       <c r="K69" t="n">
-        <v>73.05</v>
+        <v>-50.65</v>
       </c>
       <c r="L69" t="n">
-        <v>226.39</v>
+        <v>385.47</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:27:15</t>
+          <t>09:27:07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>4.63</v>
+        <v>3.8</v>
       </c>
       <c r="F70" t="n">
-        <v>11.23</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="G70" t="n">
-        <v>147</v>
+        <v>133.9</v>
       </c>
       <c r="H70" t="n">
-        <v>22.1</v>
+        <v>64.8</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J70" t="n">
-        <v>172.37</v>
+        <v>82.13</v>
       </c>
       <c r="K70" t="n">
-        <v>7.68</v>
+        <v>-193.85</v>
       </c>
       <c r="L70" t="n">
-        <v>172.54</v>
+        <v>210.52</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:31:14</t>
+          <t>09:32:46</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.39</v>
+        <v>4.21</v>
       </c>
       <c r="F71" t="n">
         <v>11.96</v>
       </c>
       <c r="G71" t="n">
-        <v>106.1</v>
+        <v>140.4</v>
       </c>
       <c r="H71" t="n">
-        <v>18.5</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I71" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-39.63</v>
+        <v>-267.71</v>
       </c>
       <c r="K71" t="n">
-        <v>-337.6</v>
+        <v>5.97</v>
       </c>
       <c r="L71" t="n">
-        <v>339.92</v>
+        <v>267.78</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:32:42</t>
+          <t>09:34:01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.42</v>
+        <v>4.02</v>
       </c>
       <c r="F72" t="n">
-        <v>11.96</v>
+        <v>10.97</v>
       </c>
       <c r="G72" t="n">
-        <v>120.3</v>
+        <v>146.8</v>
       </c>
       <c r="H72" t="n">
-        <v>27.8</v>
+        <v>57.8</v>
       </c>
       <c r="I72" t="n">
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>9.17</v>
+        <v>-175.49</v>
       </c>
       <c r="K72" t="n">
-        <v>213.15</v>
+        <v>-194.67</v>
       </c>
       <c r="L72" t="n">
-        <v>213.35</v>
+        <v>262.09</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:33:18</t>
+          <t>09:35:09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.58</v>
+        <v>3.87</v>
       </c>
       <c r="F73" t="n">
-        <v>11.33</v>
+        <v>11.38</v>
       </c>
       <c r="G73" t="n">
-        <v>136.2</v>
+        <v>139</v>
       </c>
       <c r="H73" t="n">
-        <v>26.1</v>
+        <v>40.1</v>
       </c>
       <c r="I73" t="n">
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>310.25</v>
+        <v>-82.47</v>
       </c>
       <c r="K73" t="n">
-        <v>6.84</v>
+        <v>-236.18</v>
       </c>
       <c r="L73" t="n">
-        <v>310.33</v>
+        <v>250.16</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:45:59</t>
+          <t>09:43:55</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.76</v>
+        <v>4.94</v>
       </c>
       <c r="F74" t="n">
-        <v>10.44</v>
+        <v>11.96</v>
       </c>
       <c r="G74" t="n">
-        <v>120.3</v>
+        <v>118.4</v>
       </c>
       <c r="H74" t="n">
-        <v>30.4</v>
+        <v>22.4</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J74" t="n">
-        <v>34.17</v>
+        <v>63.9</v>
       </c>
       <c r="K74" t="n">
-        <v>43.69</v>
+        <v>-73.37</v>
       </c>
       <c r="L74" t="n">
-        <v>55.46</v>
+        <v>97.3</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:47:54</t>
+          <t>09:44:44</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.68</v>
+        <v>4.03</v>
       </c>
       <c r="F75" t="n">
-        <v>11.33</v>
+        <v>5.72</v>
       </c>
       <c r="G75" t="n">
-        <v>113.2</v>
+        <v>137.6</v>
       </c>
       <c r="H75" t="n">
-        <v>26.2</v>
+        <v>5.1</v>
       </c>
       <c r="I75" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="J75" t="n">
-        <v>-99.45</v>
+        <v>43.67</v>
       </c>
       <c r="K75" t="n">
-        <v>41.34</v>
+        <v>-55.9</v>
       </c>
       <c r="L75" t="n">
-        <v>107.7</v>
+        <v>70.94</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:49:13</t>
+          <t>09:46:17</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>4.12</v>
+        <v>3.58</v>
       </c>
       <c r="F76" t="n">
-        <v>11.96</v>
+        <v>11.13</v>
       </c>
       <c r="G76" t="n">
-        <v>131.3</v>
+        <v>127.3</v>
       </c>
       <c r="H76" t="n">
-        <v>23.2</v>
+        <v>85.3</v>
       </c>
       <c r="I76" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J76" t="n">
-        <v>28.37</v>
+        <v>-40.98</v>
       </c>
       <c r="K76" t="n">
-        <v>80.93000000000001</v>
+        <v>-47.12</v>
       </c>
       <c r="L76" t="n">
-        <v>85.76000000000001</v>
+        <v>62.45</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:54:25</t>
+          <t>09:52:29</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>3.89</v>
+        <v>4.31</v>
       </c>
       <c r="F77" t="n">
-        <v>10.17</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="G77" t="n">
-        <v>120.3</v>
+        <v>125.4</v>
       </c>
       <c r="H77" t="n">
-        <v>21.8</v>
+        <v>28.6</v>
       </c>
       <c r="I77" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="J77" t="n">
-        <v>-77.27</v>
+        <v>253.32</v>
       </c>
       <c r="K77" t="n">
-        <v>23.92</v>
+        <v>-94.59</v>
       </c>
       <c r="L77" t="n">
-        <v>80.89</v>
+        <v>270.41</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:56:29</t>
+          <t>09:54:09</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.56</v>
+        <v>4.24</v>
       </c>
       <c r="F78" t="n">
         <v>11.96</v>
       </c>
       <c r="G78" t="n">
+        <v>124.1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>66</v>
+      </c>
+      <c r="I78" t="n">
+        <v>26</v>
+      </c>
+      <c r="J78" t="n">
         <v>128.1</v>
       </c>
-      <c r="H78" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="I78" t="n">
-        <v>27</v>
-      </c>
-      <c r="J78" t="n">
-        <v>50.07</v>
-      </c>
       <c r="K78" t="n">
-        <v>46.07</v>
+        <v>88.83</v>
       </c>
       <c r="L78" t="n">
-        <v>68.04000000000001</v>
+        <v>155.89</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:57:53</t>
+          <t>09:56:52</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>4.65</v>
+        <v>3.89</v>
       </c>
       <c r="F79" t="n">
-        <v>11.96</v>
+        <v>6.55</v>
       </c>
       <c r="G79" t="n">
-        <v>133.5</v>
+        <v>132.2</v>
       </c>
       <c r="H79" t="n">
-        <v>25.5</v>
+        <v>21.3</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J79" t="n">
-        <v>-63.61</v>
+        <v>5.2</v>
       </c>
       <c r="K79" t="n">
-        <v>50.98</v>
+        <v>-100.39</v>
       </c>
       <c r="L79" t="n">
-        <v>81.52</v>
+        <v>100.53</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:02:53</t>
+          <t>10:01:09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>4.32</v>
+        <v>3.99</v>
       </c>
       <c r="F80" t="n">
-        <v>11.96</v>
+        <v>10.68</v>
       </c>
       <c r="G80" t="n">
-        <v>129.6</v>
+        <v>113.8</v>
       </c>
       <c r="H80" t="n">
-        <v>27.3</v>
+        <v>27.6</v>
       </c>
       <c r="I80" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="J80" t="n">
-        <v>58.58</v>
+        <v>147.8</v>
       </c>
       <c r="K80" t="n">
-        <v>-85.28</v>
+        <v>24.99</v>
       </c>
       <c r="L80" t="n">
-        <v>103.46</v>
+        <v>149.9</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:04:27</t>
+          <t>10:02:21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.14</v>
+        <v>4.44</v>
       </c>
       <c r="F81" t="n">
-        <v>11.56</v>
+        <v>10.55</v>
       </c>
       <c r="G81" t="n">
-        <v>124.1</v>
+        <v>119.9</v>
       </c>
       <c r="H81" t="n">
-        <v>17.6</v>
+        <v>64.3</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J81" t="n">
-        <v>109.71</v>
+        <v>82.20999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-21.67</v>
+        <v>-109.09</v>
       </c>
       <c r="L81" t="n">
-        <v>111.83</v>
+        <v>136.6</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:06:32</t>
+          <t>10:03:38</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>4.45</v>
+        <v>5.15</v>
       </c>
       <c r="F82" t="n">
-        <v>11.01</v>
+        <v>11.74</v>
       </c>
       <c r="G82" t="n">
-        <v>131.8</v>
+        <v>147.4</v>
       </c>
       <c r="H82" t="n">
-        <v>23.1</v>
+        <v>35.5</v>
       </c>
       <c r="I82" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-84.98</v>
+        <v>40.93</v>
       </c>
       <c r="K82" t="n">
-        <v>-55.24</v>
+        <v>-222.97</v>
       </c>
       <c r="L82" t="n">
-        <v>101.36</v>
+        <v>226.69</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:10:43</t>
+          <t>10:07:14</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.89</v>
+        <v>4.38</v>
       </c>
       <c r="F83" t="n">
         <v>11.96</v>
       </c>
       <c r="G83" t="n">
-        <v>127.8</v>
+        <v>139.6</v>
       </c>
       <c r="H83" t="n">
-        <v>20.4</v>
+        <v>33.7</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>178.67</v>
+        <v>234.01</v>
       </c>
       <c r="K83" t="n">
-        <v>28.94</v>
+        <v>60.41</v>
       </c>
       <c r="L83" t="n">
-        <v>181</v>
+        <v>241.69</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:12:25</t>
+          <t>10:09:20</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.27</v>
+        <v>4.38</v>
       </c>
       <c r="F84" t="n">
         <v>11.96</v>
       </c>
       <c r="G84" t="n">
-        <v>117.4</v>
+        <v>120.2</v>
       </c>
       <c r="H84" t="n">
-        <v>21.1</v>
+        <v>42.3</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J84" t="n">
-        <v>0.39</v>
+        <v>143.19</v>
       </c>
       <c r="K84" t="n">
-        <v>150.29</v>
+        <v>-150.58</v>
       </c>
       <c r="L84" t="n">
-        <v>150.29</v>
+        <v>207.8</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:13:13</t>
+          <t>10:10:56</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="F85" t="n">
-        <v>11.77</v>
+        <v>11.96</v>
       </c>
       <c r="G85" t="n">
-        <v>121.8</v>
+        <v>117.8</v>
       </c>
       <c r="H85" t="n">
-        <v>20.3</v>
+        <v>52.7</v>
       </c>
       <c r="I85" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="J85" t="n">
-        <v>136.45</v>
+        <v>214.26</v>
       </c>
       <c r="K85" t="n">
-        <v>-64.66</v>
+        <v>-101.7</v>
       </c>
       <c r="L85" t="n">
-        <v>151</v>
+        <v>237.18</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:19:15</t>
+          <t>10:16:31</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.5</v>
+        <v>4.48</v>
       </c>
       <c r="F86" t="n">
-        <v>10.42</v>
+        <v>11.96</v>
       </c>
       <c r="G86" t="n">
-        <v>123.6</v>
+        <v>124.1</v>
       </c>
       <c r="H86" t="n">
-        <v>21.9</v>
+        <v>39.8</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J86" t="n">
-        <v>179.01</v>
+        <v>300.39</v>
       </c>
       <c r="K86" t="n">
-        <v>-175.65</v>
+        <v>79.02</v>
       </c>
       <c r="L86" t="n">
-        <v>250.79</v>
+        <v>310.6</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:20:56</t>
+          <t>10:18:38</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>3.74</v>
+        <v>4.83</v>
       </c>
       <c r="F87" t="n">
-        <v>8.85</v>
+        <v>11.83</v>
       </c>
       <c r="G87" t="n">
-        <v>110.3</v>
+        <v>131.4</v>
       </c>
       <c r="H87" t="n">
-        <v>26.5</v>
+        <v>61.4</v>
       </c>
       <c r="I87" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>117.14</v>
+        <v>128.03</v>
       </c>
       <c r="K87" t="n">
-        <v>-248.86</v>
+        <v>389.42</v>
       </c>
       <c r="L87" t="n">
-        <v>275.05</v>
+        <v>409.93</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:22:35</t>
+          <t>10:19:29</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.67</v>
+        <v>4.27</v>
       </c>
       <c r="F88" t="n">
-        <v>11.96</v>
+        <v>11.29</v>
       </c>
       <c r="G88" t="n">
-        <v>109.2</v>
+        <v>130.9</v>
       </c>
       <c r="H88" t="n">
-        <v>20.2</v>
+        <v>52</v>
       </c>
       <c r="I88" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>365.84</v>
+        <v>245.66</v>
       </c>
       <c r="K88" t="n">
-        <v>255.77</v>
+        <v>96.61</v>
       </c>
       <c r="L88" t="n">
-        <v>446.38</v>
+        <v>263.97</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-10.xlsx
+++ b/output/2024-09-10.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3.79</v>
+        <v>3.39</v>
       </c>
       <c r="F14" t="n">
-        <v>9.33</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>122.3</v>
+        <v>134.5</v>
       </c>
       <c r="H14" t="n">
-        <v>73.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>63.97</v>
+        <v>-31.87</v>
       </c>
       <c r="K14" t="n">
-        <v>5.17</v>
+        <v>-53.43</v>
       </c>
       <c r="L14" t="n">
-        <v>64.18000000000001</v>
+        <v>62.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>06:37:55</t>
+          <t>06:38:10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.37</v>
+        <v>4.1</v>
       </c>
       <c r="F15" t="n">
-        <v>7.8</v>
+        <v>11.96</v>
       </c>
       <c r="G15" t="n">
-        <v>116.2</v>
+        <v>133.7</v>
       </c>
       <c r="H15" t="n">
-        <v>54.9</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.73</v>
+        <v>52.42</v>
       </c>
       <c r="K15" t="n">
-        <v>63.63</v>
+        <v>-58.81</v>
       </c>
       <c r="L15" t="n">
-        <v>64.09999999999999</v>
+        <v>78.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>06:39:04</t>
+          <t>06:39:10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>3.76</v>
+        <v>3.42</v>
       </c>
       <c r="F16" t="n">
-        <v>7.8</v>
+        <v>5.52</v>
       </c>
       <c r="G16" t="n">
-        <v>126.9</v>
+        <v>126.4</v>
       </c>
       <c r="H16" t="n">
-        <v>78.40000000000001</v>
+        <v>19</v>
       </c>
       <c r="I16" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>1.11</v>
+        <v>-51.49</v>
       </c>
       <c r="K16" t="n">
-        <v>-76.36</v>
+        <v>14.89</v>
       </c>
       <c r="L16" t="n">
-        <v>76.37</v>
+        <v>53.6</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>06:42:51</t>
+          <t>06:42:08</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="F17" t="n">
-        <v>11.31</v>
+        <v>8.77</v>
       </c>
       <c r="G17" t="n">
-        <v>126.2</v>
+        <v>131.1</v>
       </c>
       <c r="H17" t="n">
-        <v>41.8</v>
+        <v>69.3</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J17" t="n">
-        <v>-19.64</v>
+        <v>28.89</v>
       </c>
       <c r="K17" t="n">
-        <v>-75.27</v>
+        <v>-110.36</v>
       </c>
       <c r="L17" t="n">
-        <v>77.79000000000001</v>
+        <v>114.08</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>06:44:34</t>
+          <t>06:43:13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>3.15</v>
+        <v>3.72</v>
       </c>
       <c r="F18" t="n">
-        <v>8.039999999999999</v>
+        <v>9.94</v>
       </c>
       <c r="G18" t="n">
-        <v>133.4</v>
+        <v>123</v>
       </c>
       <c r="H18" t="n">
-        <v>68.7</v>
+        <v>53</v>
       </c>
       <c r="I18" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-48.52</v>
+        <v>55.86</v>
       </c>
       <c r="K18" t="n">
-        <v>58.27</v>
+        <v>-38.68</v>
       </c>
       <c r="L18" t="n">
-        <v>75.81999999999999</v>
+        <v>67.94</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>06:46:46</t>
+          <t>06:45:05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>3.93</v>
+        <v>3.17</v>
       </c>
       <c r="F19" t="n">
-        <v>11.19</v>
+        <v>7.08</v>
       </c>
       <c r="G19" t="n">
-        <v>133.1</v>
+        <v>130.5</v>
       </c>
       <c r="H19" t="n">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="I19" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J19" t="n">
-        <v>-85.17</v>
+        <v>-82.84</v>
       </c>
       <c r="K19" t="n">
-        <v>109.2</v>
+        <v>-30.76</v>
       </c>
       <c r="L19" t="n">
-        <v>138.49</v>
+        <v>88.37</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>06:51:56</t>
+          <t>06:49:47</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>3.49</v>
+        <v>3.79</v>
       </c>
       <c r="F20" t="n">
-        <v>9.09</v>
+        <v>11.96</v>
       </c>
       <c r="G20" t="n">
-        <v>136.2</v>
+        <v>134.9</v>
       </c>
       <c r="H20" t="n">
-        <v>60</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>27.14</v>
+        <v>-138.76</v>
       </c>
       <c r="K20" t="n">
-        <v>-135.25</v>
+        <v>33.7</v>
       </c>
       <c r="L20" t="n">
-        <v>137.94</v>
+        <v>142.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>06:54:06</t>
+          <t>06:50:46</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>3.35</v>
+        <v>3.54</v>
       </c>
       <c r="F21" t="n">
-        <v>6.56</v>
+        <v>9.48</v>
       </c>
       <c r="G21" t="n">
-        <v>119.4</v>
+        <v>119.2</v>
       </c>
       <c r="H21" t="n">
-        <v>52.1</v>
+        <v>36.3</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>90.59</v>
+        <v>126.86</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4</v>
+        <v>59.08</v>
       </c>
       <c r="L21" t="n">
-        <v>90.62</v>
+        <v>139.94</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>06:55:13</t>
+          <t>06:51:41</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>3.34</v>
+        <v>3.92</v>
       </c>
       <c r="F22" t="n">
-        <v>7.32</v>
+        <v>8.41</v>
       </c>
       <c r="G22" t="n">
-        <v>128.2</v>
+        <v>116.8</v>
       </c>
       <c r="H22" t="n">
-        <v>64.3</v>
+        <v>53.7</v>
       </c>
       <c r="I22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.53</v>
+        <v>91.13</v>
       </c>
       <c r="K22" t="n">
-        <v>-120.68</v>
+        <v>107.62</v>
       </c>
       <c r="L22" t="n">
-        <v>120.68</v>
+        <v>141.02</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:00:47</t>
+          <t>06:57:12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>4.07</v>
+        <v>3.76</v>
       </c>
       <c r="F23" t="n">
-        <v>9.800000000000001</v>
+        <v>10.54</v>
       </c>
       <c r="G23" t="n">
-        <v>130.4</v>
+        <v>126.8</v>
       </c>
       <c r="H23" t="n">
-        <v>47.1</v>
+        <v>44.8</v>
       </c>
       <c r="I23" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>-174.58</v>
+        <v>27.87</v>
       </c>
       <c r="K23" t="n">
-        <v>-176.57</v>
+        <v>208.46</v>
       </c>
       <c r="L23" t="n">
-        <v>248.31</v>
+        <v>210.31</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:01:43</t>
+          <t>06:58:11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.59</v>
+        <v>3.83</v>
       </c>
       <c r="F24" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="G24" t="n">
-        <v>128.5</v>
+        <v>122.7</v>
       </c>
       <c r="H24" t="n">
-        <v>53.8</v>
+        <v>35</v>
       </c>
       <c r="I24" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J24" t="n">
-        <v>208.64</v>
+        <v>-8.26</v>
       </c>
       <c r="K24" t="n">
-        <v>110.98</v>
+        <v>-284.53</v>
       </c>
       <c r="L24" t="n">
-        <v>236.32</v>
+        <v>284.65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:03:26</t>
+          <t>07:00:44</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>4.01</v>
+        <v>3.43</v>
       </c>
       <c r="F25" t="n">
-        <v>10.14</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>149.1</v>
+        <v>129.5</v>
       </c>
       <c r="H25" t="n">
-        <v>69.2</v>
+        <v>48.6</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J25" t="n">
-        <v>-155.41</v>
+        <v>-135.67</v>
       </c>
       <c r="K25" t="n">
-        <v>-253.61</v>
+        <v>-98.79000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>297.44</v>
+        <v>167.82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:09:47</t>
+          <t>07:04:40</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>3.46</v>
+        <v>3.32</v>
       </c>
       <c r="F26" t="n">
-        <v>7.61</v>
+        <v>4.84</v>
       </c>
       <c r="G26" t="n">
-        <v>128.3</v>
+        <v>132.5</v>
       </c>
       <c r="H26" t="n">
-        <v>57.7</v>
+        <v>45.5</v>
       </c>
       <c r="I26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>194.92</v>
+        <v>27.99</v>
       </c>
       <c r="K26" t="n">
-        <v>-182.46</v>
+        <v>-183.97</v>
       </c>
       <c r="L26" t="n">
-        <v>266.99</v>
+        <v>186.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:12:09</t>
+          <t>07:05:54</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="F27" t="n">
-        <v>8.9</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>128.9</v>
+        <v>129.4</v>
       </c>
       <c r="H27" t="n">
-        <v>57</v>
+        <v>70.8</v>
       </c>
       <c r="I27" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-127.3</v>
+        <v>-81.58</v>
       </c>
       <c r="K27" t="n">
-        <v>-149.03</v>
+        <v>-277.49</v>
       </c>
       <c r="L27" t="n">
-        <v>196</v>
+        <v>289.23</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:14:00</t>
+          <t>07:07:50</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>4.74</v>
+        <v>3.46</v>
       </c>
       <c r="F28" t="n">
-        <v>11.96</v>
+        <v>5.66</v>
       </c>
       <c r="G28" t="n">
-        <v>148.6</v>
+        <v>124.7</v>
       </c>
       <c r="H28" t="n">
-        <v>52.1</v>
+        <v>69</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>-226.83</v>
+        <v>13.9</v>
       </c>
       <c r="K28" t="n">
-        <v>-159.13</v>
+        <v>-241.21</v>
       </c>
       <c r="L28" t="n">
-        <v>277.09</v>
+        <v>241.61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:24:24</t>
+          <t>07:20:41</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>4.11</v>
+        <v>3.44</v>
       </c>
       <c r="F29" t="n">
-        <v>11.95</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G29" t="n">
-        <v>132.7</v>
+        <v>122.3</v>
       </c>
       <c r="H29" t="n">
-        <v>2.3</v>
+        <v>73.8</v>
       </c>
       <c r="I29" t="n">
         <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>51.72</v>
+        <v>53.87</v>
       </c>
       <c r="K29" t="n">
-        <v>-42.96</v>
+        <v>15.28</v>
       </c>
       <c r="L29" t="n">
-        <v>67.23999999999999</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:26:44</t>
+          <t>07:23:14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>4.19</v>
+        <v>3.57</v>
       </c>
       <c r="F30" t="n">
-        <v>11.96</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>129.8</v>
+        <v>132.3</v>
       </c>
       <c r="H30" t="n">
-        <v>46.6</v>
+        <v>70.2</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J30" t="n">
-        <v>83.28</v>
+        <v>26.29</v>
       </c>
       <c r="K30" t="n">
-        <v>13.45</v>
+        <v>56.48</v>
       </c>
       <c r="L30" t="n">
-        <v>84.34999999999999</v>
+        <v>62.3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>07:28:28</t>
+          <t>07:24:40</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>4.26</v>
+        <v>3.76</v>
       </c>
       <c r="F31" t="n">
-        <v>11.96</v>
+        <v>9.91</v>
       </c>
       <c r="G31" t="n">
-        <v>138.3</v>
+        <v>126.9</v>
       </c>
       <c r="H31" t="n">
-        <v>28.2</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-37.19</v>
+        <v>-16.08</v>
       </c>
       <c r="K31" t="n">
-        <v>22.62</v>
+        <v>-73.31999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>43.53</v>
+        <v>75.06999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>07:34:09</t>
+          <t>07:29:18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>4.08</v>
+        <v>4.17</v>
       </c>
       <c r="F32" t="n">
-        <v>9.43</v>
+        <v>11.96</v>
       </c>
       <c r="G32" t="n">
-        <v>138.2</v>
+        <v>127.1</v>
       </c>
       <c r="H32" t="n">
-        <v>56.8</v>
+        <v>44.1</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J32" t="n">
-        <v>-76.95</v>
+        <v>86.12</v>
       </c>
       <c r="K32" t="n">
-        <v>-55.07</v>
+        <v>-34.69</v>
       </c>
       <c r="L32" t="n">
-        <v>94.63</v>
+        <v>92.84999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>07:35:36</t>
+          <t>07:31:40</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>3.45</v>
+        <v>4.23</v>
       </c>
       <c r="F33" t="n">
-        <v>8.029999999999999</v>
+        <v>9.91</v>
       </c>
       <c r="G33" t="n">
-        <v>130.2</v>
+        <v>133.4</v>
       </c>
       <c r="H33" t="n">
-        <v>38.3</v>
+        <v>68.7</v>
       </c>
       <c r="I33" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J33" t="n">
-        <v>82.43000000000001</v>
+        <v>-67.05</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.05</v>
+        <v>77.41</v>
       </c>
       <c r="L33" t="n">
-        <v>82.43000000000001</v>
+        <v>102.41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>07:37:22</t>
+          <t>07:32:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>3.43</v>
+        <v>4.14</v>
       </c>
       <c r="F34" t="n">
-        <v>8.48</v>
+        <v>11.96</v>
       </c>
       <c r="G34" t="n">
-        <v>127.7</v>
+        <v>138</v>
       </c>
       <c r="H34" t="n">
-        <v>64.7</v>
+        <v>26.3</v>
       </c>
       <c r="I34" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J34" t="n">
-        <v>101.15</v>
+        <v>36.67</v>
       </c>
       <c r="K34" t="n">
-        <v>9.67</v>
+        <v>15.3</v>
       </c>
       <c r="L34" t="n">
-        <v>101.61</v>
+        <v>39.74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>07:41:51</t>
+          <t>07:38:27</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>3.65</v>
+        <v>4.19</v>
       </c>
       <c r="F35" t="n">
-        <v>9.289999999999999</v>
+        <v>10.07</v>
       </c>
       <c r="G35" t="n">
-        <v>126.9</v>
+        <v>134.4</v>
       </c>
       <c r="H35" t="n">
-        <v>45.7</v>
+        <v>49.2</v>
       </c>
       <c r="I35" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J35" t="n">
-        <v>76.66</v>
+        <v>-154.22</v>
       </c>
       <c r="K35" t="n">
-        <v>-46.2</v>
+        <v>-61.46</v>
       </c>
       <c r="L35" t="n">
-        <v>89.5</v>
+        <v>166.02</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>07:44:27</t>
+          <t>07:39:29</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4.65</v>
+        <v>4.23</v>
       </c>
       <c r="F36" t="n">
-        <v>10.62</v>
+        <v>9.08</v>
       </c>
       <c r="G36" t="n">
-        <v>142.7</v>
+        <v>147.6</v>
       </c>
       <c r="H36" t="n">
-        <v>53.8</v>
+        <v>21.3</v>
       </c>
       <c r="I36" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J36" t="n">
-        <v>164.4</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-7.14</v>
+        <v>-113.15</v>
       </c>
       <c r="L36" t="n">
-        <v>164.55</v>
+        <v>134</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>07:46:38</t>
+          <t>07:40:21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>4.19</v>
+        <v>3.54</v>
       </c>
       <c r="F37" t="n">
-        <v>11.96</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="G37" t="n">
-        <v>135.1</v>
+        <v>121.6</v>
       </c>
       <c r="H37" t="n">
-        <v>28.5</v>
+        <v>44.5</v>
       </c>
       <c r="I37" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J37" t="n">
-        <v>-142.6</v>
+        <v>108.16</v>
       </c>
       <c r="K37" t="n">
-        <v>108.3</v>
+        <v>-31.34</v>
       </c>
       <c r="L37" t="n">
-        <v>179.06</v>
+        <v>112.61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>07:52:00</t>
+          <t>07:44:16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>4.35</v>
+        <v>4.1</v>
       </c>
       <c r="F38" t="n">
-        <v>11.96</v>
+        <v>7.9</v>
       </c>
       <c r="G38" t="n">
-        <v>122.5</v>
+        <v>130.4</v>
       </c>
       <c r="H38" t="n">
-        <v>63.7</v>
+        <v>47.1</v>
       </c>
       <c r="I38" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J38" t="n">
-        <v>167.04</v>
+        <v>-234.38</v>
       </c>
       <c r="K38" t="n">
-        <v>-48.57</v>
+        <v>-133.1</v>
       </c>
       <c r="L38" t="n">
-        <v>173.95</v>
+        <v>269.53</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>07:53:23</t>
+          <t>07:45:28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>4.03</v>
+        <v>3.79</v>
       </c>
       <c r="F39" t="n">
-        <v>11.96</v>
+        <v>9.82</v>
       </c>
       <c r="G39" t="n">
-        <v>131.8</v>
+        <v>123.6</v>
       </c>
       <c r="H39" t="n">
-        <v>58.9</v>
+        <v>45.4</v>
       </c>
       <c r="I39" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J39" t="n">
-        <v>46.74</v>
+        <v>231.2</v>
       </c>
       <c r="K39" t="n">
-        <v>215.64</v>
+        <v>-23.12</v>
       </c>
       <c r="L39" t="n">
-        <v>220.65</v>
+        <v>232.35</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>07:55:36</t>
+          <t>07:47:31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>3.71</v>
+        <v>3.58</v>
       </c>
       <c r="F40" t="n">
-        <v>11.96</v>
+        <v>10.04</v>
       </c>
       <c r="G40" t="n">
-        <v>133.4</v>
+        <v>149.1</v>
       </c>
       <c r="H40" t="n">
-        <v>9.4</v>
+        <v>69.2</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J40" t="n">
-        <v>191.11</v>
+        <v>-176.84</v>
       </c>
       <c r="K40" t="n">
-        <v>159.13</v>
+        <v>-178.69</v>
       </c>
       <c r="L40" t="n">
-        <v>248.68</v>
+        <v>251.4</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:00:20</t>
+          <t>07:53:13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>4.07</v>
+        <v>3.65</v>
       </c>
       <c r="F41" t="n">
-        <v>10.61</v>
+        <v>8.4</v>
       </c>
       <c r="G41" t="n">
-        <v>129.2</v>
+        <v>125.6</v>
       </c>
       <c r="H41" t="n">
-        <v>19.2</v>
+        <v>44.8</v>
       </c>
       <c r="I41" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J41" t="n">
-        <v>-119.21</v>
+        <v>-151.05</v>
       </c>
       <c r="K41" t="n">
-        <v>-128.47</v>
+        <v>228.44</v>
       </c>
       <c r="L41" t="n">
-        <v>175.26</v>
+        <v>273.87</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:01:47</t>
+          <t>07:54:50</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>4.55</v>
+        <v>3.98</v>
       </c>
       <c r="F42" t="n">
-        <v>11.96</v>
+        <v>10.57</v>
       </c>
       <c r="G42" t="n">
-        <v>124.9</v>
+        <v>121</v>
       </c>
       <c r="H42" t="n">
-        <v>41.1</v>
+        <v>56.3</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J42" t="n">
-        <v>251.46</v>
+        <v>172.9</v>
       </c>
       <c r="K42" t="n">
-        <v>-227.64</v>
+        <v>258.2</v>
       </c>
       <c r="L42" t="n">
-        <v>339.2</v>
+        <v>310.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:03:40</t>
+          <t>07:56:30</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>3.87</v>
+        <v>3.99</v>
       </c>
       <c r="F43" t="n">
-        <v>8.57</v>
+        <v>11.06</v>
       </c>
       <c r="G43" t="n">
-        <v>120.5</v>
+        <v>153.5</v>
       </c>
       <c r="H43" t="n">
-        <v>86.5</v>
+        <v>24.9</v>
       </c>
       <c r="I43" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J43" t="n">
-        <v>132.41</v>
+        <v>81.77</v>
       </c>
       <c r="K43" t="n">
-        <v>-111.02</v>
+        <v>216.08</v>
       </c>
       <c r="L43" t="n">
-        <v>172.79</v>
+        <v>231.03</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:15:34</t>
+          <t>08:06:13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="F44" t="n">
-        <v>11.92</v>
+        <v>8</v>
       </c>
       <c r="G44" t="n">
-        <v>133.4</v>
+        <v>127.9</v>
       </c>
       <c r="H44" t="n">
-        <v>26</v>
+        <v>55.9</v>
       </c>
       <c r="I44" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J44" t="n">
-        <v>46.17</v>
+        <v>37.55</v>
       </c>
       <c r="K44" t="n">
-        <v>84.48999999999999</v>
+        <v>-59.64</v>
       </c>
       <c r="L44" t="n">
-        <v>96.28</v>
+        <v>70.47</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:18:02</t>
+          <t>08:07:35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>4.27</v>
+        <v>4.09</v>
       </c>
       <c r="F45" t="n">
         <v>11.96</v>
       </c>
       <c r="G45" t="n">
-        <v>123.9</v>
+        <v>129.8</v>
       </c>
       <c r="H45" t="n">
-        <v>9.9</v>
+        <v>46.6</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-45.27</v>
+        <v>71.41</v>
       </c>
       <c r="K45" t="n">
-        <v>76.73999999999999</v>
+        <v>30.38</v>
       </c>
       <c r="L45" t="n">
-        <v>89.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:19:25</t>
+          <t>08:08:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>3.89</v>
+        <v>4.43</v>
       </c>
       <c r="F46" t="n">
-        <v>10.81</v>
+        <v>11.96</v>
       </c>
       <c r="G46" t="n">
-        <v>127.1</v>
+        <v>121.6</v>
       </c>
       <c r="H46" t="n">
-        <v>9.9</v>
+        <v>29.2</v>
       </c>
       <c r="I46" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J46" t="n">
-        <v>29.88</v>
+        <v>61.53</v>
       </c>
       <c r="K46" t="n">
-        <v>62.87</v>
+        <v>2.58</v>
       </c>
       <c r="L46" t="n">
-        <v>69.61</v>
+        <v>61.59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:23:43</t>
+          <t>08:14:09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>4.01</v>
+        <v>3.74</v>
       </c>
       <c r="F47" t="n">
-        <v>8.69</v>
+        <v>10.89</v>
       </c>
       <c r="G47" t="n">
-        <v>141.6</v>
+        <v>132.1</v>
       </c>
       <c r="H47" t="n">
-        <v>88</v>
+        <v>41.9</v>
       </c>
       <c r="I47" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-75.37</v>
+        <v>-60.79</v>
       </c>
       <c r="K47" t="n">
-        <v>81.13</v>
+        <v>-32.04</v>
       </c>
       <c r="L47" t="n">
-        <v>110.74</v>
+        <v>68.70999999999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:25:45</t>
+          <t>08:15:54</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>4.3</v>
+        <v>3.92</v>
       </c>
       <c r="F48" t="n">
-        <v>11.96</v>
+        <v>10.51</v>
       </c>
       <c r="G48" t="n">
-        <v>116.1</v>
+        <v>128.6</v>
       </c>
       <c r="H48" t="n">
-        <v>76.90000000000001</v>
+        <v>43.4</v>
       </c>
       <c r="I48" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>6.16</v>
+        <v>48.71</v>
       </c>
       <c r="K48" t="n">
-        <v>-81.84999999999999</v>
+        <v>-69.11</v>
       </c>
       <c r="L48" t="n">
-        <v>82.08</v>
+        <v>84.55</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:28:01</t>
+          <t>08:18:02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>3.89</v>
+        <v>4.37</v>
       </c>
       <c r="F49" t="n">
-        <v>10.58</v>
+        <v>10.73</v>
       </c>
       <c r="G49" t="n">
-        <v>136.6</v>
+        <v>125.7</v>
       </c>
       <c r="H49" t="n">
-        <v>42.8</v>
+        <v>34.4</v>
       </c>
       <c r="I49" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J49" t="n">
-        <v>-79.3</v>
+        <v>30.03</v>
       </c>
       <c r="K49" t="n">
-        <v>-46.37</v>
+        <v>-91.40000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>91.86</v>
+        <v>96.2</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:33:47</t>
+          <t>08:21:53</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>4.53</v>
+        <v>4.01</v>
       </c>
       <c r="F50" t="n">
-        <v>11.74</v>
+        <v>10.79</v>
       </c>
       <c r="G50" t="n">
-        <v>134.6</v>
+        <v>117.4</v>
       </c>
       <c r="H50" t="n">
-        <v>98.7</v>
+        <v>41.3</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J50" t="n">
-        <v>87.59</v>
+        <v>71.97</v>
       </c>
       <c r="K50" t="n">
-        <v>-108.14</v>
+        <v>-93.52</v>
       </c>
       <c r="L50" t="n">
-        <v>139.16</v>
+        <v>118.01</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:34:57</t>
+          <t>08:24:23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>3.95</v>
+        <v>3.89</v>
       </c>
       <c r="F51" t="n">
-        <v>10.04</v>
+        <v>11.12</v>
       </c>
       <c r="G51" t="n">
-        <v>113.6</v>
+        <v>119.4</v>
       </c>
       <c r="H51" t="n">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="I51" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J51" t="n">
-        <v>-124.22</v>
+        <v>113.59</v>
       </c>
       <c r="K51" t="n">
-        <v>-3.09</v>
+        <v>87.70999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>124.26</v>
+        <v>143.52</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:36:44</t>
+          <t>08:26:43</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>3.9</v>
+        <v>4.35</v>
       </c>
       <c r="F52" t="n">
-        <v>9.460000000000001</v>
+        <v>11.96</v>
       </c>
       <c r="G52" t="n">
-        <v>133.8</v>
+        <v>121.8</v>
       </c>
       <c r="H52" t="n">
-        <v>44.8</v>
+        <v>63.2</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J52" t="n">
-        <v>-60.75</v>
+        <v>-89.88</v>
       </c>
       <c r="K52" t="n">
-        <v>-104.06</v>
+        <v>-139.32</v>
       </c>
       <c r="L52" t="n">
-        <v>120.49</v>
+        <v>165.8</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>08:42:31</t>
+          <t>08:32:16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>4.07</v>
+        <v>3.19</v>
       </c>
       <c r="F53" t="n">
-        <v>10.74</v>
+        <v>10.09</v>
       </c>
       <c r="G53" t="n">
-        <v>136.3</v>
+        <v>135.4</v>
       </c>
       <c r="H53" t="n">
-        <v>55.4</v>
+        <v>24.6</v>
       </c>
       <c r="I53" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J53" t="n">
-        <v>183.74</v>
+        <v>131.4</v>
       </c>
       <c r="K53" t="n">
-        <v>200.41</v>
+        <v>139.41</v>
       </c>
       <c r="L53" t="n">
-        <v>271.89</v>
+        <v>191.57</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>08:43:26</t>
+          <t>08:34:31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>3.43</v>
+        <v>3.82</v>
       </c>
       <c r="F54" t="n">
-        <v>8.08</v>
+        <v>10.76</v>
       </c>
       <c r="G54" t="n">
-        <v>119.5</v>
+        <v>138.9</v>
       </c>
       <c r="H54" t="n">
-        <v>45.7</v>
+        <v>42</v>
       </c>
       <c r="I54" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J54" t="n">
-        <v>227.73</v>
+        <v>205.36</v>
       </c>
       <c r="K54" t="n">
-        <v>1.85</v>
+        <v>91.34999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>227.73</v>
+        <v>224.76</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>08:44:58</t>
+          <t>08:36:46</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>3.15</v>
+        <v>4.04</v>
       </c>
       <c r="F55" t="n">
-        <v>7.81</v>
+        <v>11.19</v>
       </c>
       <c r="G55" t="n">
-        <v>124.9</v>
+        <v>140.9</v>
       </c>
       <c r="H55" t="n">
-        <v>34.1</v>
+        <v>36.6</v>
       </c>
       <c r="I55" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>138.02</v>
+        <v>-56.53</v>
       </c>
       <c r="K55" t="n">
-        <v>-74.84</v>
+        <v>-263.6</v>
       </c>
       <c r="L55" t="n">
-        <v>157</v>
+        <v>269.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>08:48:31</t>
+          <t>08:42:04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>4.63</v>
+        <v>4.23</v>
       </c>
       <c r="F56" t="n">
         <v>11.96</v>
       </c>
       <c r="G56" t="n">
-        <v>144.8</v>
+        <v>127.7</v>
       </c>
       <c r="H56" t="n">
-        <v>65.90000000000001</v>
+        <v>57</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>306.82</v>
+        <v>-227.56</v>
       </c>
       <c r="K56" t="n">
-        <v>10.15</v>
+        <v>184.93</v>
       </c>
       <c r="L56" t="n">
-        <v>306.99</v>
+        <v>293.23</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>08:49:30</t>
+          <t>08:44:10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>4.47</v>
+        <v>4.39</v>
       </c>
       <c r="F57" t="n">
-        <v>11.96</v>
+        <v>11.9</v>
       </c>
       <c r="G57" t="n">
-        <v>130.8</v>
+        <v>131.5</v>
       </c>
       <c r="H57" t="n">
-        <v>27.8</v>
+        <v>70.3</v>
       </c>
       <c r="I57" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J57" t="n">
-        <v>-177.38</v>
+        <v>-131.6</v>
       </c>
       <c r="K57" t="n">
-        <v>-152.98</v>
+        <v>299.46</v>
       </c>
       <c r="L57" t="n">
-        <v>234.23</v>
+        <v>327.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>08:50:54</t>
+          <t>08:45:44</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>4.51</v>
+        <v>4.04</v>
       </c>
       <c r="F58" t="n">
-        <v>9.869999999999999</v>
+        <v>10.48</v>
       </c>
       <c r="G58" t="n">
-        <v>114.7</v>
+        <v>119.9</v>
       </c>
       <c r="H58" t="n">
-        <v>42.3</v>
+        <v>43.8</v>
       </c>
       <c r="I58" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>188.56</v>
+        <v>-233.29</v>
       </c>
       <c r="K58" t="n">
-        <v>77.84</v>
+        <v>31.36</v>
       </c>
       <c r="L58" t="n">
-        <v>203.99</v>
+        <v>235.39</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>08:59:39</t>
+          <t>08:56:47</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>4.21</v>
+        <v>4.34</v>
       </c>
       <c r="F59" t="n">
         <v>11.96</v>
       </c>
       <c r="G59" t="n">
-        <v>129.4</v>
+        <v>130.3</v>
       </c>
       <c r="H59" t="n">
-        <v>55.4</v>
+        <v>48</v>
       </c>
       <c r="I59" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>-74.69</v>
+        <v>0.88</v>
       </c>
       <c r="K59" t="n">
-        <v>12.68</v>
+        <v>-137.12</v>
       </c>
       <c r="L59" t="n">
-        <v>75.76000000000001</v>
+        <v>137.12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:01:10</t>
+          <t>08:58:43</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>4.55</v>
+        <v>4.44</v>
       </c>
       <c r="F60" t="n">
         <v>11.96</v>
       </c>
       <c r="G60" t="n">
-        <v>121.9</v>
+        <v>133.9</v>
       </c>
       <c r="H60" t="n">
-        <v>28.1</v>
+        <v>86.7</v>
       </c>
       <c r="I60" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J60" t="n">
-        <v>110.9</v>
+        <v>-64.38</v>
       </c>
       <c r="K60" t="n">
-        <v>-10.11</v>
+        <v>33.12</v>
       </c>
       <c r="L60" t="n">
-        <v>111.36</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:03:15</t>
+          <t>09:00:38</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>4.44</v>
+        <v>3.95</v>
       </c>
       <c r="F61" t="n">
-        <v>10.28</v>
+        <v>11.6</v>
       </c>
       <c r="G61" t="n">
-        <v>115.6</v>
+        <v>130.4</v>
       </c>
       <c r="H61" t="n">
-        <v>36.6</v>
+        <v>17.8</v>
       </c>
       <c r="I61" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J61" t="n">
-        <v>60.38</v>
+        <v>-43.47</v>
       </c>
       <c r="K61" t="n">
-        <v>-54.4</v>
+        <v>-64.59999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>81.28</v>
+        <v>77.86</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:08:16</t>
+          <t>09:05:02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>3.92</v>
+        <v>3.63</v>
       </c>
       <c r="F62" t="n">
-        <v>11.66</v>
+        <v>11.96</v>
       </c>
       <c r="G62" t="n">
-        <v>136.7</v>
+        <v>127.2</v>
       </c>
       <c r="H62" t="n">
-        <v>30.8</v>
+        <v>26.9</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>-60.15</v>
+        <v>71.48</v>
       </c>
       <c r="K62" t="n">
-        <v>-40</v>
+        <v>11.87</v>
       </c>
       <c r="L62" t="n">
-        <v>72.23999999999999</v>
+        <v>72.45999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:09:12</t>
+          <t>09:07:40</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>4.15</v>
+        <v>4.77</v>
       </c>
       <c r="F63" t="n">
-        <v>8.859999999999999</v>
+        <v>11.96</v>
       </c>
       <c r="G63" t="n">
-        <v>134.8</v>
+        <v>118.8</v>
       </c>
       <c r="H63" t="n">
-        <v>49.5</v>
+        <v>65.2</v>
       </c>
       <c r="I63" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J63" t="n">
-        <v>86.8</v>
+        <v>-37.49</v>
       </c>
       <c r="K63" t="n">
-        <v>-28.36</v>
+        <v>110.04</v>
       </c>
       <c r="L63" t="n">
-        <v>91.31999999999999</v>
+        <v>116.25</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:11:37</t>
+          <t>09:09:10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>4.72</v>
+        <v>4.98</v>
       </c>
       <c r="F64" t="n">
-        <v>10.03</v>
+        <v>11.96</v>
       </c>
       <c r="G64" t="n">
-        <v>142.5</v>
+        <v>127.6</v>
       </c>
       <c r="H64" t="n">
-        <v>62.4</v>
+        <v>33.5</v>
       </c>
       <c r="I64" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>146.72</v>
+        <v>8.01</v>
       </c>
       <c r="K64" t="n">
-        <v>45.94</v>
+        <v>-135.54</v>
       </c>
       <c r="L64" t="n">
-        <v>153.75</v>
+        <v>135.78</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:15:06</t>
+          <t>09:13:02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>4.47</v>
+        <v>4.11</v>
       </c>
       <c r="F65" t="n">
-        <v>10.7</v>
+        <v>11.96</v>
       </c>
       <c r="G65" t="n">
-        <v>138.2</v>
+        <v>133.7</v>
       </c>
       <c r="H65" t="n">
-        <v>52.1</v>
+        <v>49.1</v>
       </c>
       <c r="I65" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>141.77</v>
+        <v>24.43</v>
       </c>
       <c r="K65" t="n">
-        <v>42.73</v>
+        <v>131.67</v>
       </c>
       <c r="L65" t="n">
-        <v>148.07</v>
+        <v>133.92</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:16:27</t>
+          <t>09:13:38</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.77</v>
+        <v>4.51</v>
       </c>
       <c r="F66" t="n">
-        <v>10.28</v>
+        <v>11.28</v>
       </c>
       <c r="G66" t="n">
-        <v>121.2</v>
+        <v>131</v>
       </c>
       <c r="H66" t="n">
-        <v>66.8</v>
+        <v>23.1</v>
       </c>
       <c r="I66" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>139.2</v>
+        <v>-12.77</v>
       </c>
       <c r="K66" t="n">
-        <v>-16.56</v>
+        <v>-227.33</v>
       </c>
       <c r="L66" t="n">
-        <v>140.18</v>
+        <v>227.69</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:19:03</t>
+          <t>09:16:14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>4.78</v>
+        <v>4.52</v>
       </c>
       <c r="F67" t="n">
-        <v>11.96</v>
+        <v>11.2</v>
       </c>
       <c r="G67" t="n">
-        <v>113.9</v>
+        <v>129.3</v>
       </c>
       <c r="H67" t="n">
-        <v>39</v>
+        <v>25.7</v>
       </c>
       <c r="I67" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>221.3</v>
+        <v>142.97</v>
       </c>
       <c r="K67" t="n">
-        <v>-19.41</v>
+        <v>23.46</v>
       </c>
       <c r="L67" t="n">
-        <v>222.15</v>
+        <v>144.89</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:23:35</t>
+          <t>09:20:30</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>4.08</v>
+        <v>4.49</v>
       </c>
       <c r="F68" t="n">
         <v>11.96</v>
       </c>
       <c r="G68" t="n">
-        <v>133.8</v>
+        <v>118</v>
       </c>
       <c r="H68" t="n">
-        <v>30.9</v>
+        <v>23.9</v>
       </c>
       <c r="I68" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J68" t="n">
-        <v>221.38</v>
+        <v>-126.78</v>
       </c>
       <c r="K68" t="n">
-        <v>78.73</v>
+        <v>216.64</v>
       </c>
       <c r="L68" t="n">
-        <v>234.96</v>
+        <v>251.01</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:25:09</t>
+          <t>09:22:17</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>4.16</v>
+        <v>4.45</v>
       </c>
       <c r="F69" t="n">
-        <v>11.39</v>
+        <v>11.96</v>
       </c>
       <c r="G69" t="n">
-        <v>121.4</v>
+        <v>119.5</v>
       </c>
       <c r="H69" t="n">
-        <v>35.1</v>
+        <v>65.8</v>
       </c>
       <c r="I69" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J69" t="n">
-        <v>382.13</v>
+        <v>10.99</v>
       </c>
       <c r="K69" t="n">
-        <v>-50.65</v>
+        <v>176.6</v>
       </c>
       <c r="L69" t="n">
-        <v>385.47</v>
+        <v>176.95</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:27:07</t>
+          <t>09:23:52</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>3.8</v>
+        <v>3.91</v>
       </c>
       <c r="F70" t="n">
-        <v>8.869999999999999</v>
+        <v>11.96</v>
       </c>
       <c r="G70" t="n">
-        <v>133.9</v>
+        <v>128.4</v>
       </c>
       <c r="H70" t="n">
-        <v>64.8</v>
+        <v>74.3</v>
       </c>
       <c r="I70" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J70" t="n">
-        <v>82.13</v>
+        <v>-75.25</v>
       </c>
       <c r="K70" t="n">
-        <v>-193.85</v>
+        <v>-102.75</v>
       </c>
       <c r="L70" t="n">
-        <v>210.52</v>
+        <v>127.36</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:32:46</t>
+          <t>09:29:30</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>4.21</v>
+        <v>4.11</v>
       </c>
       <c r="F71" t="n">
-        <v>11.96</v>
+        <v>10.57</v>
       </c>
       <c r="G71" t="n">
-        <v>140.4</v>
+        <v>131.6</v>
       </c>
       <c r="H71" t="n">
-        <v>65.40000000000001</v>
+        <v>35.6</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>-267.71</v>
+        <v>-49.83</v>
       </c>
       <c r="K71" t="n">
-        <v>5.97</v>
+        <v>-348.49</v>
       </c>
       <c r="L71" t="n">
-        <v>267.78</v>
+        <v>352.03</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:34:01</t>
+          <t>09:32:06</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>4.02</v>
+        <v>4.99</v>
       </c>
       <c r="F72" t="n">
-        <v>10.97</v>
+        <v>11.13</v>
       </c>
       <c r="G72" t="n">
-        <v>146.8</v>
+        <v>122.9</v>
       </c>
       <c r="H72" t="n">
-        <v>57.8</v>
+        <v>29.2</v>
       </c>
       <c r="I72" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J72" t="n">
-        <v>-175.49</v>
+        <v>-350.33</v>
       </c>
       <c r="K72" t="n">
-        <v>-194.67</v>
+        <v>-192.98</v>
       </c>
       <c r="L72" t="n">
-        <v>262.09</v>
+        <v>399.96</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:35:09</t>
+          <t>09:33:01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>3.87</v>
+        <v>4.02</v>
       </c>
       <c r="F73" t="n">
-        <v>11.38</v>
+        <v>10.45</v>
       </c>
       <c r="G73" t="n">
-        <v>139</v>
+        <v>126.6</v>
       </c>
       <c r="H73" t="n">
-        <v>40.1</v>
+        <v>19.4</v>
       </c>
       <c r="I73" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>-82.47</v>
+        <v>-156.88</v>
       </c>
       <c r="K73" t="n">
-        <v>-236.18</v>
+        <v>-147.71</v>
       </c>
       <c r="L73" t="n">
-        <v>250.16</v>
+        <v>215.47</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>09:43:55</t>
+          <t>09:42:19</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>4.94</v>
+        <v>3.87</v>
       </c>
       <c r="F74" t="n">
-        <v>11.96</v>
+        <v>11.63</v>
       </c>
       <c r="G74" t="n">
-        <v>118.4</v>
+        <v>148</v>
       </c>
       <c r="H74" t="n">
-        <v>22.4</v>
+        <v>45.7</v>
       </c>
       <c r="I74" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J74" t="n">
-        <v>63.9</v>
+        <v>-36.61</v>
       </c>
       <c r="K74" t="n">
-        <v>-73.37</v>
+        <v>-66.68000000000001</v>
       </c>
       <c r="L74" t="n">
-        <v>97.3</v>
+        <v>76.06999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>09:44:44</t>
+          <t>09:44:35</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>4.03</v>
+        <v>4.17</v>
       </c>
       <c r="F75" t="n">
-        <v>5.72</v>
+        <v>10.76</v>
       </c>
       <c r="G75" t="n">
-        <v>137.6</v>
+        <v>123.2</v>
       </c>
       <c r="H75" t="n">
-        <v>5.1</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J75" t="n">
-        <v>43.67</v>
+        <v>6.97</v>
       </c>
       <c r="K75" t="n">
-        <v>-55.9</v>
+        <v>68.89</v>
       </c>
       <c r="L75" t="n">
-        <v>70.94</v>
+        <v>69.23999999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>09:46:17</t>
+          <t>09:45:21</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>3.58</v>
+        <v>4.32</v>
       </c>
       <c r="F76" t="n">
-        <v>11.13</v>
+        <v>9.31</v>
       </c>
       <c r="G76" t="n">
-        <v>127.3</v>
+        <v>122.3</v>
       </c>
       <c r="H76" t="n">
-        <v>85.3</v>
+        <v>59.2</v>
       </c>
       <c r="I76" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-40.98</v>
+        <v>15.98</v>
       </c>
       <c r="K76" t="n">
-        <v>-47.12</v>
+        <v>-77.68000000000001</v>
       </c>
       <c r="L76" t="n">
-        <v>62.45</v>
+        <v>79.3</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>09:52:29</t>
+          <t>09:50:40</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>4.31</v>
+        <v>4.11</v>
       </c>
       <c r="F77" t="n">
-        <v>9.460000000000001</v>
+        <v>11.65</v>
       </c>
       <c r="G77" t="n">
-        <v>125.4</v>
+        <v>129.6</v>
       </c>
       <c r="H77" t="n">
-        <v>28.6</v>
+        <v>26.7</v>
       </c>
       <c r="I77" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>253.32</v>
+        <v>-117.06</v>
       </c>
       <c r="K77" t="n">
-        <v>-94.59</v>
+        <v>20.07</v>
       </c>
       <c r="L77" t="n">
-        <v>270.41</v>
+        <v>118.77</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>09:54:09</t>
+          <t>09:52:23</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>4.24</v>
+        <v>4.09</v>
       </c>
       <c r="F78" t="n">
         <v>11.96</v>
       </c>
       <c r="G78" t="n">
-        <v>124.1</v>
+        <v>122.9</v>
       </c>
       <c r="H78" t="n">
-        <v>66</v>
+        <v>40.2</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J78" t="n">
-        <v>128.1</v>
+        <v>99.70999999999999</v>
       </c>
       <c r="K78" t="n">
-        <v>88.83</v>
+        <v>-34.39</v>
       </c>
       <c r="L78" t="n">
-        <v>155.89</v>
+        <v>105.47</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>09:56:52</t>
+          <t>09:54:08</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>3.89</v>
+        <v>4.02</v>
       </c>
       <c r="F79" t="n">
-        <v>6.55</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="G79" t="n">
-        <v>132.2</v>
+        <v>128.8</v>
       </c>
       <c r="H79" t="n">
-        <v>21.3</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I79" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>5.2</v>
+        <v>103.01</v>
       </c>
       <c r="K79" t="n">
-        <v>-100.39</v>
+        <v>-71.09999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>100.53</v>
+        <v>125.16</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:01:09</t>
+          <t>09:57:11</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>3.99</v>
+        <v>5</v>
       </c>
       <c r="F80" t="n">
-        <v>10.68</v>
+        <v>11.38</v>
       </c>
       <c r="G80" t="n">
-        <v>113.8</v>
+        <v>130.9</v>
       </c>
       <c r="H80" t="n">
-        <v>27.6</v>
+        <v>58.4</v>
       </c>
       <c r="I80" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>147.8</v>
+        <v>133.31</v>
       </c>
       <c r="K80" t="n">
-        <v>24.99</v>
+        <v>-163.22</v>
       </c>
       <c r="L80" t="n">
-        <v>149.9</v>
+        <v>210.74</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:02:21</t>
+          <t>09:58:33</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>4.44</v>
+        <v>4.05</v>
       </c>
       <c r="F81" t="n">
-        <v>10.55</v>
+        <v>11.96</v>
       </c>
       <c r="G81" t="n">
-        <v>119.9</v>
+        <v>135.3</v>
       </c>
       <c r="H81" t="n">
-        <v>64.3</v>
+        <v>15.9</v>
       </c>
       <c r="I81" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J81" t="n">
-        <v>82.20999999999999</v>
+        <v>-124.93</v>
       </c>
       <c r="K81" t="n">
-        <v>-109.09</v>
+        <v>-19.93</v>
       </c>
       <c r="L81" t="n">
-        <v>136.6</v>
+        <v>126.51</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:03:38</t>
+          <t>10:00:00</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>5.15</v>
+        <v>3.76</v>
       </c>
       <c r="F82" t="n">
-        <v>11.74</v>
+        <v>10.82</v>
       </c>
       <c r="G82" t="n">
-        <v>147.4</v>
+        <v>130.2</v>
       </c>
       <c r="H82" t="n">
-        <v>35.5</v>
+        <v>16.5</v>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J82" t="n">
-        <v>40.93</v>
+        <v>117.31</v>
       </c>
       <c r="K82" t="n">
-        <v>-222.97</v>
+        <v>-38.6</v>
       </c>
       <c r="L82" t="n">
-        <v>226.69</v>
+        <v>123.5</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:07:14</t>
+          <t>10:05:17</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>4.38</v>
+        <v>3.8</v>
       </c>
       <c r="F83" t="n">
-        <v>11.96</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="G83" t="n">
-        <v>139.6</v>
+        <v>132.8</v>
       </c>
       <c r="H83" t="n">
-        <v>33.7</v>
+        <v>28.7</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>234.01</v>
+        <v>63.48</v>
       </c>
       <c r="K83" t="n">
-        <v>60.41</v>
+        <v>188.91</v>
       </c>
       <c r="L83" t="n">
-        <v>241.69</v>
+        <v>199.29</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:09:20</t>
+          <t>10:06:40</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>4.38</v>
+        <v>4.18</v>
       </c>
       <c r="F84" t="n">
-        <v>11.96</v>
+        <v>11.75</v>
       </c>
       <c r="G84" t="n">
-        <v>120.2</v>
+        <v>120.3</v>
       </c>
       <c r="H84" t="n">
-        <v>42.3</v>
+        <v>46.4</v>
       </c>
       <c r="I84" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J84" t="n">
-        <v>143.19</v>
+        <v>111.61</v>
       </c>
       <c r="K84" t="n">
-        <v>-150.58</v>
+        <v>-254.19</v>
       </c>
       <c r="L84" t="n">
-        <v>207.8</v>
+        <v>277.61</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:10:56</t>
+          <t>10:08:32</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>4.3</v>
+        <v>4.12</v>
       </c>
       <c r="F85" t="n">
-        <v>11.96</v>
+        <v>10.76</v>
       </c>
       <c r="G85" t="n">
-        <v>117.8</v>
+        <v>116.7</v>
       </c>
       <c r="H85" t="n">
-        <v>52.7</v>
+        <v>44.7</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J85" t="n">
-        <v>214.26</v>
+        <v>233.62</v>
       </c>
       <c r="K85" t="n">
-        <v>-101.7</v>
+        <v>-181.58</v>
       </c>
       <c r="L85" t="n">
-        <v>237.18</v>
+        <v>295.89</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:16:31</t>
+          <t>10:13:13</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>4.48</v>
+        <v>4.36</v>
       </c>
       <c r="F86" t="n">
         <v>11.96</v>
       </c>
       <c r="G86" t="n">
-        <v>124.1</v>
+        <v>126.2</v>
       </c>
       <c r="H86" t="n">
-        <v>39.8</v>
+        <v>57.3</v>
       </c>
       <c r="I86" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>300.39</v>
+        <v>147.9</v>
       </c>
       <c r="K86" t="n">
-        <v>79.02</v>
+        <v>-371.37</v>
       </c>
       <c r="L86" t="n">
-        <v>310.6</v>
+        <v>399.74</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:18:38</t>
+          <t>10:15:12</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>4.83</v>
+        <v>4.07</v>
       </c>
       <c r="F87" t="n">
-        <v>11.83</v>
+        <v>11.96</v>
       </c>
       <c r="G87" t="n">
-        <v>131.4</v>
+        <v>121.4</v>
       </c>
       <c r="H87" t="n">
-        <v>61.4</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J87" t="n">
-        <v>128.03</v>
+        <v>-213.07</v>
       </c>
       <c r="K87" t="n">
-        <v>389.42</v>
+        <v>-257.48</v>
       </c>
       <c r="L87" t="n">
-        <v>409.93</v>
+        <v>334.21</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:19:29</t>
+          <t>10:17:43</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>4.27</v>
+        <v>4.17</v>
       </c>
       <c r="F88" t="n">
-        <v>11.29</v>
+        <v>11.2</v>
       </c>
       <c r="G88" t="n">
-        <v>130.9</v>
+        <v>117.7</v>
       </c>
       <c r="H88" t="n">
-        <v>52</v>
+        <v>32.2</v>
       </c>
       <c r="I88" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J88" t="n">
-        <v>245.66</v>
+        <v>-71.33</v>
       </c>
       <c r="K88" t="n">
-        <v>96.61</v>
+        <v>-255.54</v>
       </c>
       <c r="L88" t="n">
-        <v>263.97</v>
+        <v>265.31</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-10.xlsx
+++ b/output/2024-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-27.51</v>
+        <v>-29.62</v>
       </c>
       <c r="K14" t="n">
-        <v>45.72</v>
+        <v>49.22</v>
       </c>
       <c r="L14" t="n">
-        <v>53.36</v>
+        <v>57.45</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-50.48</v>
+        <v>-54.66</v>
       </c>
       <c r="K15" t="n">
-        <v>-20.93</v>
+        <v>-22.67</v>
       </c>
       <c r="L15" t="n">
-        <v>54.65</v>
+        <v>59.18</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>52.85</v>
+        <v>52.8</v>
       </c>
       <c r="K16" t="n">
-        <v>-47.1</v>
+        <v>-47.05</v>
       </c>
       <c r="L16" t="n">
-        <v>70.8</v>
+        <v>70.72</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-53.1</v>
+        <v>-60.47</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.36</v>
+        <v>-6.11</v>
       </c>
       <c r="L17" t="n">
-        <v>53.37</v>
+        <v>60.77</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-85.02</v>
+        <v>-85.61</v>
       </c>
       <c r="K18" t="n">
-        <v>-21.59</v>
+        <v>-21.74</v>
       </c>
       <c r="L18" t="n">
-        <v>87.72</v>
+        <v>88.33</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>-37.17</v>
+        <v>-42.46</v>
       </c>
       <c r="K19" t="n">
-        <v>32.96</v>
+        <v>37.65</v>
       </c>
       <c r="L19" t="n">
-        <v>49.68</v>
+        <v>56.75</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>-81.55</v>
+        <v>-96.91</v>
       </c>
       <c r="K20" t="n">
-        <v>-16.98</v>
+        <v>-20.18</v>
       </c>
       <c r="L20" t="n">
-        <v>83.3</v>
+        <v>98.98</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>37.1</v>
+        <v>44.17</v>
       </c>
       <c r="K21" t="n">
-        <v>90.84</v>
+        <v>108.17</v>
       </c>
       <c r="L21" t="n">
-        <v>98.12</v>
+        <v>116.84</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>8.81</v>
+        <v>10.3</v>
       </c>
       <c r="K22" t="n">
-        <v>79.12</v>
+        <v>92.53</v>
       </c>
       <c r="L22" t="n">
-        <v>79.61</v>
+        <v>93.09999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="J23" t="n">
-        <v>-120.56</v>
+        <v>-137.09</v>
       </c>
       <c r="K23" t="n">
-        <v>69.53</v>
+        <v>79.06</v>
       </c>
       <c r="L23" t="n">
-        <v>139.17</v>
+        <v>158.26</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>20.39</v>
+        <v>22.82</v>
       </c>
       <c r="K24" t="n">
-        <v>175.31</v>
+        <v>196.19</v>
       </c>
       <c r="L24" t="n">
-        <v>176.49</v>
+        <v>197.52</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>25</v>
       </c>
       <c r="J25" t="n">
-        <v>-104.74</v>
+        <v>-122.98</v>
       </c>
       <c r="K25" t="n">
-        <v>63.87</v>
+        <v>74.98999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>122.68</v>
+        <v>144.04</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>-14.28</v>
+        <v>-17.13</v>
       </c>
       <c r="K26" t="n">
-        <v>-176.91</v>
+        <v>-212.23</v>
       </c>
       <c r="L26" t="n">
-        <v>177.48</v>
+        <v>212.92</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>184.68</v>
+        <v>234.02</v>
       </c>
       <c r="K27" t="n">
-        <v>-79.64</v>
+        <v>-100.92</v>
       </c>
       <c r="L27" t="n">
-        <v>201.12</v>
+        <v>254.85</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>28</v>
       </c>
       <c r="J28" t="n">
-        <v>172.1</v>
+        <v>201.07</v>
       </c>
       <c r="K28" t="n">
-        <v>-76.23999999999999</v>
+        <v>-89.08</v>
       </c>
       <c r="L28" t="n">
-        <v>188.23</v>
+        <v>219.92</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-66.7</v>
+        <v>-67.36</v>
       </c>
       <c r="K29" t="n">
-        <v>-35.83</v>
+        <v>-36.19</v>
       </c>
       <c r="L29" t="n">
-        <v>75.70999999999999</v>
+        <v>76.45999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-45.77</v>
+        <v>-50.04</v>
       </c>
       <c r="K30" t="n">
-        <v>-24.63</v>
+        <v>-26.93</v>
       </c>
       <c r="L30" t="n">
-        <v>51.98</v>
+        <v>56.83</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>61.5</v>
+        <v>64.39</v>
       </c>
       <c r="K31" t="n">
-        <v>17.34</v>
+        <v>18.16</v>
       </c>
       <c r="L31" t="n">
-        <v>63.9</v>
+        <v>66.90000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>14.16</v>
+        <v>16.61</v>
       </c>
       <c r="K32" t="n">
-        <v>41.49</v>
+        <v>48.67</v>
       </c>
       <c r="L32" t="n">
-        <v>43.84</v>
+        <v>51.43</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>44.27</v>
+        <v>48.22</v>
       </c>
       <c r="K33" t="n">
-        <v>-56.33</v>
+        <v>-61.35</v>
       </c>
       <c r="L33" t="n">
-        <v>71.64</v>
+        <v>78.03</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>32.77</v>
+        <v>35.83</v>
       </c>
       <c r="K34" t="n">
-        <v>51.69</v>
+        <v>56.51</v>
       </c>
       <c r="L34" t="n">
-        <v>61.2</v>
+        <v>66.91</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-4.79</v>
+        <v>-5.39</v>
       </c>
       <c r="K35" t="n">
-        <v>85.3</v>
+        <v>95.94</v>
       </c>
       <c r="L35" t="n">
-        <v>85.43000000000001</v>
+        <v>96.09</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>26</v>
       </c>
       <c r="J36" t="n">
-        <v>-3.8</v>
+        <v>-4.21</v>
       </c>
       <c r="K36" t="n">
-        <v>-94.73999999999999</v>
+        <v>-104.92</v>
       </c>
       <c r="L36" t="n">
-        <v>94.81999999999999</v>
+        <v>105</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-80.59</v>
+        <v>-91.2</v>
       </c>
       <c r="K37" t="n">
-        <v>33.39</v>
+        <v>37.78</v>
       </c>
       <c r="L37" t="n">
-        <v>87.23</v>
+        <v>98.72</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>24</v>
       </c>
       <c r="J38" t="n">
-        <v>192.51</v>
+        <v>208.5</v>
       </c>
       <c r="K38" t="n">
-        <v>-4.64</v>
+        <v>-5.03</v>
       </c>
       <c r="L38" t="n">
-        <v>192.57</v>
+        <v>208.56</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>27</v>
       </c>
       <c r="J39" t="n">
-        <v>85.23</v>
+        <v>105.82</v>
       </c>
       <c r="K39" t="n">
-        <v>62.54</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>105.72</v>
+        <v>131.25</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>10.86</v>
+        <v>11.98</v>
       </c>
       <c r="K40" t="n">
-        <v>-187.84</v>
+        <v>-207.21</v>
       </c>
       <c r="L40" t="n">
-        <v>188.16</v>
+        <v>207.56</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-148.6</v>
+        <v>-186.92</v>
       </c>
       <c r="K41" t="n">
-        <v>-85.03</v>
+        <v>-106.96</v>
       </c>
       <c r="L41" t="n">
-        <v>171.21</v>
+        <v>215.36</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>194.33</v>
+        <v>227.54</v>
       </c>
       <c r="K42" t="n">
-        <v>-81.52</v>
+        <v>-95.45999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>210.74</v>
+        <v>246.75</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>196.72</v>
+        <v>226.84</v>
       </c>
       <c r="K43" t="n">
-        <v>210.61</v>
+        <v>242.86</v>
       </c>
       <c r="L43" t="n">
-        <v>288.2</v>
+        <v>332.32</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-39.29</v>
+        <v>-38.02</v>
       </c>
       <c r="K44" t="n">
-        <v>-64</v>
+        <v>-61.93</v>
       </c>
       <c r="L44" t="n">
-        <v>75.09999999999999</v>
+        <v>72.67</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-6.4</v>
+        <v>-7.33</v>
       </c>
       <c r="K45" t="n">
-        <v>-47.25</v>
+        <v>-54.12</v>
       </c>
       <c r="L45" t="n">
-        <v>47.68</v>
+        <v>54.61</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>31.52</v>
+        <v>36.72</v>
       </c>
       <c r="K46" t="n">
-        <v>-10.11</v>
+        <v>-11.77</v>
       </c>
       <c r="L46" t="n">
-        <v>33.1</v>
+        <v>38.56</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>37.5</v>
+        <v>38.97</v>
       </c>
       <c r="K47" t="n">
-        <v>67.58</v>
+        <v>70.23</v>
       </c>
       <c r="L47" t="n">
-        <v>77.28</v>
+        <v>80.31999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>24.14</v>
+        <v>23.49</v>
       </c>
       <c r="K48" t="n">
-        <v>-112.65</v>
+        <v>-109.59</v>
       </c>
       <c r="L48" t="n">
-        <v>115.21</v>
+        <v>112.08</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.33</v>
+        <v>-12.56</v>
       </c>
       <c r="K49" t="n">
-        <v>-77.61</v>
+        <v>-79.02</v>
       </c>
       <c r="L49" t="n">
-        <v>78.59</v>
+        <v>80.02</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>14.19</v>
+        <v>16.59</v>
       </c>
       <c r="K50" t="n">
-        <v>-98.06</v>
+        <v>-114.61</v>
       </c>
       <c r="L50" t="n">
-        <v>99.08</v>
+        <v>115.8</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>23</v>
       </c>
       <c r="J51" t="n">
-        <v>-78.58</v>
+        <v>-91.45999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>-65.11</v>
+        <v>-75.78</v>
       </c>
       <c r="L51" t="n">
-        <v>102.05</v>
+        <v>118.78</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>26</v>
       </c>
       <c r="J52" t="n">
-        <v>-39.34</v>
+        <v>-47.71</v>
       </c>
       <c r="K52" t="n">
-        <v>69.78</v>
+        <v>84.63</v>
       </c>
       <c r="L52" t="n">
-        <v>80.09999999999999</v>
+        <v>97.16</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>6.76</v>
+        <v>7.85</v>
       </c>
       <c r="K53" t="n">
-        <v>-132.46</v>
+        <v>-153.76</v>
       </c>
       <c r="L53" t="n">
-        <v>132.64</v>
+        <v>153.96</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>83.38</v>
+        <v>99.34</v>
       </c>
       <c r="K54" t="n">
-        <v>100.97</v>
+        <v>120.31</v>
       </c>
       <c r="L54" t="n">
-        <v>130.95</v>
+        <v>156.02</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>-108.23</v>
+        <v>-122.68</v>
       </c>
       <c r="K55" t="n">
-        <v>95.31999999999999</v>
+        <v>108.05</v>
       </c>
       <c r="L55" t="n">
-        <v>144.22</v>
+        <v>163.48</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>97.56</v>
+        <v>121.77</v>
       </c>
       <c r="K56" t="n">
-        <v>-156.44</v>
+        <v>-195.26</v>
       </c>
       <c r="L56" t="n">
-        <v>184.37</v>
+        <v>230.12</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>-251.24</v>
+        <v>-296.11</v>
       </c>
       <c r="K57" t="n">
-        <v>-177.44</v>
+        <v>-209.12</v>
       </c>
       <c r="L57" t="n">
-        <v>307.58</v>
+        <v>362.51</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>22</v>
       </c>
       <c r="J58" t="n">
-        <v>-140.05</v>
+        <v>-182.16</v>
       </c>
       <c r="K58" t="n">
-        <v>100.07</v>
+        <v>130.16</v>
       </c>
       <c r="L58" t="n">
-        <v>172.13</v>
+        <v>223.88</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>64.8</v>
+        <v>67.69</v>
       </c>
       <c r="K59" t="n">
-        <v>26.71</v>
+        <v>27.9</v>
       </c>
       <c r="L59" t="n">
-        <v>70.09</v>
+        <v>73.22</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.48</v>
+        <v>-9.82</v>
       </c>
       <c r="K60" t="n">
-        <v>69.70999999999999</v>
+        <v>72.19</v>
       </c>
       <c r="L60" t="n">
-        <v>70.34999999999999</v>
+        <v>72.84999999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>74.73999999999999</v>
+        <v>76.22</v>
       </c>
       <c r="K61" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="L61" t="n">
-        <v>74.73999999999999</v>
+        <v>76.23</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>30.62</v>
+        <v>29.97</v>
       </c>
       <c r="K62" t="n">
-        <v>-92.08</v>
+        <v>-90.14</v>
       </c>
       <c r="L62" t="n">
-        <v>97.04000000000001</v>
+        <v>94.98999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-61.15</v>
+        <v>-62.66</v>
       </c>
       <c r="K63" t="n">
-        <v>44.47</v>
+        <v>45.57</v>
       </c>
       <c r="L63" t="n">
-        <v>75.61</v>
+        <v>77.48</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>62.67</v>
+        <v>62.3</v>
       </c>
       <c r="K64" t="n">
-        <v>-87.5</v>
+        <v>-86.98</v>
       </c>
       <c r="L64" t="n">
-        <v>107.63</v>
+        <v>106.99</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>73.25</v>
+        <v>83.83</v>
       </c>
       <c r="K65" t="n">
-        <v>-87.27</v>
+        <v>-99.88</v>
       </c>
       <c r="L65" t="n">
-        <v>113.94</v>
+        <v>130.4</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-98.69</v>
+        <v>-111.09</v>
       </c>
       <c r="K66" t="n">
-        <v>18.23</v>
+        <v>20.52</v>
       </c>
       <c r="L66" t="n">
-        <v>100.36</v>
+        <v>112.97</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>19.74</v>
+        <v>21.5</v>
       </c>
       <c r="K67" t="n">
-        <v>-114.95</v>
+        <v>-125.2</v>
       </c>
       <c r="L67" t="n">
-        <v>116.63</v>
+        <v>127.03</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>114.95</v>
+        <v>129.14</v>
       </c>
       <c r="K68" t="n">
-        <v>-92.12</v>
+        <v>-103.5</v>
       </c>
       <c r="L68" t="n">
-        <v>147.31</v>
+        <v>165.5</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>26</v>
       </c>
       <c r="J69" t="n">
-        <v>162.65</v>
+        <v>179.72</v>
       </c>
       <c r="K69" t="n">
-        <v>76.18000000000001</v>
+        <v>84.17</v>
       </c>
       <c r="L69" t="n">
-        <v>179.6</v>
+        <v>198.45</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>131.05</v>
+        <v>161.54</v>
       </c>
       <c r="K70" t="n">
-        <v>41.46</v>
+        <v>51.1</v>
       </c>
       <c r="L70" t="n">
-        <v>137.45</v>
+        <v>169.43</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>-68.12</v>
+        <v>-80.65000000000001</v>
       </c>
       <c r="K71" t="n">
-        <v>-314.94</v>
+        <v>-372.87</v>
       </c>
       <c r="L71" t="n">
-        <v>322.22</v>
+        <v>381.5</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-49.08</v>
+        <v>-64.45</v>
       </c>
       <c r="K72" t="n">
-        <v>192.46</v>
+        <v>252.76</v>
       </c>
       <c r="L72" t="n">
-        <v>198.62</v>
+        <v>260.84</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>249.58</v>
+        <v>287.5</v>
       </c>
       <c r="K73" t="n">
-        <v>30</v>
+        <v>34.55</v>
       </c>
       <c r="L73" t="n">
-        <v>251.38</v>
+        <v>289.57</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>35.43</v>
+        <v>37.78</v>
       </c>
       <c r="K74" t="n">
-        <v>48.08</v>
+        <v>51.27</v>
       </c>
       <c r="L74" t="n">
-        <v>59.73</v>
+        <v>63.69</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-86.8</v>
+        <v>-83.59</v>
       </c>
       <c r="K75" t="n">
-        <v>35.63</v>
+        <v>34.31</v>
       </c>
       <c r="L75" t="n">
-        <v>93.83</v>
+        <v>90.36</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>28.13</v>
+        <v>27.5</v>
       </c>
       <c r="K76" t="n">
-        <v>82.58</v>
+        <v>80.73999999999999</v>
       </c>
       <c r="L76" t="n">
-        <v>87.23999999999999</v>
+        <v>85.3</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-80.23</v>
+        <v>-83.7</v>
       </c>
       <c r="K77" t="n">
-        <v>25.32</v>
+        <v>26.41</v>
       </c>
       <c r="L77" t="n">
-        <v>84.13</v>
+        <v>87.77</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>47.35</v>
+        <v>52.84</v>
       </c>
       <c r="K78" t="n">
-        <v>50.46</v>
+        <v>56.32</v>
       </c>
       <c r="L78" t="n">
-        <v>69.2</v>
+        <v>77.23</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-56.03</v>
+        <v>-61.31</v>
       </c>
       <c r="K79" t="n">
-        <v>45.56</v>
+        <v>49.85</v>
       </c>
       <c r="L79" t="n">
-        <v>72.20999999999999</v>
+        <v>79.02</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>49.6</v>
+        <v>59.57</v>
       </c>
       <c r="K80" t="n">
-        <v>-87.44</v>
+        <v>-105.02</v>
       </c>
       <c r="L80" t="n">
-        <v>100.53</v>
+        <v>120.74</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>28</v>
       </c>
       <c r="J81" t="n">
-        <v>89.22</v>
+        <v>103.52</v>
       </c>
       <c r="K81" t="n">
-        <v>-8.65</v>
+        <v>-10.03</v>
       </c>
       <c r="L81" t="n">
-        <v>89.63</v>
+        <v>104.01</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>22</v>
       </c>
       <c r="J82" t="n">
-        <v>-100.85</v>
+        <v>-117.28</v>
       </c>
       <c r="K82" t="n">
-        <v>-40.09</v>
+        <v>-46.63</v>
       </c>
       <c r="L82" t="n">
-        <v>108.52</v>
+        <v>126.21</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>131.52</v>
+        <v>166.33</v>
       </c>
       <c r="K83" t="n">
-        <v>53.49</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="L83" t="n">
-        <v>141.98</v>
+        <v>179.56</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>27</v>
       </c>
       <c r="J84" t="n">
-        <v>-32.64</v>
+        <v>-39.01</v>
       </c>
       <c r="K84" t="n">
-        <v>125.91</v>
+        <v>150.51</v>
       </c>
       <c r="L84" t="n">
-        <v>130.07</v>
+        <v>155.48</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>108.77</v>
+        <v>132.26</v>
       </c>
       <c r="K85" t="n">
-        <v>-46.05</v>
+        <v>-55.99</v>
       </c>
       <c r="L85" t="n">
-        <v>118.11</v>
+        <v>143.62</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>22</v>
       </c>
       <c r="J86" t="n">
-        <v>155.65</v>
+        <v>199.83</v>
       </c>
       <c r="K86" t="n">
-        <v>-167.16</v>
+        <v>-214.61</v>
       </c>
       <c r="L86" t="n">
-        <v>228.4</v>
+        <v>293.24</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>25</v>
       </c>
       <c r="J87" t="n">
-        <v>70.51000000000001</v>
+        <v>81.77</v>
       </c>
       <c r="K87" t="n">
-        <v>-223.19</v>
+        <v>-258.82</v>
       </c>
       <c r="L87" t="n">
-        <v>234.06</v>
+        <v>271.43</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>28</v>
       </c>
       <c r="J88" t="n">
-        <v>295.34</v>
+        <v>336.83</v>
       </c>
       <c r="K88" t="n">
-        <v>225.08</v>
+        <v>256.7</v>
       </c>
       <c r="L88" t="n">
-        <v>371.33</v>
+        <v>423.49</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-09-10.xlsx
+++ b/output/2024-09-10.xlsx
@@ -640,13 +640,13 @@
         <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-29.62</v>
+        <v>-32.66</v>
       </c>
       <c r="K14" t="n">
-        <v>49.22</v>
+        <v>54.28</v>
       </c>
       <c r="L14" t="n">
-        <v>57.45</v>
+        <v>63.34</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-54.66</v>
+        <v>-59.68</v>
       </c>
       <c r="K15" t="n">
-        <v>-22.67</v>
+        <v>-24.75</v>
       </c>
       <c r="L15" t="n">
-        <v>59.18</v>
+        <v>64.61</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>52.8</v>
+        <v>53.17</v>
       </c>
       <c r="K16" t="n">
-        <v>-47.05</v>
+        <v>-47.38</v>
       </c>
       <c r="L16" t="n">
-        <v>70.72</v>
+        <v>71.22</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>27</v>
       </c>
       <c r="J17" t="n">
-        <v>-60.47</v>
+        <v>-62.99</v>
       </c>
       <c r="K17" t="n">
-        <v>-6.11</v>
+        <v>-6.36</v>
       </c>
       <c r="L17" t="n">
-        <v>60.77</v>
+        <v>63.31</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-85.61</v>
+        <v>-92.02</v>
       </c>
       <c r="K18" t="n">
-        <v>-21.74</v>
+        <v>-23.36</v>
       </c>
       <c r="L18" t="n">
-        <v>88.33</v>
+        <v>94.94</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>-42.46</v>
+        <v>-44.73</v>
       </c>
       <c r="K19" t="n">
-        <v>37.65</v>
+        <v>39.66</v>
       </c>
       <c r="L19" t="n">
-        <v>56.75</v>
+        <v>59.78</v>
       </c>
     </row>
     <row r="20">
@@ -1270,13 +1270,13 @@
         <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>-67.36</v>
+        <v>-75.47</v>
       </c>
       <c r="K29" t="n">
-        <v>-36.19</v>
+        <v>-40.54</v>
       </c>
       <c r="L29" t="n">
-        <v>76.45999999999999</v>
+        <v>85.68000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>-50.04</v>
+        <v>-60.96</v>
       </c>
       <c r="K30" t="n">
-        <v>-26.93</v>
+        <v>-32.81</v>
       </c>
       <c r="L30" t="n">
-        <v>56.83</v>
+        <v>69.23</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>23</v>
       </c>
       <c r="J31" t="n">
-        <v>64.39</v>
+        <v>86.64</v>
       </c>
       <c r="K31" t="n">
-        <v>18.16</v>
+        <v>24.43</v>
       </c>
       <c r="L31" t="n">
-        <v>66.90000000000001</v>
+        <v>90.02</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>16.61</v>
+        <v>17.75</v>
       </c>
       <c r="K32" t="n">
-        <v>48.67</v>
+        <v>52.01</v>
       </c>
       <c r="L32" t="n">
-        <v>51.43</v>
+        <v>54.96</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>22</v>
       </c>
       <c r="J33" t="n">
-        <v>48.22</v>
+        <v>55.91</v>
       </c>
       <c r="K33" t="n">
-        <v>-61.35</v>
+        <v>-71.13</v>
       </c>
       <c r="L33" t="n">
-        <v>78.03</v>
+        <v>90.48</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>35.83</v>
+        <v>41.8</v>
       </c>
       <c r="K34" t="n">
-        <v>56.51</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>66.91</v>
+        <v>78.06</v>
       </c>
     </row>
     <row r="35">
@@ -1900,13 +1900,13 @@
         <v>28</v>
       </c>
       <c r="J44" t="n">
-        <v>-38.02</v>
+        <v>-42.43</v>
       </c>
       <c r="K44" t="n">
-        <v>-61.93</v>
+        <v>-69.11</v>
       </c>
       <c r="L44" t="n">
-        <v>72.67</v>
+        <v>81.09999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.33</v>
+        <v>-8.98</v>
       </c>
       <c r="K45" t="n">
-        <v>-54.12</v>
+        <v>-66.33</v>
       </c>
       <c r="L45" t="n">
-        <v>54.61</v>
+        <v>66.94</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>36.72</v>
+        <v>43.29</v>
       </c>
       <c r="K46" t="n">
-        <v>-11.77</v>
+        <v>-13.88</v>
       </c>
       <c r="L46" t="n">
-        <v>38.56</v>
+        <v>45.46</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>27</v>
       </c>
       <c r="J47" t="n">
-        <v>38.97</v>
+        <v>46.24</v>
       </c>
       <c r="K47" t="n">
-        <v>70.23</v>
+        <v>83.33</v>
       </c>
       <c r="L47" t="n">
-        <v>80.31999999999999</v>
+        <v>95.3</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>23.49</v>
+        <v>29.83</v>
       </c>
       <c r="K48" t="n">
-        <v>-109.59</v>
+        <v>-139.19</v>
       </c>
       <c r="L48" t="n">
-        <v>112.08</v>
+        <v>142.35</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-12.56</v>
+        <v>-13.52</v>
       </c>
       <c r="K49" t="n">
-        <v>-79.02</v>
+        <v>-85.06999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>80.02</v>
+        <v>86.13</v>
       </c>
     </row>
     <row r="50">
@@ -2530,13 +2530,13 @@
         <v>22</v>
       </c>
       <c r="J59" t="n">
-        <v>67.69</v>
+        <v>85.37</v>
       </c>
       <c r="K59" t="n">
-        <v>27.9</v>
+        <v>35.19</v>
       </c>
       <c r="L59" t="n">
-        <v>73.22</v>
+        <v>92.34</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-9.82</v>
+        <v>-13.77</v>
       </c>
       <c r="K60" t="n">
-        <v>72.19</v>
+        <v>101.26</v>
       </c>
       <c r="L60" t="n">
-        <v>72.84999999999999</v>
+        <v>102.19</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>76.22</v>
+        <v>88.23</v>
       </c>
       <c r="K61" t="n">
-        <v>0.79</v>
+        <v>0.92</v>
       </c>
       <c r="L61" t="n">
-        <v>76.23</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>29.97</v>
+        <v>33.96</v>
       </c>
       <c r="K62" t="n">
-        <v>-90.14</v>
+        <v>-102.13</v>
       </c>
       <c r="L62" t="n">
-        <v>94.98999999999999</v>
+        <v>107.63</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>28</v>
       </c>
       <c r="J63" t="n">
-        <v>-62.66</v>
+        <v>-70.23999999999999</v>
       </c>
       <c r="K63" t="n">
-        <v>45.57</v>
+        <v>51.08</v>
       </c>
       <c r="L63" t="n">
-        <v>77.48</v>
+        <v>86.84999999999999</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>62.3</v>
+        <v>75.78</v>
       </c>
       <c r="K64" t="n">
-        <v>-86.98</v>
+        <v>-105.79</v>
       </c>
       <c r="L64" t="n">
-        <v>106.99</v>
+        <v>130.13</v>
       </c>
     </row>
     <row r="65">
@@ -3160,13 +3160,13 @@
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>37.78</v>
+        <v>53.1</v>
       </c>
       <c r="K74" t="n">
-        <v>51.27</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="L74" t="n">
-        <v>63.69</v>
+        <v>89.52</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>27</v>
       </c>
       <c r="J75" t="n">
-        <v>-83.59</v>
+        <v>-115.65</v>
       </c>
       <c r="K75" t="n">
-        <v>34.31</v>
+        <v>47.47</v>
       </c>
       <c r="L75" t="n">
-        <v>90.36</v>
+        <v>125.02</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>27.5</v>
+        <v>33.99</v>
       </c>
       <c r="K76" t="n">
-        <v>80.73999999999999</v>
+        <v>99.78</v>
       </c>
       <c r="L76" t="n">
-        <v>85.3</v>
+        <v>105.41</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>22</v>
       </c>
       <c r="J77" t="n">
-        <v>-83.7</v>
+        <v>-94.39</v>
       </c>
       <c r="K77" t="n">
-        <v>26.41</v>
+        <v>29.79</v>
       </c>
       <c r="L77" t="n">
-        <v>87.77</v>
+        <v>98.98</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>52.84</v>
+        <v>66.09</v>
       </c>
       <c r="K78" t="n">
-        <v>56.32</v>
+        <v>70.44</v>
       </c>
       <c r="L78" t="n">
-        <v>77.23</v>
+        <v>96.59</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-61.31</v>
+        <v>-77.75</v>
       </c>
       <c r="K79" t="n">
-        <v>49.85</v>
+        <v>63.22</v>
       </c>
       <c r="L79" t="n">
-        <v>79.02</v>
+        <v>100.21</v>
       </c>
     </row>
     <row r="80">
